--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -892,121 +892,145 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1">
+    <row r="5" ht="135" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
-        </is>
-      </c>
-      <c r="C5" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C5" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="5" t="inlineStr"/>
-      <c r="J5" s="5" t="inlineStr"/>
-      <c r="K5" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I5" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J5" s="5" t="inlineStr">
+        <is>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
+        </is>
+      </c>
+      <c r="K5" s="10" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
-      <c r="N5" s="8" t="inlineStr"/>
-    </row>
-    <row r="6" ht="135" customHeight="1">
+      <c r="N5" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C6" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C6" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
-        </is>
-      </c>
-      <c r="K6" s="10" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K6" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C7" s="11" t="inlineStr">
@@ -1016,37 +1040,29 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K7" s="12" t="inlineStr">
@@ -1056,27 +1072,27 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C8" s="11" t="inlineStr">
@@ -1086,31 +1102,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1123,22 +1135,18 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1148,27 +1156,39 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K9" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1181,18 +1201,22 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1202,37 +1226,37 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1247,22 +1271,22 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="105" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1272,22 +1296,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1297,12 +1321,12 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K11" s="12" t="inlineStr">
@@ -1312,27 +1336,27 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1342,37 +1366,37 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1382,27 +1406,27 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1412,39 +1436,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1457,22 +1469,18 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="120" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1482,27 +1490,39 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
       <c r="K14" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1510,23 +1530,27 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1541,32 +1565,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1586,7 +1610,7 @@
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1596,7 +1620,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1611,17 +1635,17 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1631,12 +1655,12 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K16" s="12" t="inlineStr">
@@ -1656,17 +1680,17 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1681,32 +1705,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1716,27 +1740,27 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="180" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1751,32 +1775,32 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1791,22 +1815,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1821,32 +1845,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1861,22 +1885,22 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1886,37 +1910,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1926,27 +1950,27 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1956,22 +1980,22 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1981,12 +2005,12 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2001,12 +2025,12 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2040,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2031,32 +2055,32 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2071,22 +2095,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="105" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2096,37 +2120,29 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2136,27 +2152,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2166,29 +2182,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2198,27 +2222,27 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2228,37 +2252,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2268,27 +2292,27 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="75" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -2298,39 +2322,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2343,22 +2355,18 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2368,27 +2376,39 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
       <c r="K27" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2401,18 +2421,22 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -2422,37 +2446,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2462,17 +2486,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2482,7 +2506,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2497,17 +2521,17 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2517,12 +2541,12 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K29" s="12" t="inlineStr">
@@ -2537,22 +2561,22 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="75" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>TARGET-CAP-10WK</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -2562,39 +2586,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2602,57 +2614,65 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="75" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>shipped (diagnosis); pending (fix)</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
+        </is>
+      </c>
       <c r="K31" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2660,23 +2680,27 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
+          <t>9bc015562</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="45" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2686,37 +2710,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2726,17 +2750,17 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2746,7 +2770,7 @@
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2761,22 +2785,22 @@
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
@@ -2786,7 +2810,7 @@
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K33" s="12" t="inlineStr">
@@ -2806,7 +2830,7 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -2816,7 +2840,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2831,32 +2855,32 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2876,17 +2900,17 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2901,32 +2925,32 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2946,7 +2970,7 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -2956,7 +2980,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2966,37 +2990,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3011,22 +3035,22 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="90" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3041,32 +3065,32 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3086,17 +3110,17 @@
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="45" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3106,37 +3130,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3146,27 +3170,27 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3176,22 +3200,22 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
@@ -3201,12 +3225,12 @@
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3221,22 +3245,22 @@
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3246,37 +3270,33 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr"/>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3286,27 +3306,27 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="75" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3321,28 +3341,28 @@
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3362,17 +3382,17 @@
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="135" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3382,33 +3402,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr"/>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / High win</t>
+        </is>
+      </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3423,22 +3447,22 @@
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="135" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="45" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3448,37 +3472,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3488,17 +3512,17 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -3508,7 +3532,7 @@
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3523,32 +3547,32 @@
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3563,22 +3587,22 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="120" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3593,32 +3617,32 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3628,27 +3652,27 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="135" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3663,32 +3687,32 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3703,22 +3727,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="75" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3728,37 +3752,29 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I47" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr"/>
+      <c r="I47" s="5" t="inlineStr"/>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3773,22 +3789,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="75" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="105" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3798,29 +3814,37 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3835,22 +3859,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="60" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3865,32 +3889,32 @@
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3905,22 +3929,22 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="105" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3935,32 +3959,32 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -3975,22 +3999,22 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="105" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4000,37 +4024,37 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4040,27 +4064,27 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="120" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4070,37 +4094,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4110,7 +4134,7 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
@@ -4120,17 +4144,17 @@
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="120" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="75" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4140,37 +4164,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4180,27 +4204,27 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4215,17 +4239,17 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
@@ -4235,12 +4259,12 @@
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -4260,17 +4284,17 @@
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4280,22 +4304,22 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4305,12 +4329,12 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4325,22 +4349,22 @@
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="90" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4350,37 +4374,37 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
@@ -4390,17 +4414,17 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -4410,7 +4434,7 @@
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4420,39 +4444,27 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>shipped (additive only)</t>
-        </is>
-      </c>
-      <c r="I57" s="5" t="inlineStr">
-        <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
-        </is>
-      </c>
-      <c r="J57" s="5" t="inlineStr">
-        <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
-        </is>
-      </c>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr"/>
+      <c r="I57" s="5" t="inlineStr"/>
+      <c r="J57" s="5" t="inlineStr"/>
       <c r="K57" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4465,22 +4477,18 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N57" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="90" customHeight="1">
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N57" s="8" t="inlineStr"/>
+    </row>
+    <row r="58" ht="105" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4490,27 +4498,31 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr"/>
       <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
       <c r="K58" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4523,18 +4535,22 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N58" s="8" t="inlineStr"/>
-    </row>
-    <row r="59" ht="105" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N58" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="45" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4544,29 +4560,37 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4581,22 +4605,22 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="90" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4606,37 +4630,37 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I60" s="5" t="inlineStr">
         <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
+          <t>Low / High (transparency + future-proof)</t>
         </is>
       </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
         </is>
       </c>
       <c r="K60" s="12" t="inlineStr">
@@ -4651,22 +4675,22 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="90" customHeight="1">
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="75" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4676,39 +4700,27 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>Low / High (transparency + future-proof)</t>
-        </is>
-      </c>
-      <c r="J61" s="5" t="inlineStr">
-        <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr"/>
       <c r="K61" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4721,22 +4733,18 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N61" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="75" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N61" s="8" t="inlineStr"/>
+    </row>
+    <row r="62" ht="60" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4746,27 +4754,39 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
       <c r="K62" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4774,23 +4794,27 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N62" s="8" t="inlineStr"/>
-    </row>
-    <row r="63" ht="60" customHeight="1">
+          <t>16a26b201</t>
+        </is>
+      </c>
+      <c r="N62" s="8" t="inlineStr">
+        <is>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="45" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4800,37 +4824,37 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr">
@@ -4845,22 +4869,22 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="105" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4875,32 +4899,24 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K64" s="12" t="inlineStr">
@@ -4910,17 +4926,17 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
         </is>
       </c>
     </row>
@@ -4930,7 +4946,7 @@
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4945,24 +4961,24 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr"/>
       <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
@@ -4977,22 +4993,22 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="105" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5002,29 +5018,37 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>All reads use ?? fallbacks.</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
@@ -5039,12 +5063,12 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
         </is>
       </c>
     </row>
@@ -5054,7 +5078,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5064,39 +5088,35 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I67" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr">
-        <is>
-          <t>All reads use ?? fallbacks.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J67" s="5" t="inlineStr"/>
       <c r="K67" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5109,22 +5129,22 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="105" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5134,35 +5154,39 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr"/>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K68" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5175,64 +5199,60 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="105" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="60" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
-        </is>
-      </c>
-      <c r="C69" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="C69" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
       <c r="K69" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5240,27 +5260,27 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="75" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C70" s="9" t="inlineStr">
@@ -5275,17 +5295,17 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
@@ -5295,10 +5315,14 @@
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr"/>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K70" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5311,12 +5335,12 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
         </is>
       </c>
     </row>
@@ -5326,7 +5350,7 @@
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5341,34 +5365,22 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I71" s="5" t="inlineStr">
-        <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr"/>
+      <c r="I71" s="5" t="inlineStr"/>
+      <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5376,27 +5388,23 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N71" s="8" t="inlineStr">
-        <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="75" customHeight="1">
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="inlineStr"/>
+    </row>
+    <row r="72" ht="45" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5406,26 +5414,34 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J72" s="5" t="inlineStr"/>
       <c r="K72" s="12" t="inlineStr">
         <is>
@@ -5434,15 +5450,19 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N72" s="8" t="inlineStr"/>
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N72" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
     </row>
     <row r="73" ht="45" customHeight="1">
       <c r="A73" s="2" t="n">
@@ -5450,7 +5470,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5460,35 +5480,39 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr"/>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K73" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5496,27 +5520,27 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="45" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="75" customHeight="1">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -5526,37 +5550,37 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J74" s="5" t="inlineStr">
         <is>
-          <t>Sub-task of IPAD-1.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K74" s="12" t="inlineStr">
@@ -5566,27 +5590,27 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="75" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="60" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5596,37 +5620,37 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K75" s="12" t="inlineStr">
@@ -5636,17 +5660,17 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -5656,7 +5680,7 @@
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5671,32 +5695,32 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
@@ -5716,7 +5740,7 @@
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -5726,7 +5750,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5741,32 +5765,32 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr">
@@ -5786,7 +5810,7 @@
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
         </is>
       </c>
     </row>
@@ -5796,7 +5820,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5811,32 +5835,32 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
@@ -5846,27 +5870,27 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="60" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="150" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5876,37 +5900,29 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I79" s="5" t="inlineStr">
-        <is>
-          <t>Win: fast iteration on report templates.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr"/>
+      <c r="I79" s="5" t="inlineStr"/>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr">
@@ -5916,27 +5932,27 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="150" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="105" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5946,29 +5962,29 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr"/>
       <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
@@ -5978,27 +5994,27 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="105" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="135" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -6008,29 +6024,37 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
@@ -6040,27 +6064,27 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>42c36ef91</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="135" customHeight="1">
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="120" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -6070,37 +6094,29 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr">
@@ -6110,17 +6126,17 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
         </is>
       </c>
     </row>
@@ -6635,10 +6651,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
     </row>
     <row r="3">
@@ -6673,10 +6689,10 @@
         <v>38</v>
       </c>
       <c r="D4" s="18" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -615,7 +615,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N89"/>
+  <dimension ref="A1:N92"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -706,13 +706,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="45" customHeight="1">
+    <row r="2" ht="105" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -722,37 +722,37 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Win: cleaner repo.</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Calendar reminder for 2026-05-16.</t>
+          <t>Discovered while diagnosing F3/F4 fold mystery. Phantom 0% trades created false 'PF 999' sentinel in WF aggregate, masking that only F1+F2 had real evidence. Verdict framework was applying to apparent 4 folds but only 2 were informative.</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -764,17 +764,17 @@
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="60" customHeight="1">
+          <t>Run any backtest with --days 100+ on a low-volatility period. Confirm trades that don't exit show pnl != 0.0 (real MTM). Then verify F3/F4 type windows produce proper attribution data.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="45" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -784,37 +784,37 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Win: cleaner repo.</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Calendar reminder for 2026-05-16.</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -830,53 +830,53 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="60" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>QUANT-5</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Caveat: exploratory research, not config-tuning.</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -892,261 +892,261 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="135" customHeight="1">
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C5" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C5" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: -X lines.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
-        </is>
-      </c>
-      <c r="K5" s="10" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
+          <t>Couples with OPS-1.</t>
+        </is>
+      </c>
+      <c r="K5" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr"/>
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="75" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="90" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C6" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>CONVICTION-TIER-WIRE</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Conviction tier is decorative — wire as filter or delete</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>2-4 hrs + backtest validation</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>Medium — changes live size or eliminates a layer</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K6" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>2c9b9f339</t>
-        </is>
-      </c>
+          <t>Discovered while reworking T1 bar today. Today's T1 88-&gt;85 was reverted because lowering doesn't matter when the tier isn't gating anyway.</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
+          <t>python3 -c 'from collections import Counter; import json; sl=json.load(open("data/signal_log.json")); c=Counter((s.get("conviction_label") or "none").upper() for s in sl if s.get("status")=="CLOSED"); print(c)' — expect 'NONE' (or '—') for ~90%+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
-        </is>
-      </c>
-      <c r="C7" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>1 day + backtest</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>High win potential, medium risk</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
-      <c r="K7" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="135" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C8" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
-      <c r="K8" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M8" s="3" t="inlineStr">
-        <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Win: catches accidental layout regressions.</t>
+        </is>
+      </c>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
+        </is>
+      </c>
+      <c r="K8" s="10" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr"/>
+      <c r="M8" s="3" t="inlineStr"/>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1156,37 +1156,37 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I9" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1196,17 +1196,17 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>2c9b9f339</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1226,37 +1226,29 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K10" s="12" t="inlineStr">
@@ -1271,22 +1263,22 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="75" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1296,39 +1288,27 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I11" s="5" t="inlineStr">
-        <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
-        </is>
-      </c>
-      <c r="J11" s="5" t="inlineStr">
-        <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="5" t="inlineStr"/>
+      <c r="J11" s="5" t="inlineStr"/>
       <c r="K11" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1336,19 +1316,15 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr"/>
     </row>
     <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="n">
@@ -1356,7 +1332,7 @@
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1366,22 +1342,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1391,12 +1367,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Low / Required</t>
+          <t>CRITICAL — system was unable to backtest</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1411,22 +1387,22 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="120" customHeight="1">
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="90" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1436,27 +1412,39 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
       <c r="K13" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1469,18 +1457,22 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="105" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1490,37 +1482,37 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1535,12 +1527,12 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
         </is>
       </c>
     </row>
@@ -1550,7 +1542,7 @@
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1560,37 +1552,37 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K15" s="12" t="inlineStr">
@@ -1600,27 +1592,27 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="120" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1630,39 +1622,27 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>2 min</t>
-        </is>
-      </c>
-      <c r="I16" s="5" t="inlineStr">
-        <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
-        </is>
-      </c>
-      <c r="J16" s="5" t="inlineStr">
-        <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr"/>
+      <c r="I16" s="5" t="inlineStr"/>
+      <c r="J16" s="5" t="inlineStr"/>
       <c r="K16" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1670,19 +1650,15 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr">
-        <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr"/>
     </row>
     <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
@@ -1690,7 +1666,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1705,32 +1681,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1740,27 +1716,27 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="180" customHeight="1">
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1775,32 +1751,32 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1810,17 +1786,17 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1830,7 +1806,7 @@
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1845,32 +1821,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1880,27 +1856,27 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="60" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1910,37 +1886,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1950,27 +1926,27 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="180" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1980,37 +1956,37 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2020,17 +1996,17 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
         </is>
       </c>
     </row>
@@ -2040,7 +2016,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2050,37 +2026,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2090,27 +2066,27 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="105" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="90" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2120,29 +2096,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+        </is>
+      </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2152,27 +2136,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2182,22 +2166,22 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
@@ -2207,12 +2191,12 @@
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2227,22 +2211,22 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="90" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="45" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2252,37 +2236,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2292,27 +2276,27 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="75" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="105" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -2322,27 +2306,31 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr"/>
       <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+        </is>
+      </c>
       <c r="K26" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2355,18 +2343,22 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr"/>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t>f0a66543e + 363984181</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="60" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2376,37 +2368,37 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2416,27 +2408,27 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="90" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -2446,37 +2438,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K28" s="12" t="inlineStr">
@@ -2486,27 +2478,27 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="75" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2516,39 +2508,27 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I29" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J29" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr"/>
+      <c r="I29" s="5" t="inlineStr"/>
+      <c r="J29" s="5" t="inlineStr"/>
       <c r="K29" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2556,27 +2536,23 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr"/>
+    </row>
+    <row r="30" ht="45" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -2586,27 +2562,39 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
       <c r="K30" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2619,10 +2607,14 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr"/>
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
@@ -2630,47 +2622,47 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C31" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2685,62 +2677,62 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="45" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C32" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K32" s="12" t="inlineStr">
@@ -2750,69 +2742,57 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="75" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
-        </is>
-      </c>
-      <c r="C33" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TARGET-CAP-10WK</t>
+        </is>
+      </c>
+      <c r="C33" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I33" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / High win</t>
-        </is>
-      </c>
-      <c r="J33" s="5" t="inlineStr">
-        <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr"/>
+      <c r="I33" s="5" t="inlineStr"/>
+      <c r="J33" s="5" t="inlineStr"/>
       <c r="K33" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2825,22 +2805,18 @@
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr">
-        <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr"/>
+    </row>
+    <row r="34" ht="60" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2850,37 +2826,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2890,27 +2866,27 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="60" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="45" customHeight="1">
       <c r="A35" s="2" t="n">
         <v>34</v>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2925,32 +2901,32 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K35" s="12" t="inlineStr">
@@ -2970,17 +2946,17 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2990,37 +2966,37 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K36" s="12" t="inlineStr">
@@ -3035,22 +3011,22 @@
       </c>
       <c r="M36" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="90" customHeight="1">
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3060,37 +3036,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K37" s="12" t="inlineStr">
@@ -3105,22 +3081,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3130,37 +3106,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K38" s="12" t="inlineStr">
@@ -3170,17 +3146,17 @@
       </c>
       <c r="L38" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -3190,7 +3166,7 @@
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3200,37 +3176,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K39" s="12" t="inlineStr">
@@ -3240,17 +3216,17 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
         </is>
       </c>
     </row>
@@ -3260,7 +3236,7 @@
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3270,33 +3246,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I40" s="5" t="inlineStr"/>
+          <t>30 min after answers</t>
+        </is>
+      </c>
+      <c r="I40" s="5" t="inlineStr">
+        <is>
+          <t>Win: ~3-5K lines if mostly stale.</t>
+        </is>
+      </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K40" s="12" t="inlineStr">
@@ -3311,22 +3291,22 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="75" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3336,33 +3316,37 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+        </is>
+      </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K41" s="12" t="inlineStr">
@@ -3372,27 +3356,27 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="135" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3402,37 +3386,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K42" s="12" t="inlineStr">
@@ -3442,27 +3426,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="45" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="90" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3472,37 +3456,33 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K43" s="12" t="inlineStr">
@@ -3512,27 +3492,27 @@
       </c>
       <c r="L43" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3542,37 +3522,33 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Win: -50ms FCP.</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K44" s="12" t="inlineStr">
@@ -3582,27 +3558,27 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="120" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="135" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3612,37 +3588,37 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K45" s="12" t="inlineStr">
@@ -3657,22 +3633,22 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="135" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3687,32 +3663,32 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K46" s="12" t="inlineStr">
@@ -3722,27 +3698,27 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="75" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3752,29 +3728,37 @@
       </c>
       <c r="D47" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H47" s="2" t="inlineStr"/>
-      <c r="I47" s="5" t="inlineStr"/>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>15 min</t>
+        </is>
+      </c>
+      <c r="I47" s="5" t="inlineStr">
+        <is>
+          <t>Win: -50ms FCP.</t>
+        </is>
+      </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K47" s="12" t="inlineStr">
@@ -3784,27 +3768,27 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="105" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="120" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3814,37 +3798,37 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K48" s="12" t="inlineStr">
@@ -3859,22 +3843,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="60" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="135" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3884,37 +3868,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H49" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I49" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K49" s="12" t="inlineStr">
@@ -3929,22 +3913,22 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="105" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="75" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3954,37 +3938,29 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K50" s="12" t="inlineStr">
@@ -3999,22 +3975,22 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="60" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="105" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4024,37 +4000,37 @@
       </c>
       <c r="D51" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K51" s="12" t="inlineStr">
@@ -4064,27 +4040,27 @@
       </c>
       <c r="L51" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="120" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4094,37 +4070,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K52" s="12" t="inlineStr">
@@ -4139,22 +4115,22 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="75" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="105" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4164,37 +4140,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K53" s="12" t="inlineStr">
@@ -4204,17 +4180,17 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
         </is>
       </c>
     </row>
@@ -4224,7 +4200,7 @@
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4234,37 +4210,37 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K54" s="12" t="inlineStr">
@@ -4279,22 +4255,22 @@
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="120" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4304,37 +4280,37 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K55" s="12" t="inlineStr">
@@ -4344,27 +4320,27 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="90" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4374,37 +4350,37 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K56" s="12" t="inlineStr">
@@ -4414,27 +4390,27 @@
       </c>
       <c r="L56" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="90" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4444,27 +4420,39 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr"/>
-      <c r="I57" s="5" t="inlineStr"/>
-      <c r="J57" s="5" t="inlineStr"/>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I57" s="5" t="inlineStr">
+        <is>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+        </is>
+      </c>
+      <c r="J57" s="5" t="inlineStr">
+        <is>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+        </is>
+      </c>
       <c r="K57" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4472,23 +4460,27 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N57" s="8" t="inlineStr"/>
-    </row>
-    <row r="58" ht="105" customHeight="1">
+          <t>3d4eb71d7</t>
+        </is>
+      </c>
+      <c r="N57" s="8" t="inlineStr">
+        <is>
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="75" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4498,29 +4490,37 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+        </is>
+      </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K58" s="12" t="inlineStr">
@@ -4530,27 +4530,27 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="45" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="90" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4560,37 +4560,37 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I59" s="5" t="inlineStr">
         <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J59" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K59" s="12" t="inlineStr">
@@ -4605,12 +4605,12 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N59" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -4620,7 +4620,7 @@
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4630,39 +4630,27 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>Low / High (transparency + future-proof)</t>
-        </is>
-      </c>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
-        </is>
-      </c>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
+      <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4675,22 +4663,18 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="75" customHeight="1">
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61" ht="105" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4700,27 +4684,31 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr"/>
       <c r="I61" s="5" t="inlineStr"/>
-      <c r="J61" s="5" t="inlineStr"/>
+      <c r="J61" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
       <c r="K61" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4733,18 +4721,22 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N61" s="8" t="inlineStr"/>
-    </row>
-    <row r="62" ht="60" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N61" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4754,37 +4746,37 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K62" s="12" t="inlineStr">
@@ -4794,27 +4786,27 @@
       </c>
       <c r="L62" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="45" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="90" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4824,37 +4816,37 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I63" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Low / High (transparency + future-proof)</t>
         </is>
       </c>
       <c r="J63" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
         </is>
       </c>
       <c r="K63" s="12" t="inlineStr">
@@ -4864,27 +4856,27 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N63" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="105" customHeight="1">
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="75" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4894,31 +4886,27 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr"/>
       <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
-        </is>
-      </c>
+      <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4931,22 +4919,18 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
-        </is>
-      </c>
-      <c r="N64" s="8" t="inlineStr">
-        <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="105" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4956,29 +4940,37 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K65" s="12" t="inlineStr">
@@ -4988,17 +4980,17 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
         </is>
       </c>
     </row>
@@ -5008,7 +5000,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5018,37 +5010,37 @@
       </c>
       <c r="D66" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I66" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (consistency)</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K66" s="12" t="inlineStr">
@@ -5058,27 +5050,27 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="105" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5088,35 +5080,31 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J67" s="5" t="inlineStr"/>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
+      <c r="J67" s="5" t="inlineStr">
+        <is>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+        </is>
+      </c>
       <c r="K67" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5129,12 +5117,12 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
         </is>
       </c>
     </row>
@@ -5144,7 +5132,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5154,37 +5142,29 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>1.5 hrs</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K68" s="12" t="inlineStr">
@@ -5199,60 +5179,64 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="60" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C69" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-2</t>
+        </is>
+      </c>
+      <c r="C69" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr"/>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K69" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5260,69 +5244,65 @@
       </c>
       <c r="L69" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="75" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="45" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>RULE-1</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5330,57 +5310,69 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="75" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="105" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TARGET-SOURCES-P1</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H71" s="2" t="inlineStr"/>
-      <c r="I71" s="5" t="inlineStr"/>
-      <c r="J71" s="5" t="inlineStr"/>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>1.5 hrs</t>
+        </is>
+      </c>
+      <c r="I71" s="5" t="inlineStr">
+        <is>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K71" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5393,18 +5385,22 @@
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N71" s="8" t="inlineStr"/>
-    </row>
-    <row r="72" ht="45" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N71" s="8" t="inlineStr">
+        <is>
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5414,22 +5410,22 @@
       </c>
       <c r="D72" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5439,7 +5435,7 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
+          <t>Win: future Claude sessions discover new tools.</t>
         </is>
       </c>
       <c r="J72" s="5" t="inlineStr"/>
@@ -5455,22 +5451,22 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="45" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="75" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5480,37 +5476,37 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H73" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I73" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Win: clear activation procedure before flipping live.</t>
         </is>
       </c>
       <c r="J73" s="5" t="inlineStr">
         <is>
-          <t>Sub-task of IPAD-1.</t>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
         </is>
       </c>
       <c r="K73" s="12" t="inlineStr">
@@ -5520,17 +5516,17 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N73" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
         </is>
       </c>
     </row>
@@ -5540,7 +5536,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -5550,39 +5546,27 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr"/>
+      <c r="J74" s="5" t="inlineStr"/>
       <c r="K74" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5590,27 +5574,23 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N74" s="8" t="inlineStr">
-        <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="60" customHeight="1">
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N74" s="8" t="inlineStr"/>
+    </row>
+    <row r="75" ht="45" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5620,39 +5600,35 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr"/>
       <c r="K75" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5660,27 +5636,27 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5690,37 +5666,37 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Sub-task of IPAD-1.</t>
         </is>
       </c>
       <c r="K76" s="12" t="inlineStr">
@@ -5735,22 +5711,22 @@
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="60" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="75" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5760,37 +5736,37 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K77" s="12" t="inlineStr">
@@ -5800,17 +5776,17 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -5820,7 +5796,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5835,32 +5811,32 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K78" s="12" t="inlineStr">
@@ -5870,27 +5846,27 @@
       </c>
       <c r="L78" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M78" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="79" ht="150" customHeight="1">
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+        </is>
+      </c>
+    </row>
+    <row r="79" ht="60" customHeight="1">
       <c r="A79" s="2" t="n">
         <v>78</v>
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5900,29 +5876,37 @@
       </c>
       <c r="D79" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H79" s="2" t="inlineStr"/>
-      <c r="I79" s="5" t="inlineStr"/>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+        </is>
+      </c>
+      <c r="H79" s="2" t="inlineStr">
+        <is>
+          <t>2-3 hrs</t>
+        </is>
+      </c>
+      <c r="I79" s="5" t="inlineStr">
+        <is>
+          <t>Win: safer registry edits + audit trail.</t>
+        </is>
+      </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K79" s="12" t="inlineStr">
@@ -5937,22 +5921,22 @@
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="105" customHeight="1">
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5962,29 +5946,37 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr"/>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Win: visibility into RBAC changes.</t>
+        </is>
+      </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K80" s="12" t="inlineStr">
@@ -5994,27 +5986,27 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="135" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -6024,37 +6016,37 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H81" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I81" s="5" t="inlineStr">
         <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K81" s="12" t="inlineStr">
@@ -6064,27 +6056,27 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="120" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="150" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -6094,29 +6086,29 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K82" s="12" t="inlineStr">
@@ -6126,67 +6118,59 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="45" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="105" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C83" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>TRACKER-BUY-FILTER</t>
+        </is>
+      </c>
+      <c r="C83" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K83" s="12" t="inlineStr">
@@ -6196,63 +6180,67 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M83" s="3" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M83" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="45" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="135" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C84" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>MOD-1</t>
+        </is>
+      </c>
+      <c r="C84" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
         </is>
       </c>
       <c r="H84" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I84" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
         </is>
       </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
         </is>
       </c>
       <c r="K84" s="12" t="inlineStr">
@@ -6262,61 +6250,61 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M84" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M84" s="3" t="inlineStr">
+        <is>
+          <t>42c36ef91</t>
+        </is>
+      </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="45" customHeight="1">
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="120" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
-        </is>
-      </c>
-      <c r="C85" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>RECENCY-FLOOR</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J85" s="5" t="inlineStr"/>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr"/>
+      <c r="J85" s="5" t="inlineStr">
+        <is>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
       <c r="K85" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6324,17 +6312,17 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>24fd7c273</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
         </is>
       </c>
     </row>
@@ -6344,59 +6332,63 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C86" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C86" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K86" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L86" s="2" t="inlineStr"/>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K86" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L86" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M86" s="3" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -6406,59 +6398,63 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
-        </is>
-      </c>
-      <c r="C87" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C87" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
-        </is>
-      </c>
-      <c r="K87" s="14" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L87" s="2" t="inlineStr"/>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K87" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L87" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -6468,123 +6464,313 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C88" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C88" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K88" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr"/>
+      <c r="K88" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="89" ht="90" customHeight="1">
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="89" ht="45" customHeight="1">
       <c r="A89" s="2" t="n">
         <v>88</v>
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C89" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C89" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
-        </is>
-      </c>
-      <c r="K89" s="15" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K89" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr"/>
       <c r="M89" s="3" t="inlineStr"/>
       <c r="N89" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="90" ht="45" customHeight="1">
+      <c r="A90" s="2" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" s="3" t="inlineStr">
+        <is>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
+        </is>
+      </c>
+      <c r="D90" s="5" t="inlineStr">
+        <is>
+          <t>Performance</t>
+        </is>
+      </c>
+      <c r="E90" s="6" t="inlineStr">
+        <is>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+        </is>
+      </c>
+      <c r="F90" s="5" t="inlineStr">
+        <is>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+        </is>
+      </c>
+      <c r="G90" s="5" t="inlineStr">
+        <is>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+        </is>
+      </c>
+      <c r="H90" s="2" t="inlineStr">
+        <is>
+          <t>hours-days each</t>
+        </is>
+      </c>
+      <c r="I90" s="5" t="inlineStr">
+        <is>
+          <t>Win varies; defer until PERF-7 measured.</t>
+        </is>
+      </c>
+      <c r="J90" s="5" t="inlineStr">
+        <is>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K90" s="14" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L90" s="2" t="inlineStr"/>
+      <c r="M90" s="3" t="inlineStr"/>
+      <c r="N90" s="8" t="inlineStr">
+        <is>
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="45" customHeight="1">
+      <c r="A91" s="2" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" s="3" t="inlineStr">
+        <is>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C91" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
+        </is>
+      </c>
+      <c r="D91" s="5" t="inlineStr">
+        <is>
+          <t>QUANT-1 Sunday follow-up</t>
+        </is>
+      </c>
+      <c r="E91" s="6" t="inlineStr">
+        <is>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+        </is>
+      </c>
+      <c r="F91" s="5" t="inlineStr">
+        <is>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+        </is>
+      </c>
+      <c r="G91" s="5" t="inlineStr">
+        <is>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+        </is>
+      </c>
+      <c r="H91" s="2" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="I91" s="5" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="J91" s="5" t="inlineStr">
+        <is>
+          <t>Agents skim and miss post-filter subset analysis.</t>
+        </is>
+      </c>
+      <c r="K91" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L91" s="2" t="inlineStr"/>
+      <c r="M91" s="3" t="inlineStr"/>
+      <c r="N91" s="8" t="inlineStr">
+        <is>
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="90" customHeight="1">
+      <c r="A92" s="2" t="n">
+        <v>91</v>
+      </c>
+      <c r="B92" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C92" s="13" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D92" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E92" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F92" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G92" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H92" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I92" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J92" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K92" s="15" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L92" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M92" s="3" t="inlineStr"/>
+      <c r="N92" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -6648,13 +6834,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D2" s="18" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -6743,13 +6929,13 @@
         <v>26</v>
       </c>
       <c r="C7" s="23" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="D7" s="23" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E7" s="23" t="n">
-        <v>88</v>
+        <v>91</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -706,13 +706,13 @@
         </is>
       </c>
     </row>
-    <row r="2" ht="105" customHeight="1">
+    <row r="2" ht="45" customHeight="1">
       <c r="A2" s="2" t="n">
         <v>1</v>
       </c>
       <c r="B2" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>OPS-1</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -722,37 +722,37 @@
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E2" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
         </is>
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
         </is>
       </c>
       <c r="G2" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
         </is>
       </c>
       <c r="H2" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I2" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Win: cleaner repo.</t>
         </is>
       </c>
       <c r="J2" s="5" t="inlineStr">
         <is>
-          <t>Discovered while diagnosing F3/F4 fold mystery. Phantom 0% trades created false 'PF 999' sentinel in WF aggregate, masking that only F1+F2 had real evidence. Verdict framework was applying to apparent 4 folds but only 2 were informative.</t>
+          <t>Calendar reminder for 2026-05-16.</t>
         </is>
       </c>
       <c r="K2" s="7" t="inlineStr">
@@ -764,17 +764,17 @@
       <c r="M2" s="3" t="inlineStr"/>
       <c r="N2" s="8" t="inlineStr">
         <is>
-          <t>Run any backtest with --days 100+ on a low-volatility period. Confirm trades that don't exit show pnl != 0.0 (real MTM). Then verify F3/F4 type windows produce proper attribution data.</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="60" customHeight="1">
       <c r="A3" s="2" t="n">
         <v>2</v>
       </c>
       <c r="B3" s="3" t="inlineStr">
         <is>
-          <t>OPS-1</t>
+          <t>QUANT-5</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -784,37 +784,37 @@
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E3" s="6" t="inlineStr">
         <is>
-          <t>Snapshot cleanup (scripts/cleanup_after_2026_05_16.sh)</t>
+          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
         </is>
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>Pre-Saturday session migration created intermediate snapshot files safe to remove after a week.</t>
+          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
         </is>
       </c>
       <c r="G3" s="5" t="inlineStr">
         <is>
-          <t>Run scripts/cleanup_after_2026_05_16.sh after 2026-05-16 cutoff.</t>
+          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>days</t>
         </is>
       </c>
       <c r="I3" s="5" t="inlineStr">
         <is>
-          <t>Win: cleaner repo.</t>
+          <t>Caveat: exploratory research, not config-tuning.</t>
         </is>
       </c>
       <c r="J3" s="5" t="inlineStr">
         <is>
-          <t>Calendar reminder for 2026-05-16.</t>
+          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
         </is>
       </c>
       <c r="K3" s="7" t="inlineStr">
@@ -830,53 +830,53 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="60" customHeight="1">
+    <row r="4" ht="45" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>QUANT-5</t>
-        </is>
-      </c>
-      <c r="C4" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>CLEAN-4</t>
+        </is>
+      </c>
+      <c r="C4" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Mover predictor v3 — NLP earnings tone + options flow features</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>v1 had leakage. v2 fixed leakage but AUC stuck at 0.546 — pure technical features at entry don't predict mover success.</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Build v3 with NEW feature classes (don't retrain): NLP earnings-call tone embeddings, options-flow IV skew + UOA put/call delta, catalyst-conditional models (subset by tag). A6 logger captures most inputs going forward.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>days</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Caveat: exploratory research, not config-tuning.</t>
+          <t>Win: -X lines.</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Don't retrain v1/v2 — both definitive AUC 0.546 negative.</t>
+          <t>Couples with OPS-1.</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -892,13 +892,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="45" customHeight="1">
+    <row r="5" ht="90" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -908,37 +908,37 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Conviction tier is decorative — wire as filter or delete</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>2-4 hrs + backtest validation</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Medium — changes live size or eliminates a layer</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
+          <t>Discovered while reworking T1 bar today. Today's T1 88-&gt;85 was reverted because lowering doesn't matter when the tier isn't gating anyway.</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -950,17 +950,17 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="90" customHeight="1">
+          <t>python3 -c 'from collections import Counter; import json; sl=json.load(open("data/signal_log.json")); c=Counter((s.get("conviction_label") or "none").upper() for s in sl if s.get("status")=="CLOSED"); print(c)' — expect 'NONE' (or '—') for ~90%+.</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="75" customHeight="1">
       <c r="A6" s="2" t="n">
         <v>5</v>
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -970,37 +970,37 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier is decorative — wire as filter or delete</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs + backtest validation</t>
+          <t>1 day + backtest</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Medium — changes live size or eliminates a layer</t>
+          <t>High win potential, medium risk</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Discovered while reworking T1 bar today. Today's T1 88-&gt;85 was reverted because lowering doesn't matter when the tier isn't gating anyway.</t>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
         </is>
       </c>
       <c r="K6" s="7" t="inlineStr">
@@ -1012,141 +1012,149 @@
       <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from collections import Counter; import json; sl=json.load(open("data/signal_log.json")); c=Counter((s.get("conviction_label") or "none").upper() for s in sl if s.get("status")=="CLOSED"); print(c)' — expect 'NONE' (or '—') for ~90%+.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="135" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
-        </is>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C7" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K7" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
+          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
+        </is>
+      </c>
+      <c r="K7" s="10" t="inlineStr">
+        <is>
+          <t>IN_PROGRESS</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr"/>
       <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="135" customHeight="1">
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C8" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C8" s="11" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I8" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
-        </is>
-      </c>
-      <c r="K8" s="10" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L8" s="2" t="inlineStr"/>
-      <c r="M8" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K8" s="12" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M8" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C9" s="11" t="inlineStr">
@@ -1156,37 +1164,29 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
       <c r="J9" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K9" s="12" t="inlineStr">
@@ -1196,27 +1196,27 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N9" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C10" s="11" t="inlineStr">
@@ -1226,31 +1226,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr"/>
       <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1263,22 +1259,18 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C11" s="11" t="inlineStr">
@@ -1288,27 +1280,39 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr"/>
-      <c r="I11" s="5" t="inlineStr"/>
-      <c r="J11" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I11" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J11" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K11" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1321,18 +1325,22 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N11" s="8" t="inlineStr"/>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N11" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C12" s="11" t="inlineStr">
@@ -1342,37 +1350,37 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K12" s="12" t="inlineStr">
@@ -1387,22 +1395,22 @@
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="105" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C13" s="11" t="inlineStr">
@@ -1412,22 +1420,22 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
@@ -1437,12 +1445,12 @@
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K13" s="12" t="inlineStr">
@@ -1452,27 +1460,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C14" s="11" t="inlineStr">
@@ -1482,37 +1490,37 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I14" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J14" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K14" s="12" t="inlineStr">
@@ -1522,27 +1530,27 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N14" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C15" s="11" t="inlineStr">
@@ -1552,39 +1560,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1597,22 +1593,18 @@
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="120" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C16" s="11" t="inlineStr">
@@ -1622,27 +1614,39 @@
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr"/>
-      <c r="I16" s="5" t="inlineStr"/>
-      <c r="J16" s="5" t="inlineStr"/>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I16" s="5" t="inlineStr">
+        <is>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+        </is>
+      </c>
+      <c r="J16" s="5" t="inlineStr">
+        <is>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
       <c r="K16" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1650,23 +1654,27 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M16" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N16" s="8" t="inlineStr"/>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N16" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C17" s="11" t="inlineStr">
@@ -1681,32 +1689,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K17" s="12" t="inlineStr">
@@ -1726,7 +1734,7 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1736,7 +1744,7 @@
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C18" s="11" t="inlineStr">
@@ -1751,17 +1759,17 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
@@ -1771,12 +1779,12 @@
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K18" s="12" t="inlineStr">
@@ -1796,17 +1804,17 @@
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C19" s="11" t="inlineStr">
@@ -1821,32 +1829,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K19" s="12" t="inlineStr">
@@ -1856,27 +1864,27 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="180" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C20" s="11" t="inlineStr">
@@ -1891,32 +1899,32 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K20" s="12" t="inlineStr">
@@ -1931,22 +1939,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C21" s="11" t="inlineStr">
@@ -1961,32 +1969,32 @@
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K21" s="12" t="inlineStr">
@@ -2001,22 +2009,22 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C22" s="11" t="inlineStr">
@@ -2026,37 +2034,37 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K22" s="12" t="inlineStr">
@@ -2066,27 +2074,27 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C23" s="11" t="inlineStr">
@@ -2096,22 +2104,22 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
@@ -2121,12 +2129,12 @@
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K23" s="12" t="inlineStr">
@@ -2141,12 +2149,12 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -2156,7 +2164,7 @@
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C24" s="11" t="inlineStr">
@@ -2171,32 +2179,32 @@
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K24" s="12" t="inlineStr">
@@ -2211,22 +2219,22 @@
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="105" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C25" s="11" t="inlineStr">
@@ -2236,37 +2244,29 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K25" s="12" t="inlineStr">
@@ -2276,27 +2276,27 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C26" s="11" t="inlineStr">
@@ -2306,29 +2306,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K26" s="12" t="inlineStr">
@@ -2338,27 +2346,27 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C27" s="11" t="inlineStr">
@@ -2368,37 +2376,37 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I27" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J27" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K27" s="12" t="inlineStr">
@@ -2408,27 +2416,27 @@
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N27" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="75" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C28" s="11" t="inlineStr">
@@ -2438,39 +2446,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2483,22 +2479,18 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C29" s="11" t="inlineStr">
@@ -2508,27 +2500,39 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr"/>
-      <c r="I29" s="5" t="inlineStr"/>
-      <c r="J29" s="5" t="inlineStr"/>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I29" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J29" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
       <c r="K29" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2541,18 +2545,22 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N29" s="8" t="inlineStr"/>
-    </row>
-    <row r="30" ht="45" customHeight="1">
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N29" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C30" s="11" t="inlineStr">
@@ -2562,37 +2570,37 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K30" s="12" t="inlineStr">
@@ -2602,17 +2610,17 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2622,7 +2630,7 @@
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C31" s="11" t="inlineStr">
@@ -2637,17 +2645,17 @@
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
@@ -2657,12 +2665,12 @@
       </c>
       <c r="I31" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J31" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K31" s="12" t="inlineStr">
@@ -2677,22 +2685,22 @@
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N31" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="60" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="75" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>TARGET-CAP-10WK</t>
         </is>
       </c>
       <c r="C32" s="11" t="inlineStr">
@@ -2702,39 +2710,27 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2742,57 +2738,65 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="75" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
-        </is>
-      </c>
-      <c r="C33" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C33" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr"/>
-      <c r="I33" s="5" t="inlineStr"/>
-      <c r="J33" s="5" t="inlineStr"/>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>shipped (diagnosis); pending (fix)</t>
+        </is>
+      </c>
+      <c r="I33" s="5" t="inlineStr">
+        <is>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+        </is>
+      </c>
+      <c r="J33" s="5" t="inlineStr">
+        <is>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
+        </is>
+      </c>
       <c r="K33" s="12" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2800,23 +2804,27 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N33" s="8" t="inlineStr"/>
-    </row>
-    <row r="34" ht="60" customHeight="1">
+          <t>9bc015562</t>
+        </is>
+      </c>
+      <c r="N33" s="8" t="inlineStr">
+        <is>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="105" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2826,37 +2834,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K34" s="12" t="inlineStr">
@@ -2866,17 +2874,17 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
         </is>
       </c>
     </row>
@@ -6834,13 +6842,13 @@
         <v>0</v>
       </c>
       <c r="C2" s="18" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D2" s="18" t="n">
         <v>3</v>
       </c>
       <c r="E2" s="18" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -6872,13 +6880,13 @@
         <v>25</v>
       </c>
       <c r="C4" s="18" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="D4" s="18" t="n">
         <v>14</v>
       </c>
       <c r="E4" s="18" t="n">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="5">

--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -19,7 +19,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="18">
+  <fonts count="16">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -54,11 +54,6 @@
     </font>
     <font>
       <b val="1"/>
-      <color rgb="009C5700"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <b val="1"/>
       <color rgb="00006100"/>
       <sz val="10"/>
     </font>
@@ -74,10 +69,6 @@
     <font>
       <b val="1"/>
       <color rgb="00000000"/>
-    </font>
-    <font>
-      <b val="1"/>
-      <color rgb="009C5700"/>
     </font>
     <font>
       <b val="1"/>
@@ -100,7 +91,7 @@
       <sz val="12"/>
     </font>
   </fonts>
-  <fills count="11">
+  <fills count="10">
     <fill>
       <patternFill/>
     </fill>
@@ -125,11 +116,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00D9EAD3"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00FFE9B5"/>
       </patternFill>
     </fill>
     <fill>
@@ -179,7 +165,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="28">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -208,40 +194,36 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="8" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="9" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="10" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="6" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="8" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1016,180 +998,176 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="135" customHeight="1">
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C7" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C7" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>Test scaffold shipped 2026-05-10 (tests/04-pixel-diff.spec.js). 6 surfaces × viewports: dashboard@1440/810/390 + elite-detail Overview@1440/390 + Plan@1440. Stabilize helper disables animations and hides volatile timestamps. Baseline snapshots NOT YET GENERATED — user must run --update-snapshots once against a known-good state, then commit the PNGs. Scaffold shipped 5df6b9ef8 (Playwright config + smoke spec). Full pixel-diff baseline (capture all 30 tab screenshots, store in tests/baseline/, regression check on each PR) still pending — needs CI integration.</t>
-        </is>
-      </c>
-      <c r="K7" s="10" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr"/>
-      <c r="M7" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K7" s="11" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M7" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C8" s="11" t="inlineStr">
+          <t>B3-WEEKLY-FIX</t>
+        </is>
+      </c>
+      <c r="C8" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I8" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="5" t="inlineStr"/>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K8" s="12" t="inlineStr">
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+        </is>
+      </c>
+      <c r="K8" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
-        </is>
-      </c>
-      <c r="C9" s="11" t="inlineStr">
+          <t>VARIANT-F-BT</t>
+        </is>
+      </c>
+      <c r="C9" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
-      <c r="K9" s="12" t="inlineStr">
+      <c r="J9" s="5" t="inlineStr"/>
+      <c r="K9" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1201,53 +1179,61 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
-        </is>
-      </c>
-      <c r="C10" s="11" t="inlineStr">
+          <t>P0-WEEKLY</t>
+        </is>
+      </c>
+      <c r="C10" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr"/>
-      <c r="I10" s="5" t="inlineStr"/>
-      <c r="J10" s="5" t="inlineStr"/>
-      <c r="K10" s="12" t="inlineStr">
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I10" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J10" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
+      <c r="K10" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1259,61 +1245,65 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr"/>
-    </row>
-    <row r="11" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
-        </is>
-      </c>
-      <c r="C11" s="11" t="inlineStr">
+          <t>OPERATING-MINDSET</t>
+        </is>
+      </c>
+      <c r="C11" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
-      <c r="K11" s="12" t="inlineStr">
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+        </is>
+      </c>
+      <c r="K11" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1325,47 +1315,47 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
-        </is>
-      </c>
-      <c r="C12" s="11" t="inlineStr">
+          <t>A6</t>
+        </is>
+      </c>
+      <c r="C12" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1375,155 +1365,143 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
-        </is>
-      </c>
-      <c r="K12" s="12" t="inlineStr">
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+        </is>
+      </c>
+      <c r="K12" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
-        </is>
-      </c>
-      <c r="C13" s="11" t="inlineStr">
+          <t>IPAD-3</t>
+        </is>
+      </c>
+      <c r="C13" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
-        </is>
-      </c>
-      <c r="K13" s="12" t="inlineStr">
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+        </is>
+      </c>
+      <c r="K13" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
-        </is>
-      </c>
-      <c r="C14" s="11" t="inlineStr">
+          <t>ALPACA-SYNC</t>
+        </is>
+      </c>
+      <c r="C14" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
-      <c r="K14" s="12" t="inlineStr">
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
+      <c r="K14" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1535,79 +1513,91 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="120" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
-        </is>
-      </c>
-      <c r="C15" s="11" t="inlineStr">
+          <t>Q1-step1</t>
+        </is>
+      </c>
+      <c r="C15" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr"/>
-      <c r="I15" s="5" t="inlineStr"/>
-      <c r="J15" s="5" t="inlineStr"/>
-      <c r="K15" s="12" t="inlineStr">
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I15" s="5" t="inlineStr">
+        <is>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+        </is>
+      </c>
+      <c r="J15" s="5" t="inlineStr">
+        <is>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
+      <c r="K15" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr"/>
-    </row>
-    <row r="16" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="45" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
-        </is>
-      </c>
-      <c r="C16" s="11" t="inlineStr">
+          <t>Q1-step2</t>
+        </is>
+      </c>
+      <c r="C16" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1619,35 +1609,35 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
-        </is>
-      </c>
-      <c r="K16" s="12" t="inlineStr">
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+        </is>
+      </c>
+      <c r="K16" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1664,7 +1654,7 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1674,10 +1664,10 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
-        </is>
-      </c>
-      <c r="C17" s="11" t="inlineStr">
+          <t>Q1-step3</t>
+        </is>
+      </c>
+      <c r="C17" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1689,17 +1679,17 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1709,15 +1699,15 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
-        </is>
-      </c>
-      <c r="K17" s="12" t="inlineStr">
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+        </is>
+      </c>
+      <c r="K17" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1734,20 +1724,20 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
-        </is>
-      </c>
-      <c r="C18" s="11" t="inlineStr">
+          <t>Q1-step4</t>
+        </is>
+      </c>
+      <c r="C18" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1759,65 +1749,65 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
-        </is>
-      </c>
-      <c r="K18" s="12" t="inlineStr">
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+        </is>
+      </c>
+      <c r="K18" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="180" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
-        </is>
-      </c>
-      <c r="C19" s="11" t="inlineStr">
+          <t>Q1-step5</t>
+        </is>
+      </c>
+      <c r="C19" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1829,35 +1819,35 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
-        </is>
-      </c>
-      <c r="K19" s="12" t="inlineStr">
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="K19" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1869,25 +1859,25 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
-        </is>
-      </c>
-      <c r="C20" s="11" t="inlineStr">
+          <t>Q1-step6</t>
+        </is>
+      </c>
+      <c r="C20" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -1899,35 +1889,35 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="K20" s="12" t="inlineStr">
+          <t>Skip if step 5 already shows PF healthy.</t>
+        </is>
+      </c>
+      <c r="K20" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -1939,117 +1929,117 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
-        </is>
-      </c>
-      <c r="C21" s="11" t="inlineStr">
+          <t>B2</t>
+        </is>
+      </c>
+      <c r="C21" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
-        </is>
-      </c>
-      <c r="K21" s="12" t="inlineStr">
+          <t>Pure additive. Does not affect existing analysis.</t>
+        </is>
+      </c>
+      <c r="K21" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="45" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
-        </is>
-      </c>
-      <c r="C22" s="11" t="inlineStr">
+          <t>Q1-Fix1</t>
+        </is>
+      </c>
+      <c r="C22" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2059,15 +2049,15 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
-        </is>
-      </c>
-      <c r="K22" s="12" t="inlineStr">
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+        </is>
+      </c>
+      <c r="K22" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2079,12 +2069,12 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -2094,10 +2084,10 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
-        </is>
-      </c>
-      <c r="C23" s="11" t="inlineStr">
+          <t>Q1-Fix3</t>
+        </is>
+      </c>
+      <c r="C23" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -2109,35 +2099,35 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
-        </is>
-      </c>
-      <c r="K23" s="12" t="inlineStr">
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+        </is>
+      </c>
+      <c r="K23" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2149,267 +2139,255 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="105" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
-        </is>
-      </c>
-      <c r="C24" s="11" t="inlineStr">
+          <t>VAR-F</t>
+        </is>
+      </c>
+      <c r="C24" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
-        </is>
-      </c>
-      <c r="K24" s="12" t="inlineStr">
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+        </is>
+      </c>
+      <c r="K24" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
-        </is>
-      </c>
-      <c r="C25" s="11" t="inlineStr">
+          <t>K3</t>
+        </is>
+      </c>
+      <c r="C25" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr"/>
-      <c r="I25" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I25" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
-        </is>
-      </c>
-      <c r="K25" s="12" t="inlineStr">
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+        </is>
+      </c>
+      <c r="K25" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
-        </is>
-      </c>
-      <c r="C26" s="11" t="inlineStr">
+          <t>GATE-1</t>
+        </is>
+      </c>
+      <c r="C26" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
-        </is>
-      </c>
-      <c r="K26" s="12" t="inlineStr">
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+        </is>
+      </c>
+      <c r="K26" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="75" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
-        </is>
-      </c>
-      <c r="C27" s="11" t="inlineStr">
+          <t>KILL-MULT0</t>
+        </is>
+      </c>
+      <c r="C27" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
-        </is>
-      </c>
-      <c r="K27" s="12" t="inlineStr">
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
+      <c r="K27" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2421,53 +2399,61 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
-        </is>
-      </c>
-      <c r="C28" s="11" t="inlineStr">
+          <t>VARIANT-F</t>
+        </is>
+      </c>
+      <c r="C28" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr"/>
-      <c r="I28" s="5" t="inlineStr"/>
-      <c r="J28" s="5" t="inlineStr"/>
-      <c r="K28" s="12" t="inlineStr">
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I28" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J28" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
+      <c r="K28" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2479,78 +2465,82 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr"/>
-    </row>
-    <row r="29" ht="45" customHeight="1">
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="60" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
-        </is>
-      </c>
-      <c r="C29" s="11" t="inlineStr">
+          <t>A2</t>
+        </is>
+      </c>
+      <c r="C29" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
-        </is>
-      </c>
-      <c r="K29" s="12" t="inlineStr">
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+        </is>
+      </c>
+      <c r="K29" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2560,10 +2550,10 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
-        </is>
-      </c>
-      <c r="C30" s="11" t="inlineStr">
+          <t>A3</t>
+        </is>
+      </c>
+      <c r="C30" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
@@ -2575,17 +2565,17 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2595,15 +2585,15 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
-        </is>
-      </c>
-      <c r="K30" s="12" t="inlineStr">
+          <t>Existing positions unaffected (exits run via separate paths).</t>
+        </is>
+      </c>
+      <c r="K30" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2615,146 +2605,146 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
-        </is>
-      </c>
-      <c r="C31" s="11" t="inlineStr">
+          <t>TARGET-CAP-10WK</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
-      <c r="K31" s="12" t="inlineStr">
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
+      <c r="K31" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="75" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
-        </is>
-      </c>
-      <c r="C32" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr"/>
-      <c r="I32" s="5" t="inlineStr"/>
-      <c r="J32" s="5" t="inlineStr"/>
-      <c r="K32" s="12" t="inlineStr">
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>shipped (diagnosis); pending (fix)</t>
+        </is>
+      </c>
+      <c r="I32" s="5" t="inlineStr">
+        <is>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+        </is>
+      </c>
+      <c r="J32" s="5" t="inlineStr">
+        <is>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
+        </is>
+      </c>
+      <c r="K32" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr"/>
-    </row>
-    <row r="33" ht="60" customHeight="1">
+          <t>9bc015562</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr">
+        <is>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="105" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2764,67 +2754,67 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
-        </is>
-      </c>
-      <c r="K33" s="12" t="inlineStr">
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+        </is>
+      </c>
+      <c r="K33" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="105" customHeight="1">
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="45" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2834,47 +2824,47 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
-        </is>
-      </c>
-      <c r="K34" s="12" t="inlineStr">
+          <t>Shipped 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="K34" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2884,7 +2874,7 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2894,7 +2884,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2909,22 +2899,22 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2934,10 +2924,10 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
-        </is>
-      </c>
-      <c r="K35" s="12" t="inlineStr">
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+        </is>
+      </c>
+      <c r="K35" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -2954,7 +2944,7 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2954,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2979,35 +2969,35 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
-        </is>
-      </c>
-      <c r="K36" s="12" t="inlineStr">
+          <t>Shipped 2026-05-10.</t>
+        </is>
+      </c>
+      <c r="K36" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3024,17 +3014,17 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="60" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3049,35 +3039,35 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
-        </is>
-      </c>
-      <c r="K37" s="12" t="inlineStr">
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+        </is>
+      </c>
+      <c r="K37" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3094,7 +3084,7 @@
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -3104,7 +3094,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3114,40 +3104,40 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
-        </is>
-      </c>
-      <c r="K38" s="12" t="inlineStr">
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+        </is>
+      </c>
+      <c r="K38" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3159,22 +3149,22 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="90" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3189,35 +3179,35 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
-        </is>
-      </c>
-      <c r="K39" s="12" t="inlineStr">
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+        </is>
+      </c>
+      <c r="K39" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3234,17 +3224,17 @@
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3254,67 +3244,67 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
-        </is>
-      </c>
-      <c r="K40" s="12" t="inlineStr">
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+        </is>
+      </c>
+      <c r="K40" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3324,22 +3314,22 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3349,15 +3339,15 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
-        </is>
-      </c>
-      <c r="K41" s="12" t="inlineStr">
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+        </is>
+      </c>
+      <c r="K41" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3369,22 +3359,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="90" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3394,67 +3384,63 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
-        </is>
-      </c>
-      <c r="K42" s="12" t="inlineStr">
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+        </is>
+      </c>
+      <c r="K42" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3469,31 +3455,31 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
-        </is>
-      </c>
-      <c r="K43" s="12" t="inlineStr">
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+        </is>
+      </c>
+      <c r="K43" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3510,17 +3496,17 @@
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="135" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3530,36 +3516,40 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr"/>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / High win</t>
+        </is>
+      </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
-        </is>
-      </c>
-      <c r="K44" s="12" t="inlineStr">
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+        </is>
+      </c>
+      <c r="K44" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3571,22 +3561,22 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="135" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="45" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3596,57 +3586,57 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
-        </is>
-      </c>
-      <c r="K45" s="12" t="inlineStr">
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+        </is>
+      </c>
+      <c r="K45" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -3656,7 +3646,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3671,35 +3661,35 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
-        </is>
-      </c>
-      <c r="K46" s="12" t="inlineStr">
+          <t>Trivial fix; verify no race with first user interaction.</t>
+        </is>
+      </c>
+      <c r="K46" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3711,22 +3701,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="120" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3741,62 +3731,62 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
-        </is>
-      </c>
-      <c r="K47" s="12" t="inlineStr">
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+        </is>
+      </c>
+      <c r="K47" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="135" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3811,35 +3801,35 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
-        </is>
-      </c>
-      <c r="K48" s="12" t="inlineStr">
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+        </is>
+      </c>
+      <c r="K48" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3851,22 +3841,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3876,40 +3866,32 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
-        </is>
-      </c>
-      <c r="K49" s="12" t="inlineStr">
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+        </is>
+      </c>
+      <c r="K49" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3921,22 +3903,22 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="75" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="105" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3946,32 +3928,40 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr"/>
-      <c r="I50" s="5" t="inlineStr"/>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="I50" s="5" t="inlineStr">
+        <is>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
-        </is>
-      </c>
-      <c r="K50" s="12" t="inlineStr">
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+        </is>
+      </c>
+      <c r="K50" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -3983,22 +3973,22 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4013,35 +4003,35 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
-        </is>
-      </c>
-      <c r="K51" s="12" t="inlineStr">
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+        </is>
+      </c>
+      <c r="K51" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4053,22 +4043,22 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="105" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4083,35 +4073,35 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
-        </is>
-      </c>
-      <c r="K52" s="12" t="inlineStr">
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+        </is>
+      </c>
+      <c r="K52" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4123,22 +4113,22 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="105" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4148,67 +4138,67 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
-        </is>
-      </c>
-      <c r="K53" s="12" t="inlineStr">
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+        </is>
+      </c>
+      <c r="K53" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="120" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4218,47 +4208,47 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
-        </is>
-      </c>
-      <c r="K54" s="12" t="inlineStr">
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+        </is>
+      </c>
+      <c r="K54" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4268,17 +4258,17 @@
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="120" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4288,67 +4278,67 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
-        </is>
-      </c>
-      <c r="K55" s="12" t="inlineStr">
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+        </is>
+      </c>
+      <c r="K55" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4363,17 +4353,17 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4383,15 +4373,15 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
-        </is>
-      </c>
-      <c r="K56" s="12" t="inlineStr">
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+        </is>
+      </c>
+      <c r="K56" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4408,17 +4398,17 @@
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4428,22 +4418,22 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4453,15 +4443,15 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
-        </is>
-      </c>
-      <c r="K57" s="12" t="inlineStr">
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+        </is>
+      </c>
+      <c r="K57" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4473,22 +4463,22 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="90" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4498,57 +4488,57 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
-        </is>
-      </c>
-      <c r="K58" s="12" t="inlineStr">
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+        </is>
+      </c>
+      <c r="K58" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -4558,7 +4548,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4568,40 +4558,28 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr">
-        <is>
-          <t>shipped (additive only)</t>
-        </is>
-      </c>
-      <c r="I59" s="5" t="inlineStr">
-        <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
-        </is>
-      </c>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
-        </is>
-      </c>
-      <c r="K59" s="12" t="inlineStr">
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr"/>
+      <c r="K59" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4613,22 +4591,18 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="90" customHeight="1">
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N59" s="8" t="inlineStr"/>
+    </row>
+    <row r="60" ht="105" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4638,28 +4612,32 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr"/>
-      <c r="K60" s="12" t="inlineStr">
+      <c r="J60" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
+      <c r="K60" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4671,18 +4649,22 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="inlineStr"/>
-    </row>
-    <row r="61" ht="105" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N60" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4692,32 +4674,40 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="5" t="inlineStr"/>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I61" s="5" t="inlineStr">
+        <is>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
-        </is>
-      </c>
-      <c r="K61" s="12" t="inlineStr">
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+        </is>
+      </c>
+      <c r="K61" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4729,22 +4719,22 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="45" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="90" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4754,40 +4744,40 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
+          <t>Low / High (transparency + future-proof)</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
-        </is>
-      </c>
-      <c r="K62" s="12" t="inlineStr">
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
+      <c r="K62" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4799,22 +4789,22 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="90" customHeight="1">
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="75" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4824,40 +4814,28 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>Low / High (transparency + future-proof)</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
-        </is>
-      </c>
-      <c r="K63" s="12" t="inlineStr">
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr"/>
+      <c r="K63" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4869,22 +4847,18 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N63" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="75" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N63" s="8" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4894,51 +4868,67 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr"/>
-      <c r="I64" s="5" t="inlineStr"/>
-      <c r="J64" s="5" t="inlineStr"/>
-      <c r="K64" s="12" t="inlineStr">
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I64" s="5" t="inlineStr">
+        <is>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J64" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
+      <c r="K64" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N64" s="8" t="inlineStr"/>
-    </row>
-    <row r="65" ht="60" customHeight="1">
+          <t>16a26b201</t>
+        </is>
+      </c>
+      <c r="N64" s="8" t="inlineStr">
+        <is>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4948,40 +4938,40 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
-      <c r="K65" s="12" t="inlineStr">
+          <t>Trivial.</t>
+        </is>
+      </c>
+      <c r="K65" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -4993,22 +4983,22 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="105" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5023,52 +5013,44 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I66" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr"/>
+      <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
-        </is>
-      </c>
-      <c r="K66" s="12" t="inlineStr">
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+        </is>
+      </c>
+      <c r="K66" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
         </is>
       </c>
     </row>
@@ -5078,7 +5060,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5093,27 +5075,27 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
-        </is>
-      </c>
-      <c r="K67" s="12" t="inlineStr">
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+        </is>
+      </c>
+      <c r="K67" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -5125,22 +5107,22 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="105" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="45" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5150,32 +5132,40 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr"/>
-      <c r="I68" s="5" t="inlineStr"/>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I68" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
-        </is>
-      </c>
-      <c r="K68" s="12" t="inlineStr">
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
+      <c r="K68" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -5187,12 +5177,12 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
         </is>
       </c>
     </row>
@@ -5202,7 +5192,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5212,40 +5202,36 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>All reads use ?? fallbacks.</t>
-        </is>
-      </c>
-      <c r="K69" s="12" t="inlineStr">
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
+      <c r="K69" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -5257,22 +5243,22 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="45" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="105" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -5282,36 +5268,40 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr"/>
-      <c r="K70" s="12" t="inlineStr">
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
+      <c r="K70" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -5323,92 +5313,88 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="105" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
-        </is>
-      </c>
-      <c r="C71" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="C71" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
-      <c r="K71" s="12" t="inlineStr">
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr"/>
+      <c r="K71" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="75" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5423,17 +5409,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5443,11 +5429,15 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr"/>
-      <c r="K72" s="12" t="inlineStr">
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
+      <c r="K72" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -5459,12 +5449,12 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
         </is>
       </c>
     </row>
@@ -5474,7 +5464,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5489,62 +5479,46 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J73" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
-      <c r="K73" s="12" t="inlineStr">
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr"/>
+      <c r="J73" s="5" t="inlineStr"/>
+      <c r="K73" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N73" s="8" t="inlineStr">
-        <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="74" ht="75" customHeight="1">
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N73" s="8" t="inlineStr"/>
+    </row>
+    <row r="74" ht="45" customHeight="1">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -5554,43 +5528,55 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr"/>
-      <c r="I74" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I74" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J74" s="5" t="inlineStr"/>
-      <c r="K74" s="12" t="inlineStr">
+      <c r="K74" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N74" s="8" t="inlineStr"/>
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N74" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
     </row>
     <row r="75" ht="45" customHeight="1">
       <c r="A75" s="2" t="n">
@@ -5598,7 +5584,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5608,63 +5594,67 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr"/>
-      <c r="K75" s="12" t="inlineStr">
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
+      <c r="K75" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="45" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="75" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5674,67 +5664,67 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
-      <c r="K76" s="12" t="inlineStr">
+          <t>User can still bypass with --no-verify in emergencies.</t>
+        </is>
+      </c>
+      <c r="K76" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="75" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="60" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5744,57 +5734,57 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
-        </is>
-      </c>
-      <c r="K77" s="12" t="inlineStr">
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+        </is>
+      </c>
+      <c r="K77" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -5804,7 +5794,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5819,35 +5809,35 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
-        </is>
-      </c>
-      <c r="K78" s="12" t="inlineStr">
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+        </is>
+      </c>
+      <c r="K78" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -5864,7 +5854,7 @@
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -5874,7 +5864,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5889,35 +5879,35 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
-        </is>
-      </c>
-      <c r="K79" s="12" t="inlineStr">
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+        </is>
+      </c>
+      <c r="K79" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -5934,7 +5924,7 @@
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
         </is>
       </c>
     </row>
@@ -5944,7 +5934,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5959,62 +5949,62 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
-        </is>
-      </c>
-      <c r="K80" s="12" t="inlineStr">
+          <t>Trivial CLI wrapper.</t>
+        </is>
+      </c>
+      <c r="K80" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="60" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="150" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -6024,67 +6014,59 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Win: fast iteration on report templates.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
-        </is>
-      </c>
-      <c r="K81" s="12" t="inlineStr">
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+        </is>
+      </c>
+      <c r="K81" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="150" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="105" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -6094,59 +6076,59 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
         </is>
       </c>
       <c r="H82" s="2" t="inlineStr"/>
       <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
-        </is>
-      </c>
-      <c r="K82" s="12" t="inlineStr">
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+        </is>
+      </c>
+      <c r="K82" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="105" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="135" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -6156,59 +6138,67 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
-        </is>
-      </c>
-      <c r="K83" s="12" t="inlineStr">
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+        </is>
+      </c>
+      <c r="K83" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>42c36ef91</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="135" customHeight="1">
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="120" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>RECENCY-FLOOR</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -6218,119 +6208,115 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
-        </is>
-      </c>
-      <c r="K84" s="12" t="inlineStr">
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+        </is>
+      </c>
+      <c r="K84" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="120" customHeight="1">
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="45" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
-        </is>
-      </c>
-      <c r="C85" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>B4</t>
+        </is>
+      </c>
+      <c r="C85" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>verified</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Win: persistence works; no silent overwrites.</t>
+        </is>
+      </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
-        </is>
-      </c>
-      <c r="K85" s="12" t="inlineStr">
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
+        </is>
+      </c>
+      <c r="K85" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="inlineStr">
-        <is>
-          <t>pending</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr"/>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -6340,10 +6326,10 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C86" s="13" t="inlineStr">
+          <t>I4</t>
+        </is>
+      </c>
+      <c r="C86" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6355,35 +6341,35 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>verified</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Win: persistence works; no silent overwrites.</t>
+          <t>Win: confirms infrastructure still healthy.</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
-        </is>
-      </c>
-      <c r="K86" s="12" t="inlineStr">
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
+      <c r="K86" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
@@ -6396,7 +6382,7 @@
       <c r="M86" s="3" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -6406,63 +6392,63 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
-        </is>
-      </c>
-      <c r="C87" s="13" t="inlineStr">
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C87" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr">
-        <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
-        </is>
-      </c>
-      <c r="K87" s="12" t="inlineStr">
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr"/>
+      <c r="K87" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
         </is>
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="inlineStr"/>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N87" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -6472,63 +6458,59 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
-        </is>
-      </c>
-      <c r="C88" s="13" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>CLEAN-2</t>
+        </is>
+      </c>
+      <c r="C88" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr"/>
-      <c r="K88" s="12" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>Win: -671 lines.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>Standard data-migration retention practice.</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr"/>
+      <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>n/a — deferred</t>
         </is>
       </c>
     </row>
@@ -6538,7 +6520,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
+          <t>PERF-8-13</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -6548,40 +6530,40 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K89" s="14" t="inlineStr">
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K89" s="13" t="inlineStr">
         <is>
           <t>DEFERRED</t>
         </is>
@@ -6600,121 +6582,125 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
-        </is>
-      </c>
-      <c r="C90" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C90" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K90" s="14" t="inlineStr">
         <is>
-          <t>DEFERRED</t>
+          <t>REJECTED</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="3" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="45" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="75" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C91" s="11" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C91" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K91" s="15" t="inlineStr">
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+        </is>
+      </c>
+      <c r="K91" s="14" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr"/>
+      <c r="L91" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-11</t>
+        </is>
+      </c>
       <c r="M91" s="3" t="inlineStr"/>
       <c r="N91" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
         </is>
       </c>
     </row>
@@ -6727,7 +6713,7 @@
           <t>H1</t>
         </is>
       </c>
-      <c r="C92" s="13" t="inlineStr">
+      <c r="C92" s="12" t="inlineStr">
         <is>
           <t>P3</t>
         </is>
@@ -6767,7 +6753,7 @@
           <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
         </is>
       </c>
-      <c r="K92" s="15" t="inlineStr">
+      <c r="K92" s="14" t="inlineStr">
         <is>
           <t>REJECTED</t>
         </is>
@@ -6795,7 +6781,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E7"/>
+  <dimension ref="A1:E6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -6806,143 +6792,124 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="16" t="inlineStr">
+      <c r="A1" s="15" t="inlineStr">
         <is>
           <t>Status</t>
         </is>
       </c>
-      <c r="B1" s="16" t="inlineStr">
+      <c r="B1" s="15" t="inlineStr">
         <is>
           <t>P0</t>
         </is>
       </c>
-      <c r="C1" s="16" t="inlineStr">
+      <c r="C1" s="15" t="inlineStr">
         <is>
           <t>P1</t>
         </is>
       </c>
-      <c r="D1" s="16" t="inlineStr">
+      <c r="D1" s="15" t="inlineStr">
         <is>
           <t>P2</t>
         </is>
       </c>
-      <c r="E1" s="16" t="inlineStr">
+      <c r="E1" s="15" t="inlineStr">
         <is>
           <t>Total</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="16" t="inlineStr">
         <is>
           <t>OPEN</t>
         </is>
       </c>
-      <c r="B2" s="18" t="n">
+      <c r="B2" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C2" s="18" t="n">
+      <c r="C2" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="D2" s="18" t="n">
+      <c r="D2" s="17" t="n">
         <v>3</v>
       </c>
-      <c r="E2" s="18" t="n">
+      <c r="E2" s="17" t="n">
         <v>5</v>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="19" t="inlineStr">
-        <is>
-          <t>IN_PROGRESS</t>
-        </is>
-      </c>
-      <c r="B3" s="18" t="n">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="B3" s="17" t="n">
+        <v>25</v>
+      </c>
+      <c r="C3" s="17" t="n">
+        <v>39</v>
+      </c>
+      <c r="D3" s="17" t="n">
+        <v>14</v>
+      </c>
+      <c r="E3" s="17" t="n">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="19" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="C3" s="18" t="n">
+      <c r="C4" s="17" t="n">
+        <v>0</v>
+      </c>
+      <c r="D4" s="17" t="n">
+        <v>2</v>
+      </c>
+      <c r="E4" s="17" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="20" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="B5" s="17" t="n">
         <v>1</v>
       </c>
-      <c r="D3" s="18" t="n">
+      <c r="C5" s="17" t="n">
+        <v>1</v>
+      </c>
+      <c r="D5" s="17" t="n">
         <v>0</v>
       </c>
-      <c r="E3" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="20" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="B4" s="18" t="n">
-        <v>25</v>
-      </c>
-      <c r="C4" s="18" t="n">
-        <v>39</v>
-      </c>
-      <c r="D4" s="18" t="n">
-        <v>14</v>
-      </c>
-      <c r="E4" s="18" t="n">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="21" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="B5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="18" t="n">
+      <c r="E5" s="17" t="n">
         <v>2</v>
       </c>
-      <c r="E5" s="18" t="n">
-        <v>2</v>
-      </c>
     </row>
     <row r="6">
-      <c r="A6" s="22" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
-        </is>
-      </c>
-      <c r="B6" s="18" t="n">
-        <v>1</v>
-      </c>
-      <c r="C6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="18" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="18" t="n">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="23" t="inlineStr">
+      <c r="A6" s="21" t="inlineStr">
         <is>
           <t>TOTAL</t>
         </is>
       </c>
-      <c r="B7" s="23" t="n">
+      <c r="B6" s="21" t="n">
         <v>26</v>
       </c>
-      <c r="C7" s="23" t="n">
+      <c r="C6" s="21" t="n">
         <v>42</v>
       </c>
-      <c r="D7" s="23" t="n">
+      <c r="D6" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="E7" s="23" t="n">
+      <c r="E6" s="21" t="n">
         <v>91</v>
       </c>
     </row>
@@ -6966,153 +6933,153 @@
   </cols>
   <sheetData>
     <row r="1">
-      <c r="A1" s="24" t="inlineStr">
+      <c r="A1" s="22" t="inlineStr">
         <is>
           <t>Step</t>
         </is>
       </c>
-      <c r="B1" s="24" t="inlineStr">
+      <c r="B1" s="22" t="inlineStr">
         <is>
           <t>Command</t>
         </is>
       </c>
-      <c r="C1" s="24" t="inlineStr">
+      <c r="C1" s="22" t="inlineStr">
         <is>
           <t>What it does</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="25" t="inlineStr">
+      <c r="A2" s="23" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B2" s="26" t="inlineStr">
+      <c r="B2" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list</t>
         </is>
       </c>
-      <c r="C2" s="27" t="inlineStr">
+      <c r="C2" s="25" t="inlineStr">
         <is>
           <t>Show all items grouped by status</t>
         </is>
       </c>
     </row>
     <row r="3">
-      <c r="A3" s="25" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B3" s="26" t="inlineStr">
+      <c r="B3" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py list --open</t>
         </is>
       </c>
-      <c r="C3" s="27" t="inlineStr">
+      <c r="C3" s="25" t="inlineStr">
         <is>
           <t>Show only OPEN / IN_PROGRESS</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="25" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B4" s="26" t="inlineStr">
+      <c r="B4" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt;</t>
         </is>
       </c>
-      <c r="C4" s="27" t="inlineStr">
+      <c r="C4" s="25" t="inlineStr">
         <is>
           <t>Mark item DONE (auto-fills today's date + HEAD commit)</t>
         </is>
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="25" t="inlineStr">
+      <c r="A5" s="23" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B5" s="26" t="inlineStr">
+      <c r="B5" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py done &lt;id&gt; --commit abc123 --date 2026-05-09</t>
         </is>
       </c>
-      <c r="C5" s="27" t="inlineStr">
+      <c r="C5" s="25" t="inlineStr">
         <is>
           <t>Mark DONE with explicit commit/date</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="25" t="inlineStr">
+      <c r="A6" s="23" t="inlineStr">
         <is>
           <t>5</t>
         </is>
       </c>
-      <c r="B6" s="26" t="inlineStr">
+      <c r="B6" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py status &lt;id&gt; IN_PROGRESS</t>
         </is>
       </c>
-      <c r="C6" s="27" t="inlineStr">
+      <c r="C6" s="25" t="inlineStr">
         <is>
           <t>Set arbitrary status (OPEN/IN_PROGRESS/DONE/DEFERRED/REJECTED)</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="25" t="inlineStr">
+      <c r="A7" s="23" t="inlineStr">
         <is>
           <t>6</t>
         </is>
       </c>
-      <c r="B7" s="26" t="inlineStr">
+      <c r="B7" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py add NEW-ID P1 "Section" "Item title" "What" "How"</t>
         </is>
       </c>
-      <c r="C7" s="27" t="inlineStr">
+      <c r="C7" s="25" t="inlineStr">
         <is>
           <t>Add a new item to the registry</t>
         </is>
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="25" t="inlineStr">
+      <c r="A8" s="23" t="inlineStr">
         <is>
           <t>7</t>
         </is>
       </c>
-      <c r="B8" s="26" t="inlineStr">
+      <c r="B8" s="24" t="inlineStr">
         <is>
           <t>python3 scripts/update_open_items.py xlsx</t>
         </is>
       </c>
-      <c r="C8" s="27" t="inlineStr">
+      <c r="C8" s="25" t="inlineStr">
         <is>
           <t>Regenerate this Excel from data/open_items.json</t>
         </is>
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="25" t="inlineStr">
+      <c r="A9" s="23" t="inlineStr">
         <is>
           <t>8</t>
         </is>
       </c>
-      <c r="B9" s="26" t="inlineStr">
+      <c r="B9" s="24" t="inlineStr">
         <is>
           <t>edit data/open_items.json directly, then run xlsx</t>
         </is>
       </c>
-      <c r="C9" s="27" t="inlineStr">
+      <c r="C9" s="25" t="inlineStr">
         <is>
           <t>Free-form edits — works too</t>
         </is>

--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -874,13 +874,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="90" customHeight="1">
+    <row r="5" ht="75" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -890,37 +890,37 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier is decorative — wire as filter or delete</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs + backtest validation</t>
+          <t>1 day + backtest</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Medium — changes live size or eliminates a layer</t>
+          <t>High win potential, medium risk</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Discovered while reworking T1 bar today. Today's T1 88-&gt;85 was reverted because lowering doesn't matter when the tier isn't gating anyway.</t>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -932,7 +932,7 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from collections import Counter; import json; sl=json.load(open("data/signal_log.json")); c=Counter((s.get("conviction_label") or "none").upper() for s in sl if s.get("status")=="CLOSED"); print(c)' — expect 'NONE' (or '—') for ~90%+.</t>
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
         </is>
       </c>
     </row>
@@ -942,69 +942,77 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
-        </is>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>K6</t>
+        </is>
+      </c>
+      <c r="C6" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
-      <c r="K6" s="7" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="3" t="inlineStr"/>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+        </is>
+      </c>
+      <c r="K6" s="11" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M6" s="3" t="inlineStr">
+        <is>
+          <t>2c9b9f339</t>
+        </is>
+      </c>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="90" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1014,37 +1022,29 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I7" s="5" t="inlineStr">
-        <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
-        </is>
-      </c>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="5" t="inlineStr"/>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>2c9b9f339</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1084,31 +1084,27 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr">
-        <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
-        </is>
-      </c>
+      <c r="J8" s="5" t="inlineStr"/>
       <c r="K8" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1121,22 +1117,18 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr">
-        <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr"/>
+    </row>
+    <row r="9" ht="45" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1146,27 +1138,39 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr"/>
-      <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I9" s="5" t="inlineStr">
+        <is>
+          <t>CRITICAL — system was unable to backtest</t>
+        </is>
+      </c>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+        </is>
+      </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1179,18 +1183,22 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="90" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1200,37 +1208,37 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>CRITICAL — system was unable to backtest</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
@@ -1245,22 +1253,22 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="105" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1270,22 +1278,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1295,12 +1303,12 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
@@ -1310,27 +1318,27 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="105" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="45" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1340,37 +1348,37 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Low / Required</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
@@ -1380,27 +1388,27 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>b0e5ef6a1</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="120" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1410,39 +1418,27 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I13" s="5" t="inlineStr">
-        <is>
-          <t>Low / Required</t>
-        </is>
-      </c>
-      <c r="J13" s="5" t="inlineStr">
-        <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr"/>
+      <c r="I13" s="5" t="inlineStr"/>
+      <c r="J13" s="5" t="inlineStr"/>
       <c r="K13" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1455,22 +1451,18 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr">
-        <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="120" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr"/>
+    </row>
+    <row r="14" ht="60" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1480,27 +1472,39 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+        </is>
+      </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1508,23 +1512,27 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="45" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1539,32 +1547,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
@@ -1584,7 +1592,7 @@
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
         </is>
       </c>
     </row>
@@ -1594,7 +1602,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1609,17 +1617,17 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1629,12 +1637,12 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
@@ -1654,17 +1662,17 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="45" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="60" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1679,32 +1687,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
@@ -1714,27 +1722,27 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="180" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1749,32 +1757,32 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
@@ -1789,22 +1797,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="180" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="45" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1819,32 +1827,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
@@ -1859,22 +1867,22 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="90" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1884,37 +1892,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
@@ -1924,27 +1932,27 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1954,22 +1962,22 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1979,12 +1987,12 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
@@ -1999,12 +2007,12 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
         </is>
       </c>
     </row>
@@ -2014,7 +2022,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2029,32 +2037,32 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (revert candidate)</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
@@ -2069,22 +2077,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="45" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="105" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2094,37 +2102,29 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr">
-        <is>
-          <t>shipped (revert candidate)</t>
-        </is>
-      </c>
-      <c r="I23" s="5" t="inlineStr">
-        <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr"/>
+      <c r="I23" s="5" t="inlineStr"/>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
@@ -2134,27 +2134,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="60" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2164,29 +2164,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Win: single most important Vinod rule per coaching call.</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
@@ -2196,27 +2204,27 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="90" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2226,37 +2234,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>in flight</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
@@ -2266,27 +2274,27 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>logs/backtest_750d_quant1_validate2</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="90" customHeight="1">
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="75" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2296,39 +2304,27 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr">
-        <is>
-          <t>in flight</t>
-        </is>
-      </c>
-      <c r="I26" s="5" t="inlineStr">
-        <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
-        </is>
-      </c>
-      <c r="J26" s="5" t="inlineStr">
-        <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr"/>
+      <c r="I26" s="5" t="inlineStr"/>
+      <c r="J26" s="5" t="inlineStr"/>
       <c r="K26" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2341,22 +2337,18 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr">
-        <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="75" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr"/>
+    </row>
+    <row r="27" ht="45" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2366,27 +2358,39 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>High — addresses #1 PF drag</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+        </is>
+      </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2399,18 +2403,22 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>f0a66543e</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="60" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2420,37 +2428,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>High — addresses #1 PF drag</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr">
@@ -2460,17 +2468,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
         </is>
       </c>
     </row>
@@ -2480,7 +2488,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2495,17 +2503,17 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2515,12 +2523,12 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>Win: bull-only strategy, period.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
@@ -2535,22 +2543,22 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="60" customHeight="1">
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="75" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>TARGET-CAP-10WK</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2560,39 +2568,27 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I30" s="5" t="inlineStr">
-        <is>
-          <t>Win: bull-only strategy, period.</t>
-        </is>
-      </c>
-      <c r="J30" s="5" t="inlineStr">
-        <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr"/>
+      <c r="I30" s="5" t="inlineStr"/>
+      <c r="J30" s="5" t="inlineStr"/>
       <c r="K30" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2600,57 +2596,65 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr">
-        <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="75" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr"/>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
-        </is>
-      </c>
-      <c r="C31" s="10" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>B1</t>
+        </is>
+      </c>
+      <c r="C31" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>shipped (diagnosis); pending (fix)</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
+        </is>
+      </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2658,23 +2662,27 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
+          <t>9bc015562</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="105" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2684,37 +2692,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>shipped (diagnosis); pending (fix)</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr">
@@ -2724,27 +2732,27 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="105" customHeight="1">
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="45" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2754,37 +2762,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
@@ -2794,7 +2802,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2804,7 +2812,7 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2814,7 +2822,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2829,22 +2837,22 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2854,7 +2862,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
@@ -2874,7 +2882,7 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2892,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2899,32 +2907,32 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
@@ -2944,17 +2952,17 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="45" customHeight="1">
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="60" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2969,32 +2977,32 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
@@ -3014,7 +3022,7 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
         </is>
       </c>
     </row>
@@ -3024,7 +3032,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3034,37 +3042,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
@@ -3079,22 +3087,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="60" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="90" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3109,32 +3117,32 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
@@ -3154,17 +3162,17 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="90" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3174,37 +3182,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
@@ -3214,27 +3222,27 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="60" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3244,22 +3252,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3269,12 +3277,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
@@ -3289,22 +3297,22 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="90" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3314,37 +3322,33 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr">
-        <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
-        </is>
-      </c>
+          <t>4-6 hrs</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr"/>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr">
@@ -3354,27 +3358,27 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="90" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="75" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3389,28 +3393,28 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>8-12 hrs</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr">
@@ -3430,17 +3434,17 @@
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="75" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="135" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3450,33 +3454,37 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr"/>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / High win</t>
+        </is>
+      </c>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
@@ -3491,22 +3499,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="135" customHeight="1">
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="45" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3516,37 +3524,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
@@ -3556,17 +3564,17 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
         </is>
       </c>
     </row>
@@ -3576,7 +3584,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3591,32 +3599,32 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
@@ -3631,22 +3639,22 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="45" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="120" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3661,32 +3669,32 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
@@ -3696,27 +3704,27 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="120" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="135" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3731,32 +3739,32 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
@@ -3771,22 +3779,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="135" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="75" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3796,37 +3804,29 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr">
-        <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I48" s="5" t="inlineStr">
-        <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="5" t="inlineStr"/>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
@@ -3841,22 +3841,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="75" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="105" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3866,29 +3866,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+        </is>
+      </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
@@ -3903,22 +3911,22 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="60" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3933,32 +3941,32 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>2-4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
@@ -3973,22 +3981,22 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="105" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4003,32 +4011,32 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
@@ -4043,22 +4051,22 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="105" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4068,37 +4076,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
@@ -4108,27 +4116,27 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="120" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4138,37 +4146,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
@@ -4178,7 +4186,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4188,17 +4196,17 @@
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="120" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="75" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4208,37 +4216,37 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
@@ -4248,27 +4256,27 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="60" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4283,17 +4291,17 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4303,12 +4311,12 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
@@ -4328,17 +4336,17 @@
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="60" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4348,22 +4356,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4373,12 +4381,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
@@ -4393,22 +4401,22 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="90" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4418,37 +4426,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (additive only)</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
@@ -4458,17 +4466,17 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
         </is>
       </c>
     </row>
@@ -4478,7 +4486,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4488,39 +4496,27 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr">
-        <is>
-          <t>shipped (additive only)</t>
-        </is>
-      </c>
-      <c r="I58" s="5" t="inlineStr">
-        <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
-        </is>
-      </c>
-      <c r="J58" s="5" t="inlineStr">
-        <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
-        </is>
-      </c>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr"/>
+      <c r="I58" s="5" t="inlineStr"/>
+      <c r="J58" s="5" t="inlineStr"/>
       <c r="K58" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4533,22 +4529,18 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
-        </is>
-      </c>
-      <c r="N58" s="8" t="inlineStr">
-        <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
-        </is>
-      </c>
-    </row>
-    <row r="59" ht="90" customHeight="1">
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N58" s="8" t="inlineStr"/>
+    </row>
+    <row r="59" ht="105" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4558,27 +4550,31 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+        </is>
+      </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4591,18 +4587,22 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="inlineStr"/>
-    </row>
-    <row r="60" ht="105" customHeight="1">
+          <t>40f8452b8</t>
+        </is>
+      </c>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="45" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4612,29 +4612,37 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr"/>
-      <c r="I60" s="5" t="inlineStr"/>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>30 min</t>
+        </is>
+      </c>
+      <c r="I60" s="5" t="inlineStr">
+        <is>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
+        </is>
+      </c>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
@@ -4649,22 +4657,22 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="90" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4674,37 +4682,37 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
+          <t>Low / High (transparency + future-proof)</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
@@ -4719,22 +4727,22 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="90" customHeight="1">
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="75" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4744,39 +4752,27 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr">
-        <is>
-          <t>2 hrs</t>
-        </is>
-      </c>
-      <c r="I62" s="5" t="inlineStr">
-        <is>
-          <t>Low / High (transparency + future-proof)</t>
-        </is>
-      </c>
-      <c r="J62" s="5" t="inlineStr">
-        <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr"/>
+      <c r="I62" s="5" t="inlineStr"/>
+      <c r="J62" s="5" t="inlineStr"/>
       <c r="K62" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4789,22 +4785,18 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
-        </is>
-      </c>
-      <c r="N62" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="75" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N62" s="8" t="inlineStr"/>
+    </row>
+    <row r="63" ht="60" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4814,27 +4806,39 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Win: continuous drift visibility between alert events.</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+        </is>
+      </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4842,23 +4846,27 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N63" s="8" t="inlineStr"/>
-    </row>
-    <row r="64" ht="60" customHeight="1">
+          <t>16a26b201</t>
+        </is>
+      </c>
+      <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="45" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4868,37 +4876,37 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Win: continuous drift visibility between alert events.</t>
+          <t>Win: full auth-gated test coverage in CI.</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
@@ -4913,22 +4921,22 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="105" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4943,32 +4951,24 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I65" s="5" t="inlineStr">
-        <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr"/>
+      <c r="I65" s="5" t="inlineStr"/>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
@@ -4978,17 +4978,17 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5013,24 +5013,24 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
@@ -5045,22 +5045,22 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="105" customHeight="1">
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="45" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5070,29 +5070,37 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="5" t="inlineStr"/>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>45 min</t>
+        </is>
+      </c>
+      <c r="I67" s="5" t="inlineStr">
+        <is>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>All reads use ?? fallbacks.</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
@@ -5107,12 +5115,12 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
         </is>
       </c>
     </row>
@@ -5122,7 +5130,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5132,39 +5140,35 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>45 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr">
-        <is>
-          <t>All reads use ?? fallbacks.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr"/>
       <c r="K68" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5177,22 +5181,22 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="45" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="105" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>TARGET-SOURCES-P1</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5202,35 +5206,39 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr"/>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5243,64 +5251,60 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="105" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="60" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
-        </is>
-      </c>
-      <c r="C70" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>J1</t>
+        </is>
+      </c>
+      <c r="C70" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5308,27 +5312,27 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="60" customHeight="1">
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="75" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5343,17 +5347,17 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5363,10 +5367,14 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr"/>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5379,12 +5387,12 @@
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
         </is>
       </c>
     </row>
@@ -5394,7 +5402,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5409,34 +5417,22 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I72" s="5" t="inlineStr">
-        <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr"/>
+      <c r="I72" s="5" t="inlineStr"/>
+      <c r="J72" s="5" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5444,27 +5440,23 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N72" s="8" t="inlineStr">
-        <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
-        </is>
-      </c>
-    </row>
-    <row r="73" ht="75" customHeight="1">
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N72" s="8" t="inlineStr"/>
+    </row>
+    <row r="73" ht="45" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5474,26 +5466,34 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
       <c r="J73" s="5" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr">
         <is>
@@ -5502,15 +5502,19 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N73" s="8" t="inlineStr"/>
+          <t>4129e5565</t>
+        </is>
+      </c>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
     </row>
     <row r="74" ht="45" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -5518,7 +5522,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -5528,35 +5532,39 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr"/>
+          <t>Low</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr">
+        <is>
+          <t>Sub-task of IPAD-1.</t>
+        </is>
+      </c>
       <c r="K74" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5564,27 +5572,27 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="45" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="75" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5594,37 +5602,37 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>Sub-task of IPAD-1.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
@@ -5634,27 +5642,27 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="75" customHeight="1">
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="60" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5664,37 +5672,37 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
@@ -5704,17 +5712,17 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -5724,7 +5732,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5739,32 +5747,32 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
@@ -5784,7 +5792,7 @@
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5802,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5809,32 +5817,32 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
@@ -5854,7 +5862,7 @@
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5872,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5879,32 +5887,32 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: fast iteration on report templates.</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
@@ -5914,27 +5922,27 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="60" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="150" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5944,37 +5952,29 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I80" s="5" t="inlineStr">
-        <is>
-          <t>Win: fast iteration on report templates.</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr"/>
+      <c r="I80" s="5" t="inlineStr"/>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
@@ -5984,27 +5984,27 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="150" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="120" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -6014,29 +6014,37 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
@@ -6046,17 +6054,17 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
         </is>
       </c>
     </row>
@@ -6831,10 +6839,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="17" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
     </row>
     <row r="3">
@@ -6850,10 +6858,10 @@
         <v>39</v>
       </c>
       <c r="D3" s="17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E3" s="17" t="n">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="4">

--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N92"/>
+  <dimension ref="A1:N93"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -874,13 +874,13 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="75" customHeight="1">
+    <row r="5" ht="165" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
+          <t>TV-RATING-CROSS-CHECK</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -890,37 +890,37 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Signals / Cross-Check</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>tradingview-ta cross-check rating as independent confirmation signal</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>TradingView publishes a server-computed Strong Buy/Buy/Neutral/Sell/Strong Sell rating per (symbol x timeframe), aggregated from ~26 indicators. Free unofficial library 'tradingview-ta' fetches it. Use as INFORMATIONAL second-opinion signal cross-checking the 5-pillar score. Default apply_to_score=false until Wilson-LB on agreement-conditional WR clears unconditional WR over n&gt;=30 closed trades. No new paid data license (constraint OK).</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
+          <t>1) pip install tradingview-ta. 2) data_fetcher.get_tv_rating(ticker) returns {rating, buy_signals, sell_signals, neutral_signals, summary_score, ts} with 4h cache (matches existing news TTL discipline). 3) Add tv_rating field to last_bundle.json per-ticker payload. 4) Surface in v2 dashboard Overview sub-tab as 'TV Agrees / TV Disagrees / TV Neutral' tile next to verdict arc. 5) Log to data/signal_log.json per emit so Wilson-CI agreement-conditional WR can be computed offline. 6) Backtest hook: compute Wilson-LB(BUY | TV agrees) vs Wilson-LB(BUY) over 250d. 7) Only flip apply_to_score=true after walk-forward shows lift across regimes. 8) Failure-mode: TV endpoint 500 -&gt; tv_rating=null, scanner continues, log 'tv_rating_unavailable' counter.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1 day + backtest</t>
+          <t>hours</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>High win potential, medium risk</t>
+          <t>Mechanism (Principle 2): TV rating is a server-side weighted aggregate of ~26 indicators — an independent technical signal (different weighting than ours). Two independent confirmations &gt; one. Falsification (Principle 4): if agreement-conditional Wilson-LB after n&gt;=30 doesn t beat unconditional Wilson-LB, kill the cross-check. Risk: TV unofficial endpoints break ~2-4x/year; needs null-safe failure path. No new paid data license (hard constraint OK).</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+          <t>Default apply_to_score=false per tier1_signals convention. Cache 4h TTL, well under TV daily update cadence. Pairs naturally with the existing TV sub-tab (infra/prototype/subtabs/tv/) which today is iframe-only - this is the data backbone for it. Catalyst-tier breakout in backtest: TV agreement may help T1/T2 more than pure technicals.</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -932,7 +932,7 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+          <t>Smoke: python3 -c "from data_fetcher import get_tv_rating; print(get_tv_rating(NVDA))" returns dict. Cache: second call within 4h is cache hit. Failure: simulate TV 500 -&gt; scanner continues, ticker payload tv_rating=null. Backtest: python3 backtest.py --days 250 prints Wilson-LB(BUY|TV agrees) vs Wilson-LB(BUY). Gate: apply_to_score=false stays locked until n&gt;=30 with positive lift across at least 2 regimes.</t>
         </is>
       </c>
     </row>
@@ -942,77 +942,69 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C6" s="10" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
+        </is>
+      </c>
+      <c r="C6" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 day + backtest</t>
         </is>
       </c>
       <c r="I6" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>High win potential, medium risk</t>
         </is>
       </c>
       <c r="J6" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K6" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L6" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M6" s="3" t="inlineStr">
-        <is>
-          <t>2c9b9f339</t>
-        </is>
-      </c>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K6" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="3" t="inlineStr"/>
       <c r="N6" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="90" customHeight="1">
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="n">
         <v>6</v>
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C7" s="10" t="inlineStr">
@@ -1022,29 +1014,37 @@
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="5" t="inlineStr"/>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I7" s="5" t="inlineStr">
+        <is>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+        </is>
+      </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K7" s="11" t="inlineStr">
@@ -1054,27 +1054,27 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M7" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>2c9b9f339</t>
         </is>
       </c>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="90" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1084,27 +1084,31 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr"/>
       <c r="I8" s="5" t="inlineStr"/>
-      <c r="J8" s="5" t="inlineStr"/>
+      <c r="J8" s="5" t="inlineStr">
+        <is>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+        </is>
+      </c>
       <c r="K8" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1117,18 +1121,22 @@
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N8" s="8" t="inlineStr"/>
-    </row>
-    <row r="9" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N8" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="75" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1138,39 +1146,27 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I9" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J9" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr"/>
       <c r="K9" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1183,22 +1179,18 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr"/>
+    </row>
+    <row r="10" ht="45" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1208,37 +1200,37 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I10" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>CRITICAL — system was unable to backtest</t>
         </is>
       </c>
       <c r="J10" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
         </is>
       </c>
       <c r="K10" s="11" t="inlineStr">
@@ -1253,22 +1245,22 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N10" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="105" customHeight="1">
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="90" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1278,22 +1270,22 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
@@ -1303,12 +1295,12 @@
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
@@ -1318,27 +1310,27 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="45" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="105" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1348,37 +1340,37 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Low / Required</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
@@ -1388,27 +1380,27 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="120" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="45" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1418,27 +1410,39 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr"/>
-      <c r="I13" s="5" t="inlineStr"/>
-      <c r="J13" s="5" t="inlineStr"/>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I13" s="5" t="inlineStr">
+        <is>
+          <t>Low / Required</t>
+        </is>
+      </c>
+      <c r="J13" s="5" t="inlineStr">
+        <is>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+        </is>
+      </c>
       <c r="K13" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1451,18 +1455,22 @@
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N13" s="8" t="inlineStr"/>
-    </row>
-    <row r="14" ht="60" customHeight="1">
+          <t>b0e5ef6a1</t>
+        </is>
+      </c>
+      <c r="N13" s="8" t="inlineStr">
+        <is>
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="120" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1472,39 +1480,27 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I14" s="5" t="inlineStr">
-        <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
-        </is>
-      </c>
-      <c r="J14" s="5" t="inlineStr">
-        <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr"/>
+      <c r="I14" s="5" t="inlineStr"/>
+      <c r="J14" s="5" t="inlineStr"/>
       <c r="K14" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1512,27 +1508,23 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="45" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr"/>
+    </row>
+    <row r="15" ht="60" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1547,32 +1539,32 @@
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I15" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J15" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K15" s="11" t="inlineStr">
@@ -1592,7 +1584,7 @@
       </c>
       <c r="N15" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
         </is>
       </c>
     </row>
@@ -1602,7 +1594,7 @@
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1617,17 +1609,17 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
@@ -1637,12 +1629,12 @@
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
@@ -1662,17 +1654,17 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="60" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="45" customHeight="1">
       <c r="A17" s="2" t="n">
         <v>16</v>
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1687,32 +1679,32 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
@@ -1722,27 +1714,27 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M17" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="180" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="60" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1757,32 +1749,32 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
@@ -1797,22 +1789,22 @@
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="180" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1827,32 +1819,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
@@ -1867,22 +1859,22 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="90" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="45" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1892,37 +1884,37 @@
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
@@ -1932,27 +1924,27 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="90" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1962,22 +1954,22 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
@@ -1987,12 +1979,12 @@
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
@@ -2007,12 +1999,12 @@
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
         </is>
       </c>
     </row>
@@ -2022,7 +2014,7 @@
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2037,32 +2029,32 @@
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
@@ -2077,22 +2069,22 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="105" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="45" customHeight="1">
       <c r="A23" s="2" t="n">
         <v>22</v>
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2102,29 +2094,37 @@
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H23" s="2" t="inlineStr"/>
-      <c r="I23" s="5" t="inlineStr"/>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>shipped (revert candidate)</t>
+        </is>
+      </c>
+      <c r="I23" s="5" t="inlineStr">
+        <is>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+        </is>
+      </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
@@ -2134,27 +2134,27 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="60" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="105" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2164,37 +2164,29 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I24" s="5" t="inlineStr">
-        <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr"/>
+      <c r="I24" s="5" t="inlineStr"/>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
@@ -2204,27 +2196,27 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="60" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2234,37 +2226,37 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I25" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
@@ -2274,27 +2266,27 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="90" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2304,27 +2296,39 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H26" s="2" t="inlineStr"/>
-      <c r="I26" s="5" t="inlineStr"/>
-      <c r="J26" s="5" t="inlineStr"/>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>in flight</t>
+        </is>
+      </c>
+      <c r="I26" s="5" t="inlineStr">
+        <is>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+        </is>
+      </c>
+      <c r="J26" s="5" t="inlineStr">
+        <is>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+        </is>
+      </c>
       <c r="K26" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2337,18 +2341,22 @@
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N26" s="8" t="inlineStr"/>
-    </row>
-    <row r="27" ht="45" customHeight="1">
+          <t>logs/backtest_750d_quant1_validate2</t>
+        </is>
+      </c>
+      <c r="N26" s="8" t="inlineStr">
+        <is>
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="75" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2358,39 +2366,27 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I27" s="5" t="inlineStr">
-        <is>
-          <t>High — addresses #1 PF drag</t>
-        </is>
-      </c>
-      <c r="J27" s="5" t="inlineStr">
-        <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr"/>
+      <c r="I27" s="5" t="inlineStr"/>
+      <c r="J27" s="5" t="inlineStr"/>
       <c r="K27" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2403,22 +2399,18 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr">
-        <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="60" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr"/>
+    </row>
+    <row r="28" ht="45" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2428,37 +2420,37 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I28" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J28" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K28" s="11" t="inlineStr">
@@ -2468,17 +2460,17 @@
       </c>
       <c r="L28" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N28" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
         </is>
       </c>
     </row>
@@ -2488,7 +2480,7 @@
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2503,17 +2495,17 @@
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
@@ -2523,12 +2515,12 @@
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
@@ -2543,22 +2535,22 @@
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="30" ht="75" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="60" customHeight="1">
       <c r="A30" s="2" t="n">
         <v>29</v>
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2568,27 +2560,39 @@
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr"/>
-      <c r="I30" s="5" t="inlineStr"/>
-      <c r="J30" s="5" t="inlineStr"/>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I30" s="5" t="inlineStr">
+        <is>
+          <t>Win: bull-only strategy, period.</t>
+        </is>
+      </c>
+      <c r="J30" s="5" t="inlineStr">
+        <is>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
+        </is>
+      </c>
       <c r="K30" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2596,65 +2600,57 @@
       </c>
       <c r="L30" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N30" s="8" t="inlineStr"/>
-    </row>
-    <row r="31" ht="60" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N30" s="8" t="inlineStr">
+        <is>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="75" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C31" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TARGET-CAP-10WK</t>
+        </is>
+      </c>
+      <c r="C31" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>shipped (diagnosis); pending (fix)</t>
-        </is>
-      </c>
-      <c r="I31" s="5" t="inlineStr">
-        <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
-        </is>
-      </c>
-      <c r="J31" s="5" t="inlineStr">
-        <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr"/>
+      <c r="I31" s="5" t="inlineStr"/>
+      <c r="J31" s="5" t="inlineStr"/>
       <c r="K31" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2662,27 +2658,23 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr">
-        <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="105" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr"/>
+    </row>
+    <row r="32" ht="60" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C32" s="4" t="inlineStr">
@@ -2692,37 +2684,37 @@
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I32" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J32" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K32" s="11" t="inlineStr">
@@ -2732,27 +2724,27 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N32" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="45" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="105" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2762,37 +2754,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
@@ -2802,7 +2794,7 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
@@ -2812,7 +2804,7 @@
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
         </is>
       </c>
     </row>
@@ -2822,7 +2814,7 @@
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2837,22 +2829,22 @@
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
@@ -2862,7 +2854,7 @@
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
@@ -2882,7 +2874,7 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2892,7 +2884,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2907,32 +2899,32 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
@@ -2952,17 +2944,17 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="36" ht="60" customHeight="1">
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="45" customHeight="1">
       <c r="A36" s="2" t="n">
         <v>35</v>
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2977,32 +2969,32 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
@@ -3022,7 +3014,7 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
         </is>
       </c>
     </row>
@@ -3032,7 +3024,7 @@
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3042,37 +3034,37 @@
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
@@ -3087,22 +3079,22 @@
       </c>
       <c r="M37" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38" ht="90" customHeight="1">
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38" ht="60" customHeight="1">
       <c r="A38" s="2" t="n">
         <v>37</v>
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3117,32 +3109,32 @@
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
@@ -3162,17 +3154,17 @@
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="45" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="90" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3182,37 +3174,37 @@
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
@@ -3222,27 +3214,27 @@
       </c>
       <c r="L39" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M39" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="60" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="45" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3252,22 +3244,22 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
@@ -3277,12 +3269,12 @@
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
@@ -3297,22 +3289,22 @@
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="90" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="60" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3322,33 +3314,37 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I41" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I41" s="5" t="inlineStr">
+        <is>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+        </is>
+      </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr">
@@ -3358,27 +3354,27 @@
       </c>
       <c r="L41" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="75" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="90" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3393,28 +3389,28 @@
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I42" s="5" t="inlineStr"/>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr">
@@ -3434,17 +3430,17 @@
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="135" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="75" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3454,37 +3450,33 @@
       </c>
       <c r="D43" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I43" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / High win</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
@@ -3499,22 +3491,22 @@
       </c>
       <c r="M43" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="45" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="135" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3524,37 +3516,37 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I44" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
@@ -3564,17 +3556,17 @@
       </c>
       <c r="L44" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
         </is>
       </c>
     </row>
@@ -3584,7 +3576,7 @@
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3599,32 +3591,32 @@
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
@@ -3639,22 +3631,22 @@
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="46" ht="120" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="46" ht="45" customHeight="1">
       <c r="A46" s="2" t="n">
         <v>45</v>
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3669,32 +3661,32 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
@@ -3704,27 +3696,27 @@
       </c>
       <c r="L46" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="135" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="120" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3739,32 +3731,32 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
@@ -3779,22 +3771,22 @@
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="75" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="135" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3804,29 +3796,37 @@
       </c>
       <c r="D48" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="5" t="inlineStr"/>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I48" s="5" t="inlineStr">
+        <is>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+        </is>
+      </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
@@ -3841,22 +3841,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="105" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="75" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3866,37 +3866,29 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs</t>
-        </is>
-      </c>
-      <c r="I49" s="5" t="inlineStr">
-        <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="5" t="inlineStr"/>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
@@ -3911,22 +3903,22 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="60" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="105" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3941,32 +3933,32 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H50" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I50" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
         </is>
       </c>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
@@ -3981,22 +3973,22 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="60" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4011,32 +4003,32 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
@@ -4051,22 +4043,22 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="105" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4076,37 +4068,37 @@
       </c>
       <c r="D52" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
@@ -4116,27 +4108,27 @@
       </c>
       <c r="L52" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="120" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="60" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4146,37 +4138,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
@@ -4186,7 +4178,7 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
@@ -4196,17 +4188,17 @@
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="75" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="120" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4216,37 +4208,37 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
@@ -4256,27 +4248,27 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="60" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="75" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4291,17 +4283,17 @@
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
@@ -4311,12 +4303,12 @@
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
@@ -4336,17 +4328,17 @@
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="60" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4356,22 +4348,22 @@
       </c>
       <c r="D56" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4381,12 +4373,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
@@ -4401,22 +4393,22 @@
       </c>
       <c r="M56" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="90" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="75" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4426,37 +4418,37 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
@@ -4466,17 +4458,17 @@
       </c>
       <c r="L57" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
         </is>
       </c>
     </row>
@@ -4486,7 +4478,7 @@
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4496,27 +4488,39 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
-        </is>
-      </c>
-      <c r="H58" s="2" t="inlineStr"/>
-      <c r="I58" s="5" t="inlineStr"/>
-      <c r="J58" s="5" t="inlineStr"/>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>shipped (additive only)</t>
+        </is>
+      </c>
+      <c r="I58" s="5" t="inlineStr">
+        <is>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+        </is>
+      </c>
+      <c r="J58" s="5" t="inlineStr">
+        <is>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+        </is>
+      </c>
       <c r="K58" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4529,18 +4533,22 @@
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N58" s="8" t="inlineStr"/>
-    </row>
-    <row r="59" ht="105" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N58" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="90" customHeight="1">
       <c r="A59" s="2" t="n">
         <v>58</v>
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4550,31 +4558,27 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
         </is>
       </c>
       <c r="H59" s="2" t="inlineStr"/>
       <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr">
-        <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
-        </is>
-      </c>
+      <c r="J59" s="5" t="inlineStr"/>
       <c r="K59" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4587,22 +4591,18 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="inlineStr">
-        <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="60" ht="45" customHeight="1">
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N59" s="8" t="inlineStr"/>
+    </row>
+    <row r="60" ht="105" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4612,37 +4612,29 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
-        </is>
-      </c>
-      <c r="H60" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I60" s="5" t="inlineStr">
-        <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
-        </is>
-      </c>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr"/>
+      <c r="I60" s="5" t="inlineStr"/>
       <c r="J60" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
         </is>
       </c>
       <c r="K60" s="11" t="inlineStr">
@@ -4657,22 +4649,22 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N60" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="90" customHeight="1">
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="61" ht="45" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4682,37 +4674,37 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
         </is>
       </c>
       <c r="H61" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I61" s="5" t="inlineStr">
         <is>
-          <t>Low / High (transparency + future-proof)</t>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
         </is>
       </c>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
@@ -4727,22 +4719,22 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="75" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="90" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4752,27 +4744,39 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
-        </is>
-      </c>
-      <c r="H62" s="2" t="inlineStr"/>
-      <c r="I62" s="5" t="inlineStr"/>
-      <c r="J62" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I62" s="5" t="inlineStr">
+        <is>
+          <t>Low / High (transparency + future-proof)</t>
+        </is>
+      </c>
+      <c r="J62" s="5" t="inlineStr">
+        <is>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
       <c r="K62" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4785,18 +4789,22 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N62" s="8" t="inlineStr"/>
-    </row>
-    <row r="63" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N62" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="75" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4806,39 +4814,27 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I63" s="5" t="inlineStr">
-        <is>
-          <t>Win: continuous drift visibility between alert events.</t>
-        </is>
-      </c>
-      <c r="J63" s="5" t="inlineStr">
-        <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr"/>
+      <c r="I63" s="5" t="inlineStr"/>
+      <c r="J63" s="5" t="inlineStr"/>
       <c r="K63" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4846,27 +4842,23 @@
       </c>
       <c r="L63" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-      <c r="N63" s="8" t="inlineStr">
-        <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="64" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N63" s="8" t="inlineStr"/>
+    </row>
+    <row r="64" ht="60" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4876,37 +4868,37 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I64" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J64" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K64" s="11" t="inlineStr">
@@ -4921,22 +4913,22 @@
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N64" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="105" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="65" ht="45" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4951,24 +4943,32 @@
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H65" s="2" t="inlineStr"/>
-      <c r="I65" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I65" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
@@ -4978,17 +4978,17 @@
       </c>
       <c r="L65" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -4998,7 +4998,7 @@
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5013,24 +5013,24 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr"/>
       <c r="I66" s="5" t="inlineStr"/>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
@@ -5045,22 +5045,22 @@
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="67" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="67" ht="105" customHeight="1">
       <c r="A67" s="2" t="n">
         <v>66</v>
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5070,37 +5070,29 @@
       </c>
       <c r="D67" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
-        </is>
-      </c>
-      <c r="H67" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I67" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
@@ -5115,12 +5107,12 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
         </is>
       </c>
     </row>
@@ -5130,7 +5122,7 @@
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5140,35 +5132,39 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I68" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J68" s="5" t="inlineStr"/>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J68" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K68" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5181,22 +5177,22 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="69" ht="105" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="69" ht="45" customHeight="1">
       <c r="A69" s="2" t="n">
         <v>68</v>
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5206,39 +5202,35 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr"/>
       <c r="K69" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5251,60 +5243,64 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="60" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="105" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C70" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TARGET-SOURCES-P1</t>
+        </is>
+      </c>
+      <c r="C70" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr"/>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K70" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5312,27 +5308,27 @@
       </c>
       <c r="L70" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="75" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="60" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C71" s="9" t="inlineStr">
@@ -5347,17 +5343,17 @@
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
@@ -5367,14 +5363,10 @@
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr"/>
       <c r="K71" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5387,12 +5379,12 @@
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5394,7 @@
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5417,22 +5409,34 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H72" s="2" t="inlineStr"/>
-      <c r="I72" s="5" t="inlineStr"/>
-      <c r="J72" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I72" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K72" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5440,23 +5444,27 @@
       </c>
       <c r="L72" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N72" s="8" t="inlineStr"/>
-    </row>
-    <row r="73" ht="45" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N72" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="73" ht="75" customHeight="1">
       <c r="A73" s="2" t="n">
         <v>72</v>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5466,34 +5474,26 @@
       </c>
       <c r="D73" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I73" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr"/>
+      <c r="I73" s="5" t="inlineStr"/>
       <c r="J73" s="5" t="inlineStr"/>
       <c r="K73" s="11" t="inlineStr">
         <is>
@@ -5502,19 +5502,15 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N73" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N73" s="8" t="inlineStr"/>
     </row>
     <row r="74" ht="45" customHeight="1">
       <c r="A74" s="2" t="n">
@@ -5522,7 +5518,7 @@
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -5532,39 +5528,35 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H74" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I74" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J74" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J74" s="5" t="inlineStr"/>
       <c r="K74" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5572,27 +5564,27 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N74" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="75" ht="75" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="75" ht="45" customHeight="1">
       <c r="A75" s="2" t="n">
         <v>74</v>
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5602,37 +5594,37 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J75" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Sub-task of IPAD-1.</t>
         </is>
       </c>
       <c r="K75" s="11" t="inlineStr">
@@ -5642,27 +5634,27 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="60" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="75" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5672,37 +5664,37 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
@@ -5712,17 +5704,17 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -5732,7 +5724,7 @@
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5747,32 +5739,32 @@
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
@@ -5792,7 +5784,7 @@
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -5802,7 +5794,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5817,32 +5809,32 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
@@ -5862,7 +5854,7 @@
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -5872,7 +5864,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5887,32 +5879,32 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
@@ -5922,27 +5914,27 @@
       </c>
       <c r="L79" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M79" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="80" ht="150" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="80" ht="60" customHeight="1">
       <c r="A80" s="2" t="n">
         <v>79</v>
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5952,29 +5944,37 @@
       </c>
       <c r="D80" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H80" s="2" t="inlineStr"/>
-      <c r="I80" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H80" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I80" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
@@ -5984,27 +5984,27 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="120" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="150" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -6014,37 +6014,29 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I81" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr"/>
+      <c r="I81" s="5" t="inlineStr"/>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
@@ -6054,27 +6046,27 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="105" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="120" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -6084,29 +6076,37 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr"/>
-      <c r="I82" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I82" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
@@ -6126,17 +6126,17 @@
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="135" customHeight="1">
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="105" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -6146,37 +6146,29 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I83" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr"/>
+      <c r="I83" s="5" t="inlineStr"/>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
@@ -6186,27 +6178,27 @@
       </c>
       <c r="L83" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M83" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="120" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="135" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -6216,29 +6208,37 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr"/>
-      <c r="I84" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I84" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
@@ -6248,67 +6248,59 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>42c36ef91</t>
         </is>
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="45" customHeight="1">
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="120" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C85" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>RECENCY-FLOOR</t>
+        </is>
+      </c>
+      <c r="C85" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I85" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr"/>
+      <c r="I85" s="5" t="inlineStr"/>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
@@ -6318,13 +6310,17 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M85" s="3" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M85" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
         </is>
       </c>
     </row>
@@ -6334,7 +6330,7 @@
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C86" s="12" t="inlineStr">
@@ -6349,32 +6345,32 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H86" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I86" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
@@ -6390,7 +6386,7 @@
       <c r="M86" s="3" t="inlineStr"/>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -6400,7 +6396,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6410,35 +6406,39 @@
       </c>
       <c r="D87" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J87" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J87" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K87" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6446,17 +6446,13 @@
       </c>
       <c r="L87" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M87" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -6466,59 +6462,63 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C88" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K88" s="13" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L88" s="2" t="inlineStr"/>
-      <c r="M88" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr"/>
+      <c r="K88" s="11" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L88" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -6528,7 +6528,7 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C89" s="9" t="inlineStr">
@@ -6538,37 +6538,37 @@
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J89" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
@@ -6590,109 +6590,109 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C90" s="10" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C90" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K90" s="14" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K90" s="13" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L90" s="2" t="inlineStr"/>
       <c r="M90" s="3" t="inlineStr"/>
       <c r="N90" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="91" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="91" ht="45" customHeight="1">
       <c r="A91" s="2" t="n">
         <v>90</v>
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C91" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C91" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K91" s="14" t="inlineStr">
@@ -6700,65 +6700,61 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L91" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="3" t="inlineStr"/>
       <c r="N91" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="90" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="75" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C92" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C92" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
         </is>
       </c>
       <c r="K92" s="14" t="inlineStr">
@@ -6768,11 +6764,77 @@
       </c>
       <c r="L92" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M92" s="3" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="90" customHeight="1">
+      <c r="A93" s="2" t="n">
+        <v>92</v>
+      </c>
+      <c r="B93" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C93" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D93" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E93" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F93" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G93" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H93" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I93" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J93" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K93" s="14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L93" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M93" s="3" t="inlineStr"/>
+      <c r="N93" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -6839,10 +6901,10 @@
         <v>2</v>
       </c>
       <c r="D2" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3">
@@ -6915,10 +6977,10 @@
         <v>42</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>91</v>
+        <v>92</v>
       </c>
     </row>
   </sheetData>

--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -812,53 +812,53 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="45" customHeight="1">
+    <row r="4" ht="165" customHeight="1">
       <c r="A4" s="2" t="n">
         <v>3</v>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-4</t>
-        </is>
-      </c>
-      <c r="C4" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TV-RATING-CROSS-CHECK</t>
+        </is>
+      </c>
+      <c r="C4" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Signals / Cross-Check</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
+          <t>Validate (or zero out) the ±3 TV-rating tech-score bonus</t>
         </is>
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
+          <t>DISCOVERY 2026-05-11: TV-rating ±3 score bonus has been live in analysis.py:8627 for some time, modifying every BUY signal's technical pillar score. NO _validations entry, NO Wilson-CI, NO walk-forward justification for the ±3 magnitude. Worse: tv_rating was never captured on the 689 closed trades in picks_history or 1,301 signal_log entries — retroactive validation is impossible. Violates Principle 1 (n&lt;30 refusal) + Principle 7 (no knob-tweaking without evidence).</t>
         </is>
       </c>
       <c r="G4" s="5" t="inlineStr">
         <is>
-          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
+          <t>Phase 1 (SHIPPED 2026-05-11): (a) tv_bonus zeroed in analysis.py:8627 — score no longer mutated; (b) tv_recommendation + tv_rec_value + buy/sell/neutral counts now logged per signal in signal_tracker.log_signals() so prospective evidence accumulates; (c) tv_rating still surfaced in tech['details'] as INFORMATIONAL only — no score impact. Phase 2 (PENDING n&gt;=30, est. 6-12 weeks): run Wilson-LB(BUY|TV STRONG_BUY) vs Wilson-LB(BUY) over the prospectively-logged signals. If the agreement-conditional Wilson-LB beats unconditional by a meaningful margin (&gt;=3pp), re-enable with a magnitude justified by the regression. If not, kill the cross-check permanently (Principle 4 falsification — do not retune, do not lower the threshold).</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1 min</t>
+          <t>Phase 1: hours (done). Phase 2: hours of analysis + calendar wait for n&gt;=30.</t>
         </is>
       </c>
       <c r="I4" s="5" t="inlineStr">
         <is>
-          <t>Win: -X lines.</t>
+          <t>Mechanism (Principle 2): TV rating is an independent server-side aggregation of ~26 indicators. Two independent technical aggregations may improve precision over our 5-pillar score alone. Falsification (Principle 4): if agreement-conditional Wilson-LB &lt;= unconditional after n&gt;=30, the cross-check has no edge — kill, don't retune. Risk of CURRENT state (Phase 1): we have been over-weighting TV-STRONG_BUY signals by +3 tech-pts with zero evidence; this could have systematically biased BUY selection. Capping at 0 removes that bias going forward but does not undo past trade selection bias.</t>
         </is>
       </c>
       <c r="J4" s="5" t="inlineStr">
         <is>
-          <t>Couples with OPS-1.</t>
+          <t>Default apply_to_score=false locked. Validation requires logged tv_rating on &gt;=30 CLOSED BUY trades (currently 0). Earliest Phase-2 validation window: ~6-12 weeks of scans from 2026-05-11. Pairs with the v2 dashboard TV sub-tab (infra/prototype/subtabs/tv/) which is iframe-only today. Do NOT add per-mode / per-regime elaboration until Phase 2 evidence justifies even the basic bonus.</t>
         </is>
       </c>
       <c r="K4" s="7" t="inlineStr">
@@ -870,17 +870,17 @@
       <c r="M4" s="3" t="inlineStr"/>
       <c r="N4" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="165" customHeight="1">
+          <t>Phase 1 smoke: run python3 swing_trade.py and confirm (1) tech['details']['tv_rating'] still appears in deep-dive output labeled 'informational — bonus disabled pending validation'; (2) signal_log.json entries for new scans contain tv_recommendation + tv_rec_value + buy/sell/neutral_count populated. Phase 2 trigger: when `python3 -c 'import json; print(sum(1 for r in json.load(open("data/signal_log.json")) if r.get("tv_recommendation") and r.get("result")))'` &gt;= 30, run the agreement-conditional Wilson-LB analysis.</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="45" customHeight="1">
       <c r="A5" s="2" t="n">
         <v>4</v>
       </c>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>TV-RATING-CROSS-CHECK</t>
+          <t>CLEAN-4</t>
         </is>
       </c>
       <c r="C5" s="9" t="inlineStr">
@@ -890,37 +890,37 @@
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>Signals / Cross-Check</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
-          <t>tradingview-ta cross-check rating as independent confirmation signal</t>
+          <t>scripts/migrate_role_capabilities.py — cleanup after 2026-05-16</t>
         </is>
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>TradingView publishes a server-computed Strong Buy/Buy/Neutral/Sell/Strong Sell rating per (symbol x timeframe), aggregated from ~26 indicators. Free unofficial library 'tradingview-ta' fetches it. Use as INFORMATIONAL second-opinion signal cross-checking the 5-pillar score. Default apply_to_score=false until Wilson-LB on agreement-conditional WR clears unconditional WR over n&gt;=30 closed trades. No new paid data license (constraint OK).</t>
+          <t>One-shot CapStudio backfill. Already run. Tied to OPS-1 cleanup window.</t>
         </is>
       </c>
       <c r="G5" s="5" t="inlineStr">
         <is>
-          <t>1) pip install tradingview-ta. 2) data_fetcher.get_tv_rating(ticker) returns {rating, buy_signals, sell_signals, neutral_signals, summary_score, ts} with 4h cache (matches existing news TTL discipline). 3) Add tv_rating field to last_bundle.json per-ticker payload. 4) Surface in v2 dashboard Overview sub-tab as 'TV Agrees / TV Disagrees / TV Neutral' tile next to verdict arc. 5) Log to data/signal_log.json per emit so Wilson-CI agreement-conditional WR can be computed offline. 6) Backtest hook: compute Wilson-LB(BUY | TV agrees) vs Wilson-LB(BUY) over 250d. 7) Only flip apply_to_score=true after walk-forward shows lift across regimes. 8) Failure-mode: TV endpoint 500 -&gt; tv_rating=null, scanner continues, log 'tv_rating_unavailable' counter.</t>
+          <t>Delete during OPS-1 cleanup pass after 2026-05-16.</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>hours</t>
+          <t>1 min</t>
         </is>
       </c>
       <c r="I5" s="5" t="inlineStr">
         <is>
-          <t>Mechanism (Principle 2): TV rating is a server-side weighted aggregate of ~26 indicators — an independent technical signal (different weighting than ours). Two independent confirmations &gt; one. Falsification (Principle 4): if agreement-conditional Wilson-LB after n&gt;=30 doesn t beat unconditional Wilson-LB, kill the cross-check. Risk: TV unofficial endpoints break ~2-4x/year; needs null-safe failure path. No new paid data license (hard constraint OK).</t>
+          <t>Win: -X lines.</t>
         </is>
       </c>
       <c r="J5" s="5" t="inlineStr">
         <is>
-          <t>Default apply_to_score=false per tier1_signals convention. Cache 4h TTL, well under TV daily update cadence. Pairs naturally with the existing TV sub-tab (infra/prototype/subtabs/tv/) which today is iframe-only - this is the data backbone for it. Catalyst-tier breakout in backtest: TV agreement may help T1/T2 more than pure technicals.</t>
+          <t>Couples with OPS-1.</t>
         </is>
       </c>
       <c r="K5" s="7" t="inlineStr">
@@ -932,7 +932,7 @@
       <c r="M5" s="3" t="inlineStr"/>
       <c r="N5" s="8" t="inlineStr">
         <is>
-          <t>Smoke: python3 -c "from data_fetcher import get_tv_rating; print(get_tv_rating(NVDA))" returns dict. Cache: second call within 4h is cache hit. Failure: simulate TV 500 -&gt; scanner continues, ticker payload tv_rating=null. Backtest: python3 backtest.py --days 250 prints Wilson-LB(BUY|TV agrees) vs Wilson-LB(BUY). Gate: apply_to_score=false stays locked until n&gt;=30 with positive lift across at least 2 regimes.</t>
+          <t>(test instructions to be added when shipped)</t>
         </is>
       </c>
     </row>
@@ -6898,10 +6898,10 @@
         <v>0</v>
       </c>
       <c r="C2" s="17" t="n">
+        <v>3</v>
+      </c>
+      <c r="D2" s="17" t="n">
         <v>2</v>
-      </c>
-      <c r="D2" s="17" t="n">
-        <v>3</v>
       </c>
       <c r="E2" s="17" t="n">
         <v>5</v>
@@ -6974,10 +6974,10 @@
         <v>26</v>
       </c>
       <c r="C6" s="21" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" s="21" t="n">
         <v>92</v>

--- a/cache/open_items_2026-05-11.xlsx
+++ b/cache/open_items_2026-05-11.xlsx
@@ -597,7 +597,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N93"/>
+  <dimension ref="A1:N94"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="4" customWidth="1" min="1" max="1"/>
@@ -942,7 +942,7 @@
       </c>
       <c r="B6" s="3" t="inlineStr">
         <is>
-          <t>STRUCT-TARGETS-PHASE2</t>
+          <t>ENTRY-Q-AB</t>
         </is>
       </c>
       <c r="C6" s="9" t="inlineStr">
@@ -952,39 +952,27 @@
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Targets</t>
+          <t>Strategy / Gates</t>
         </is>
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
+          <t>Regime-conditional entry_quality A/B</t>
         </is>
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
+          <t>Test relaxing entry_quality EXTENDED/MISSED to caveat-only in risk_on_choppy regime. Evidence (n=257 EXTENDED PF 1.63, n=179 MISSED PF 2.89 in choppy) suggests gate is upside-down for that regime, but selection bias + market-cycle asymmetry concerns warrant explicit A/B before promoting to default.</t>
         </is>
       </c>
       <c r="G6" s="5" t="inlineStr">
         <is>
-          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>1 day + backtest</t>
-        </is>
-      </c>
-      <c r="I6" s="5" t="inlineStr">
-        <is>
-          <t>High win potential, medium risk</t>
-        </is>
-      </c>
-      <c r="J6" s="5" t="inlineStr">
-        <is>
-          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
-        </is>
-      </c>
+          <t>Add config flag regime4_thresholds.risk_on_choppy.entry_quality_caveat_only (default false). Modify decision_engine to honor it. Run 30 days control + 30 days test. Compare WR/PF stratified by entry_quality band. Promote if test PF &gt; control by &gt;=0.3 with n&gt;=30 per band.</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="5" t="inlineStr"/>
+      <c r="J6" s="5" t="inlineStr"/>
       <c r="K6" s="7" t="inlineStr">
         <is>
           <t>OPEN</t>
@@ -992,11 +980,7 @@
       </c>
       <c r="L6" s="2" t="inlineStr"/>
       <c r="M6" s="3" t="inlineStr"/>
-      <c r="N6" s="8" t="inlineStr">
-        <is>
-          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
-        </is>
-      </c>
+      <c r="N6" s="8" t="inlineStr"/>
     </row>
     <row r="7" ht="75" customHeight="1">
       <c r="A7" s="2" t="n">
@@ -1004,77 +988,69 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>K6</t>
-        </is>
-      </c>
-      <c r="C7" s="10" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>STRUCT-TARGETS-PHASE2</t>
+        </is>
+      </c>
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>Architecture</t>
+          <t>Strategy / Targets</t>
         </is>
       </c>
       <c r="E7" s="6" t="inlineStr">
         <is>
-          <t>Single canonical trade plan object — every tab reads from one source</t>
+          <t>Structural targets Phase 2 — engine uses them as T1/T2</t>
         </is>
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
+          <t>Phase 1 (shipped 2026-05-10): structural target sources (fractal, fib, EW Wave-3) display on Plan tab as informational. Phase 2: actually use these as T1/T2 instead of ATR-multiple targets. Needs per-source x regime evidence (&gt;=30 trades each).</t>
         </is>
       </c>
       <c r="G7" s="5" t="inlineStr">
         <is>
-          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+          <t>Add config flag target_source = atr_multiple | structural. When structural, T1 = nearest_above with R:R&gt;=3 from {fractal_high, fib_127, EW_T1}. Fall back to ATR if R:R floor not met. Backtest side-by-side with current ATR-multiple.</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1 day + backtest</t>
         </is>
       </c>
       <c r="I7" s="5" t="inlineStr">
         <is>
-          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+          <t>High win potential, medium risk</t>
         </is>
       </c>
       <c r="J7" s="5" t="inlineStr">
         <is>
-          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
-        </is>
-      </c>
-      <c r="K7" s="11" t="inlineStr">
-        <is>
-          <t>DONE</t>
-        </is>
-      </c>
-      <c r="L7" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M7" s="3" t="inlineStr">
-        <is>
-          <t>2c9b9f339</t>
-        </is>
-      </c>
+          <t>Awaiting evidence. Phase 1 currently just populates display field; need 3-4 weeks of trade data with target_sources captured before Phase 2 is decidable.</t>
+        </is>
+      </c>
+      <c r="K7" s="7" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr"/>
+      <c r="M7" s="3" t="inlineStr"/>
       <c r="N7" s="8" t="inlineStr">
         <is>
-          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1">
+          <t>Run backtest with target_source=structural and target_source=atr_multiple on same window. Compare PF/WR/avg_win.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="75" customHeight="1">
       <c r="A8" s="2" t="n">
         <v>7</v>
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>B3-WEEKLY-FIX</t>
+          <t>K6</t>
         </is>
       </c>
       <c r="C8" s="10" t="inlineStr">
@@ -1084,29 +1060,37 @@
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Bug Fix</t>
+          <t>Architecture</t>
         </is>
       </c>
       <c r="E8" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
+          <t>Single canonical trade plan object — every tab reads from one source</t>
         </is>
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
+          <t>Different dashboard tabs (Plan, Overview, Technicals, Models) computed their own derived values from raw signal data — drift risk, inconsistent UI numbers.</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr">
         <is>
-          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr"/>
-      <c r="I8" s="5" t="inlineStr"/>
+          <t>New canonical_trade_plan.py — one dataclass: TradeZone / RiskMetrics / StatisticalContext / RegimeContext / CatalystContext / SetupAttribution / GateResults. swing_trade.py attaches it per signal. Live Wilson-CI lookup from signal_log per setup×regime. Mechanism hypothesis per setup family.</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I8" s="5" t="inlineStr">
+        <is>
+          <t>Win: tabs converge on one truth; future tabs bind to dataclass fields.</t>
+        </is>
+      </c>
       <c r="J8" s="5" t="inlineStr">
         <is>
-          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+          <t>402 LOC. Future tabs MUST bind to canonical fields, not recompute.</t>
         </is>
       </c>
       <c r="K8" s="11" t="inlineStr">
@@ -1116,27 +1100,27 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M8" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>2c9b9f339</t>
         </is>
       </c>
       <c r="N8" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="75" customHeight="1">
+          <t>Open infra/prototype/elite-detail.html for any ticker → Plan, Thesis, SMC, Models, Overview tabs all show IDENTICAL entry/stop/T1/T2 values. No mismatches across tabs.</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="90" customHeight="1">
       <c r="A9" s="2" t="n">
         <v>8</v>
       </c>
       <c r="B9" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F-BT</t>
+          <t>B3-WEEKLY-FIX</t>
         </is>
       </c>
       <c r="C9" s="10" t="inlineStr">
@@ -1146,27 +1130,31 @@
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>Backtest Parity</t>
+          <t>Backtest / Bug Fix</t>
         </is>
       </c>
       <c r="E9" s="6" t="inlineStr">
         <is>
-          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
+          <t>Backtest must build weekly_df from daily for weekly_bull computation</t>
         </is>
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
+          <t>Backtest harness was passing only the daily df to the engine, but weekly_bull (a hard gate in trend-continuation setups) requires resampled weekly bars. Without it, every backtest signal fell through the weekly_bull gate as 'unknown' which the engine treated as fail. Effective on-paper effect: 0 BUYs across many backtests despite valid signals in the daily series.</t>
         </is>
       </c>
       <c r="G9" s="5" t="inlineStr">
         <is>
-          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+          <t>Build weekly_df via df.resample('W').agg({open: first, high: max, low: min, close: last, volume: sum}) before each pre-trade-gate call. Pass alongside daily.</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr"/>
       <c r="I9" s="5" t="inlineStr"/>
-      <c r="J9" s="5" t="inlineStr"/>
+      <c r="J9" s="5" t="inlineStr">
+        <is>
+          <t>P0 because this silently invalidated every Trend-Continuation backtest signal in the 750d simulations Saturday. Found during Q1-step5 0-BUY investigation — daily df alone made the engine think every TC signal failed weekly_bull as "unknown".</t>
+        </is>
+      </c>
       <c r="K9" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1179,18 +1167,22 @@
       </c>
       <c r="M9" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N9" s="8" t="inlineStr"/>
-    </row>
-    <row r="10" ht="45" customHeight="1">
+          <t>985cd182b</t>
+        </is>
+      </c>
+      <c r="N9" s="8" t="inlineStr">
+        <is>
+          <t>1. python3 backtest.py --window 250d --min-score 65 → confirm BUYs &gt; 0. 2. Compare cache/portfolio_backtest_250d_min65_h5_20260510_*.json before/after fix → expected: pre-fix had 0 trades on Trend-Continuation family; post-fix has them. 3. grep -E "weekly_df|weekly_bull" backtest.py to verify the resample call is in the inner loop.</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="75" customHeight="1">
       <c r="A10" s="2" t="n">
         <v>9</v>
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>P0-WEEKLY</t>
+          <t>VARIANT-F-BT</t>
         </is>
       </c>
       <c r="C10" s="10" t="inlineStr">
@@ -1200,39 +1192,27 @@
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest Parity</t>
         </is>
       </c>
       <c r="E10" s="6" t="inlineStr">
         <is>
-          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
+          <t>Variant F regime-conditional multipliers not wired into backtest path</t>
         </is>
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
+          <t>backtest.py:418 uses tracker.get_setup_weight_multiplier (reading picks_history) but never consults config.setup_score_multiplier_by_regime. So Variant F's TC×bull=0.0 kill never applied in backtest — explains why 105 TC bull trades persisted in 250d backtest despite live kill in config.</t>
         </is>
       </c>
       <c r="G10" s="5" t="inlineStr">
         <is>
-          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>20 min</t>
-        </is>
-      </c>
-      <c r="I10" s="5" t="inlineStr">
-        <is>
-          <t>CRITICAL — system was unable to backtest</t>
-        </is>
-      </c>
-      <c r="J10" s="5" t="inlineStr">
-        <is>
-          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
-        </is>
-      </c>
+          <t>Add Variant F lookup at backtest.py:442 mirroring analysis.py:8867 logic. Same demotion gate (n&gt;=30 + wr_lb&lt;0.30). Comment cross-reference live path.</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr"/>
+      <c r="I10" s="5" t="inlineStr"/>
+      <c r="J10" s="5" t="inlineStr"/>
       <c r="K10" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1245,22 +1225,18 @@
       </c>
       <c r="M10" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
-        </is>
-      </c>
-      <c r="N10" s="8" t="inlineStr">
-        <is>
-          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="90" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N10" s="8" t="inlineStr"/>
+    </row>
+    <row r="11" ht="45" customHeight="1">
       <c r="A11" s="2" t="n">
         <v>10</v>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>OPERATING-MINDSET</t>
+          <t>P0-WEEKLY</t>
         </is>
       </c>
       <c r="C11" s="10" t="inlineStr">
@@ -1270,37 +1246,37 @@
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E11" s="6" t="inlineStr">
         <is>
-          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
+          <t>Backtest must build weekly_df from daily (0-BUYs root cause)</t>
         </is>
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
+          <t>GATE-1 produced 0 BUYs because backtest _score_as_of did not pass weekly_df. _weekly_ema_alignment(None) returned bullish=False; setup_gates demoted every BUY.</t>
         </is>
       </c>
       <c r="G11" s="5" t="inlineStr">
         <is>
-          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
+          <t>Resample daily OHLCV to W-FRI inside _score_as_of. Pass weekly_df to score_technicals. Leakage-free.</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I11" s="5" t="inlineStr">
         <is>
-          <t>Win: codified discipline survives session/agent boundaries.</t>
+          <t>CRITICAL — system was unable to backtest</t>
         </is>
       </c>
       <c r="J11" s="5" t="inlineStr">
         <is>
-          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
+          <t>Validated: --smoke produced 5 BUYs in 5d, PF 7.74.</t>
         </is>
       </c>
       <c r="K11" s="11" t="inlineStr">
@@ -1315,22 +1291,22 @@
       </c>
       <c r="M11" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N11" s="8" t="inlineStr">
         <is>
-          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="105" customHeight="1">
+          <t>python3 backtest.py --smoke - cache/portfolio_backtest.json total_trades &gt; 0.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="90" customHeight="1">
       <c r="A12" s="2" t="n">
         <v>11</v>
       </c>
       <c r="B12" s="3" t="inlineStr">
         <is>
-          <t>A6</t>
+          <t>OPERATING-MINDSET</t>
         </is>
       </c>
       <c r="C12" s="10" t="inlineStr">
@@ -1340,22 +1316,22 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>ML / Data Logging</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
         <is>
-          <t>Entry-time feature logger in swing_trade.py</t>
+          <t>20-principle hedge-fund-analyst Operating Mindset in CLAUDE.md</t>
         </is>
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
+          <t>User's standing directive: every decision in this codebase should reflect senior hedge-fund quant analyst discipline, not generic software engineering. Without explicit codification, the principles drift.</t>
         </is>
       </c>
       <c r="G12" s="5" t="inlineStr">
         <is>
-          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
+          <t>New top-level OPERATING MINDSET section in CLAUDE.md before Path Layout. 20 principles in 4 categories (Foundational discipline / Capital preservation / Information edge / Behavioral discipline / Realism) + enforcement table mapping each principle to its code location + push-back examples for when user instruction conflicts.</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -1365,12 +1341,12 @@
       </c>
       <c r="I12" s="5" t="inlineStr">
         <is>
-          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
+          <t>Win: codified discipline survives session/agent boundaries.</t>
         </is>
       </c>
       <c r="J12" s="5" t="inlineStr">
         <is>
-          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
+          <t>Includes 8 original + 12 added principles. Auto-loaded on every Claude interaction in this dir.</t>
         </is>
       </c>
       <c r="K12" s="11" t="inlineStr">
@@ -1380,27 +1356,27 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M12" s="3" t="inlineStr">
         <is>
-          <t>0574c60d4</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N12" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="45" customHeight="1">
+          <t>head -200 CLAUDE.md → 20 numbered principles in 5 categories, enforcement summary table, push-back guidance. New CLAUDE sessions auto-load this.</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="105" customHeight="1">
       <c r="A13" s="2" t="n">
         <v>12</v>
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>IPAD-3</t>
+          <t>A6</t>
         </is>
       </c>
       <c r="C13" s="10" t="inlineStr">
@@ -1410,37 +1386,37 @@
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>ML / Data Logging</t>
         </is>
       </c>
       <c r="E13" s="6" t="inlineStr">
         <is>
-          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
+          <t>Entry-time feature logger in swing_trade.py</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
+          <t>ML mover-predictor v2 result (AUC 0.546) was a method failure not strategy failure — v1 had leakage, v2 was missing entry-time market features. Need to capture them going forward for catalyst-conditional ML.</t>
         </is>
       </c>
       <c r="G13" s="5" t="inlineStr">
         <is>
-          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+          <t>Adds 30 entry-time fields to every signal_log entry, all prefixed `ef_`. Categories: Volume (rvol_5d/20d, atr_pct, atr_expansion, obv_slope, mfi, cmf), Price (dist_52w_high/20d_high, dist_ema8/21/50/200_pct), Momentum (rsi14, macd_hist, stoch_rsi), Squeeze, Catalyst (tier1_total_pts, has_pead, has_uoa_*), Options (iv_rank, put_call_ratio), Smart $$ (insider_score), News (sentiment, count_7d), Zacks/Earn.</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I13" s="5" t="inlineStr">
         <is>
-          <t>Low / Required</t>
+          <t>Win: ~150-300 trades over 30 days → enough for catalyst-conditional ML retraining.</t>
         </is>
       </c>
       <c r="J13" s="5" t="inlineStr">
         <is>
-          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+          <t>Pure additive — Wilson CI gates / hedge_fund_report / drift checker unaffected.</t>
         </is>
       </c>
       <c r="K13" s="11" t="inlineStr">
@@ -1450,27 +1426,27 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M13" s="3" t="inlineStr">
         <is>
-          <t>b0e5ef6a1</t>
+          <t>0574c60d4</t>
         </is>
       </c>
       <c r="N13" s="8" t="inlineStr">
         <is>
-          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="120" customHeight="1">
+          <t>python3 swing_trade.py → check newly-written entries in data/signal_log.json have ef_volume_surge_5d, ef_atr_pct, ef_rsi14, ef_has_pead, etc. fields populated.</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="45" customHeight="1">
       <c r="A14" s="2" t="n">
         <v>13</v>
       </c>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>ALPACA-SYNC</t>
+          <t>IPAD-3</t>
         </is>
       </c>
       <c r="C14" s="10" t="inlineStr">
@@ -1480,27 +1456,39 @@
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>Paper Trading/State Sync</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
         <is>
-          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
+          <t>iPad shell hot fix — verdict/stage/score field mismatch</t>
         </is>
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
+          <t>Phase 1 release showed 0 rows in Scanner + Elite tabs. Bundle uses stage not verdict; elite_picks shape is nested.</t>
         </is>
       </c>
       <c r="G14" s="5" t="inlineStr">
         <is>
-          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr"/>
-      <c r="I14" s="5" t="inlineStr"/>
-      <c r="J14" s="5" t="inlineStr"/>
+          <t>3 fixes in ipad.js: filter falls through to r.stage; elite tab aggregates Swing.BUY+WATCH+SHORT; buildRow score fallback.</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>20 min</t>
+        </is>
+      </c>
+      <c r="I14" s="5" t="inlineStr">
+        <is>
+          <t>Low / Required</t>
+        </is>
+      </c>
+      <c r="J14" s="5" t="inlineStr">
+        <is>
+          <t>Verified 0-&gt;61 Scanner rows, 0-&gt;5 Elite rows.</t>
+        </is>
+      </c>
       <c r="K14" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1513,18 +1501,22 @@
       </c>
       <c r="M14" s="3" t="inlineStr">
         <is>
-          <t>f26e1deb2</t>
-        </is>
-      </c>
-      <c r="N14" s="8" t="inlineStr"/>
-    </row>
-    <row r="15" ht="60" customHeight="1">
+          <t>b0e5ef6a1</t>
+        </is>
+      </c>
+      <c r="N14" s="8" t="inlineStr">
+        <is>
+          <t>Hard-refresh iPad shell. Scanner shows 60+ WATCH rows; Elite shows 5 picks.</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="120" customHeight="1">
       <c r="A15" s="2" t="n">
         <v>14</v>
       </c>
       <c r="B15" s="3" t="inlineStr">
         <is>
-          <t>Q1-step1</t>
+          <t>ALPACA-SYNC</t>
         </is>
       </c>
       <c r="C15" s="10" t="inlineStr">
@@ -1534,39 +1526,27 @@
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Paper Trading/State Sync</t>
         </is>
       </c>
       <c r="E15" s="6" t="inlineStr">
         <is>
-          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
+          <t>Local state diverges from Alpaca paper account — dashboards and feedback loops read stale 'no positions' while Alpaca has real fills</t>
         </is>
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
+          <t>portfolio_state.json + SQLite positions/trades tables report 0 rows. Alpaca has 28 filled orders since 2026-04-30 (14 BUY + 14 SELL = 14 round-trips, all stopped out 05-05 to 05-07, total paper loss ~$1,612). Effect: (a) dashboard shows wrong state, (b) portfolio_tracker can't attribute P&amp;L back to setup x regime, (c) kelly_size.drawdown_mult (commit 74cb3b208) reads local equity_curve which has no actual data → multiplier silently neutral, (d) no learning loop from actual paper losses to setup multipliers.</t>
         </is>
       </c>
       <c r="G15" s="5" t="inlineStr">
         <is>
-          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
-        </is>
-      </c>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>5 min</t>
-        </is>
-      </c>
-      <c r="I15" s="5" t="inlineStr">
-        <is>
-          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
-        </is>
-      </c>
-      <c r="J15" s="5" t="inlineStr">
-        <is>
-          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
-        </is>
-      </c>
+          <t>Build alpaca_sync.py with sync_alpaca_to_local(). v1: pull account + positions, write portfolio_state.json + SQLite positions table. v2: filled-order reconciliation, pick attribution via cache/orders.jsonl, equity_curve snapshot. Wire as Step 0 of swing_trade.py (every scan) + executor.py post-submit + standalone scripts/sync_alpaca.py for ad-hoc runs.</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="5" t="inlineStr"/>
+      <c r="J15" s="5" t="inlineStr"/>
       <c r="K15" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -1574,27 +1554,23 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M15" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
-        </is>
-      </c>
-      <c r="N15" s="8" t="inlineStr">
-        <is>
-          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="45" customHeight="1">
+          <t>f26e1deb2</t>
+        </is>
+      </c>
+      <c r="N15" s="8" t="inlineStr"/>
+    </row>
+    <row r="16" ht="60" customHeight="1">
       <c r="A16" s="2" t="n">
         <v>15</v>
       </c>
       <c r="B16" s="3" t="inlineStr">
         <is>
-          <t>Q1-step2</t>
+          <t>Q1-step1</t>
         </is>
       </c>
       <c r="C16" s="10" t="inlineStr">
@@ -1609,32 +1585,32 @@
       </c>
       <c r="E16" s="6" t="inlineStr">
         <is>
-          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
+          <t>Re-derive Saturday's empirical analysis on n=384 750d backtest</t>
         </is>
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
+          <t>Saturday's session changed live config based on agent-summarized stats. Agent's Fix 2 was actively wrong; Fix 3 had n=1 evidence in post-kill subset. Confirm Saturday's reads before any further changes.</t>
         </is>
       </c>
       <c r="G16" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
+          <t>Run inline Python script in SESSION_HANDOFF section 3 against cache/portfolio_backtest_750d_20260509_100501.json. Reproduce 'TC killed', 'TC + score≥80', score-band table 65-100, per-setup table at score≥80.</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>2 min</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I16" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
+          <t>Risk: none. Verify: TC killed PF 0.86, 80-85 band PF 1.72, VCP n=1.</t>
         </is>
       </c>
       <c r="J16" s="5" t="inlineStr">
         <is>
-          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
+          <t>Gate for everything below — do not proceed if numbers diverge. · verified inline against cache/portfolio_backtest_750d_20260509_100501.json: TC@score&gt;=80 PF 0.54, VCP@score&gt;=80 n=1, Near-VCP@score&gt;=80 PF 1.05, 90-100 band PF 0.55</t>
         </is>
       </c>
       <c r="K16" s="11" t="inlineStr">
@@ -1654,7 +1630,7 @@
       </c>
       <c r="N16" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+          <t>python3 -c 'import json; d=json.load(open("cache/portfolio_backtest_750d_20260509_100501.json")); print(d["profit_factor"])' → 0.70 confirmed.</t>
         </is>
       </c>
     </row>
@@ -1664,7 +1640,7 @@
       </c>
       <c r="B17" s="3" t="inlineStr">
         <is>
-          <t>Q1-step3</t>
+          <t>Q1-step2</t>
         </is>
       </c>
       <c r="C17" s="10" t="inlineStr">
@@ -1679,17 +1655,17 @@
       </c>
       <c r="E17" s="6" t="inlineStr">
         <is>
-          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
+          <t>Revert Fix 3 — VCP Breakout multiplier 1.2 → 0.0</t>
         </is>
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
+          <t>Saturday boosted VCP Breakout to 1.2× based on n=12 aggregate. Post-kill universe has only n=1 firing at score≥80, and it lost.</t>
         </is>
       </c>
       <c r="G17" s="5" t="inlineStr">
         <is>
-          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
+          <t>Edit config/config.json: setup_score_multiplier['VCP Breakout'] 1.2 → 0.0. Verify with git diff config/config.json.</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
@@ -1699,12 +1675,12 @@
       </c>
       <c r="I17" s="5" t="inlineStr">
         <is>
-          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
+          <t>Risk: LOW. Win: prevents Monday 1am scan from sizing into a setup with no real evidence.</t>
         </is>
       </c>
       <c r="J17" s="5" t="inlineStr">
         <is>
-          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
+          <t>Lesson: filter to 'what new config would have allowed' before extrapolating.</t>
         </is>
       </c>
       <c r="K17" s="11" t="inlineStr">
@@ -1724,17 +1700,17 @@
       </c>
       <c r="N17" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="60" customHeight="1">
+          <t>grep -A5 '"VCP Breakout"' config/config.json → setup_score_multiplier shows 0.0 (was 1.2). git diff confirms revert.</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="45" customHeight="1">
       <c r="A18" s="2" t="n">
         <v>17</v>
       </c>
       <c r="B18" s="3" t="inlineStr">
         <is>
-          <t>Q1-step4</t>
+          <t>Q1-step3</t>
         </is>
       </c>
       <c r="C18" s="10" t="inlineStr">
@@ -1749,32 +1725,32 @@
       </c>
       <c r="E18" s="6" t="inlineStr">
         <is>
-          <t>Run 250-day backtest to validate steps 2 + 3</t>
+          <t>Boost Near-VCP Breakout multiplier 0.7 → 1.0</t>
         </is>
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
+          <t>Post-kill universe at score≥80: Near-VCP Breakout n=50, PF 1.07 — workhorse currently demoted to 0.7×.</t>
         </is>
       </c>
       <c r="G18" s="5" t="inlineStr">
         <is>
-          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
+          <t>Edit config/config.json: setup_score_multiplier['Near-VCP Breakout'] 0.7 → 1.0. Verify next backtest.</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>~12 min wall-clock</t>
+          <t>2 min</t>
         </is>
       </c>
       <c r="I18" s="5" t="inlineStr">
         <is>
-          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
+          <t>Risk: LOW-MEDIUM. Win: lets proven workhorse pull full weight.</t>
         </is>
       </c>
       <c r="J18" s="5" t="inlineStr">
         <is>
-          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
+          <t>PF 1.07 has wide CI 0.85-1.30 OOS. Verify with Q1-step4 250d backtest.</t>
         </is>
       </c>
       <c r="K18" s="11" t="inlineStr">
@@ -1784,27 +1760,27 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M18" s="3" t="inlineStr">
         <is>
-          <t>985cd182b</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N18" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="180" customHeight="1">
+          <t>grep -A5 '"Near-VCP Breakout"' config/config.json → setup_score_multiplier shows 1.0 (was 0.7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="60" customHeight="1">
       <c r="A19" s="2" t="n">
         <v>18</v>
       </c>
       <c r="B19" s="3" t="inlineStr">
         <is>
-          <t>Q1-step5</t>
+          <t>Q1-step4</t>
         </is>
       </c>
       <c r="C19" s="10" t="inlineStr">
@@ -1819,32 +1795,32 @@
       </c>
       <c r="E19" s="6" t="inlineStr">
         <is>
-          <t>Run 750-day backtest to confirm if 250d passes</t>
+          <t>Run 250-day backtest to validate steps 2 + 3</t>
         </is>
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
+          <t>Need fast validation that config changes don't break things before committing 3 hours to full 750d.</t>
         </is>
       </c>
       <c r="G19" s="5" t="inlineStr">
         <is>
-          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
+          <t>python3 backtest.py --days 250 --hold 5 --min-score 65 --portfolio --equity 5000 --positions 4 --size-pct 0.25 &gt; cache/logs/backtest_250d_quant1_$(date +%Y%m%d_%H%M%S).log 2&gt;&amp;1 &amp;</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>~3 hours</t>
+          <t>~12 min wall-clock</t>
         </is>
       </c>
       <c r="I19" s="5" t="inlineStr">
         <is>
-          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
+          <t>Risk: none (offline). Verify: PF ≥ 1.0 to proceed.</t>
         </is>
       </c>
       <c r="J19" s="5" t="inlineStr">
         <is>
-          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
+          <t>PASSED smoke 5d (PF 7.74, WR 40%). Confirmed weekly_df fix unblocks BUYs.</t>
         </is>
       </c>
       <c r="K19" s="11" t="inlineStr">
@@ -1859,22 +1835,22 @@
       </c>
       <c r="M19" s="3" t="inlineStr">
         <is>
-          <t>985cd182b + run cache/portfolio_backtest_*</t>
+          <t>985cd182b</t>
         </is>
       </c>
       <c r="N19" s="8" t="inlineStr">
         <is>
-          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="180" customHeight="1">
       <c r="A20" s="2" t="n">
         <v>19</v>
       </c>
       <c r="B20" s="3" t="inlineStr">
         <is>
-          <t>Q1-step6</t>
+          <t>Q1-step5</t>
         </is>
       </c>
       <c r="C20" s="10" t="inlineStr">
@@ -1889,32 +1865,32 @@
       </c>
       <c r="E20" s="6" t="inlineStr">
         <is>
-          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
+          <t>Run 750-day backtest to confirm if 250d passes</t>
         </is>
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
+          <t>Real evidence comes from full 750d window — same methodology that produced Saturday's headline n=384 result.</t>
         </is>
       </c>
       <c r="G20" s="5" t="inlineStr">
         <is>
-          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
+          <t>Same backtest command but --days 750. Run during Sunday daytime (3hr runtime).</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>30 min + backtest</t>
+          <t>~3 hours</t>
         </is>
       </c>
       <c r="I20" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
+          <t>Risk: none. Verify: PF, WR, drawdown all directionally improved vs Saturday's PF 0.70.</t>
         </is>
       </c>
       <c r="J20" s="5" t="inlineStr">
         <is>
-          <t>Skip if step 5 already shows PF healthy.</t>
+          <t>FAILED acceptance bar over 12 months (n=142): PF 0.95 / WR 31.7% / MaxDD 32.1% / -6.3% return / Sharpe -0.17. avg_win 6.08% vs avg_loss -2.96% (asymmetry 2.05× needs ~2.5× for PF 1.4 at this WR). System produces actionable trades but too many small losers (97/142). DO NOT activate paper trading on this config. Next: try tighter entry quality, wider stops, higher score floor — need user decision on which lever first. / FAILED ACCEPTANCE BAR (2026-05-10): 250d backtest produced 0 BUYs across 3+ simulated months. Q1 multipliers + threshold combo demoted every qualifying signal. Sibling commit a18282d28 (Q1-step5 250d FINAL) logged the failure; recovery path was Variant F (commit f0a66543e) — regime-conditional TC kill ONLY in bull regime (not all 4 regimes). 250d Variant F backtest pending verification before declaring real fix.</t>
         </is>
       </c>
       <c r="K20" s="11" t="inlineStr">
@@ -1929,22 +1905,22 @@
       </c>
       <c r="M20" s="3" t="inlineStr">
         <is>
-          <t>f47958fc9</t>
+          <t>985cd182b + run cache/portfolio_backtest_*</t>
         </is>
       </c>
       <c r="N20" s="8" t="inlineStr">
         <is>
-          <t>(test instructions to be added when shipped)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="90" customHeight="1">
+          <t>cat cache/portfolio_backtest.json → check profit_factor, win_rate, max_drawdown_pct fields. Open cache/backtest_report_latest.html for per-setup attribution.</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="45" customHeight="1">
       <c r="A21" s="2" t="n">
         <v>20</v>
       </c>
       <c r="B21" s="3" t="inlineStr">
         <is>
-          <t>B2</t>
+          <t>Q1-step6</t>
         </is>
       </c>
       <c r="C21" s="10" t="inlineStr">
@@ -1954,37 +1930,37 @@
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>Quant / Backtest infra</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E21" s="6" t="inlineStr">
         <is>
-          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
+          <t>Consider buy_max_score: 90 in regime4_thresholds blocks</t>
         </is>
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
+          <t>90+ score band is anti-predictive: n=19, PF 0.32 in post-kill subset.</t>
         </is>
       </c>
       <c r="G21" s="5" t="inlineStr">
         <is>
-          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
+          <t>Add buy_max_score: 90 to each of 4 regime blocks under regime4_thresholds. Re-run final backtest.</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min + backtest</t>
         </is>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic decomposition possible on next 750d backtest.</t>
+          <t>Risk: MEDIUM (small sample n=19). Win: removes -67% PF drag if real.</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
         <is>
-          <t>Pure additive. Does not affect existing analysis.</t>
+          <t>Skip if step 5 already shows PF healthy.</t>
         </is>
       </c>
       <c r="K21" s="11" t="inlineStr">
@@ -1994,27 +1970,27 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M21" s="3" t="inlineStr">
         <is>
-          <t>f35f0c124</t>
+          <t>f47958fc9</t>
         </is>
       </c>
       <c r="N21" s="8" t="inlineStr">
         <is>
-          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="45" customHeight="1">
+          <t>(test instructions to be added when shipped)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="90" customHeight="1">
       <c r="A22" s="2" t="n">
         <v>21</v>
       </c>
       <c r="B22" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix1</t>
+          <t>B2</t>
         </is>
       </c>
       <c r="C22" s="10" t="inlineStr">
@@ -2024,22 +2000,22 @@
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>Quant / Config</t>
+          <t>Quant / Backtest infra</t>
         </is>
       </c>
       <c r="E22" s="6" t="inlineStr">
         <is>
-          <t>Trend Continuation killed (Fix 1)</t>
+          <t>Enrich backtest trade records with regime/entry_quality/sector/MAE/MFE</t>
         </is>
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
+          <t>750d backtest trade records had only ticker/dates/prices/pnl/setup_type/score/verdict/exit_reason — making per-strategy attribution impossible per A5 finding.</t>
         </is>
       </c>
       <c r="G22" s="5" t="inlineStr">
         <is>
-          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
+          <t>backtest.py:1668 captures regime/entry_quality/setup_family/catalyst_tier/conviction_tier/sector/industry/rs_rank/tier1_total_pts/has_pead/has_uoa_calls/insider_cluster_30d/iv_rank/earn_days at entry. Closed_trade record propagates all + computes mae_pct/mfe_pct from highest_price/lowest_price tracked over hold period.</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
@@ -2049,12 +2025,12 @@
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
+          <t>Win: forensic decomposition possible on next 750d backtest.</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
         <is>
-          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
+          <t>Pure additive. Does not affect existing analysis.</t>
         </is>
       </c>
       <c r="K22" s="11" t="inlineStr">
@@ -2069,12 +2045,12 @@
       </c>
       <c r="M22" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8 + 6ceca2d18</t>
+          <t>f35f0c124</t>
         </is>
       </c>
       <c r="N22" s="8" t="inlineStr">
         <is>
-          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+          <t>Run a fresh backtest (after current finishes). Open cache/portfolio_backtest_*.json → trade records contain regime, entry_quality, sector, mae_pct, mfe_pct fields.</t>
         </is>
       </c>
     </row>
@@ -2084,7 +2060,7 @@
       </c>
       <c r="B23" s="3" t="inlineStr">
         <is>
-          <t>Q1-Fix3</t>
+          <t>Q1-Fix1</t>
         </is>
       </c>
       <c r="C23" s="10" t="inlineStr">
@@ -2099,32 +2075,32 @@
       </c>
       <c r="E23" s="6" t="inlineStr">
         <is>
-          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
+          <t>Trend Continuation killed (Fix 1)</t>
         </is>
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
+          <t>750d backtest: Trend Continuation 264/384 trades (69%) at PF 0.65, Wilson LB 19.5% — single biggest portfolio drain.</t>
         </is>
       </c>
       <c r="G23" s="5" t="inlineStr">
         <is>
-          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+          <t>config/config.json: setup_score_multiplier['Trend Continuation'] 0.7→0.0 + static_setup_kill_list dict entry (n=264, wr_lb=0.195, source=static).</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>shipped (revert candidate)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+          <t>Win: prevents biggest documented setup drag on Monday 1am scan.</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
         <is>
-          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
+          <t>Bug fix in 6ceca2d18: bare-string kill_list entries silently rejected — required dict format.</t>
         </is>
       </c>
       <c r="K23" s="11" t="inlineStr">
@@ -2139,22 +2115,22 @@
       </c>
       <c r="M23" s="3" t="inlineStr">
         <is>
-          <t>fc76c9ec8</t>
+          <t>fc76c9ec8 + 6ceca2d18</t>
         </is>
       </c>
       <c r="N23" s="8" t="inlineStr">
         <is>
-          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="105" customHeight="1">
+          <t>grep -A5 'static_setup_kill_list' config/config.json → 'Trend Continuation' present in dict format with n=264 wr_lb=0.195.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="45" customHeight="1">
       <c r="A24" s="2" t="n">
         <v>23</v>
       </c>
       <c r="B24" s="3" t="inlineStr">
         <is>
-          <t>VAR-F</t>
+          <t>Q1-Fix3</t>
         </is>
       </c>
       <c r="C24" s="10" t="inlineStr">
@@ -2164,29 +2140,37 @@
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>Quant / Recovery</t>
+          <t>Quant / Config</t>
         </is>
       </c>
       <c r="E24" s="6" t="inlineStr">
         <is>
-          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
+          <t>VCP Breakout multiplier 0.0 → 1.2 (Fix 3) — needs revert</t>
         </is>
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
+          <t>Comment in config said VCP Breakout was 'removed from kill list' but value remained 0.0. Restored to 1.2 based on n=12 PF 1.79 aggregate.</t>
         </is>
       </c>
       <c r="G24" s="5" t="inlineStr">
         <is>
-          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
-        </is>
-      </c>
-      <c r="H24" s="2" t="inlineStr"/>
-      <c r="I24" s="5" t="inlineStr"/>
+          <t>config['setup_score_multiplier']['VCP Breakout']: 0.0 → 1.2.</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>shipped (revert candidate)</t>
+        </is>
+      </c>
+      <c r="I24" s="5" t="inlineStr">
+        <is>
+          <t>Risk: post-kill subset has only n=1 evidence — not real evidence. See Q1-step2.</t>
+        </is>
+      </c>
       <c r="J24" s="5" t="inlineStr">
         <is>
-          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
+          <t>REVERT CANDIDATE. Sunday plan step 2: revert to 0.0.</t>
         </is>
       </c>
       <c r="K24" s="11" t="inlineStr">
@@ -2196,27 +2180,27 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M24" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e + 363984181</t>
+          <t>fc76c9ec8</t>
         </is>
       </c>
       <c r="N24" s="8" t="inlineStr">
         <is>
-          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="60" customHeight="1">
+          <t>Same as Q1-step2 verification — VCP Breakout multiplier should NOW be 0.0 (reverted from Saturday's 1.2).</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="105" customHeight="1">
       <c r="A25" s="2" t="n">
         <v>24</v>
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>K3</t>
+          <t>VAR-F</t>
         </is>
       </c>
       <c r="C25" s="10" t="inlineStr">
@@ -2226,37 +2210,29 @@
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Recovery</t>
         </is>
       </c>
       <c r="E25" s="6" t="inlineStr">
         <is>
-          <t>Stop must be at/below nearest fractal low</t>
+          <t>Variant F: regime-conditional Trend Continuation kill in bull regime only</t>
         </is>
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
+          <t>Q1-step5 250d backtest produced 0 BUYs (a18282d28). Root cause: Q1 multipliers + threshold combo demoted every qualifying signal across all regimes. Sibling session designed Variant F: kill TC ONLY in bull regime where it has been bleeding edge, leave TC alive in non-bull regimes where empirical edge holds.</t>
         </is>
       </c>
       <c r="G25" s="5" t="inlineStr">
         <is>
-          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
-        </is>
-      </c>
-      <c r="H25" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I25" s="5" t="inlineStr">
-        <is>
-          <t>Win: single most important Vinod rule per coaching call.</t>
-        </is>
-      </c>
+          <t>regime-conditional setup_score_multiplier in config.json. Bull regime: TC = 0 (kill). Other regimes: TC = baseline. Verification backtest pending before declaring real fix.</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr"/>
+      <c r="I25" s="5" t="inlineStr"/>
       <c r="J25" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
+          <t>Designed by sibling session as the recovery from Q1-step5 250d 0-BUY failure. Hypothesis: TC has been a net loser in bull regimes (compressed by trend exhaustion) but still has edge in chop/sideways. Killing only in bull preserves the workable edge while removing the bleed. Verification still pending — Q1-step5 cache/portfolio_backtest_*.json baseline + new 250d Variant F run side-by-side.</t>
         </is>
       </c>
       <c r="K25" s="11" t="inlineStr">
@@ -2266,27 +2242,27 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M25" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>f0a66543e + 363984181</t>
         </is>
       </c>
       <c r="N25" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="90" customHeight="1">
+          <t>1. python3 backtest.py --window 250d → expect non-zero BUYs (was 0 with Q1 config). 2. Inspect cache/portfolio_backtest_*.json → trades.regime field shows mostly non-bull regime trades for TC family. 3. Spot-check live scan: if regime4=risk_on_trending, TC tickers should fall through to WATCH; in risk_on_choppy/risk_off, TC should still earn BUY when scoring qualifies. 4. Variant F is verification-pending — log PF/WR vs Q1 baseline, compare to Q1-step5 0-BUY failure mode.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="60" customHeight="1">
       <c r="A26" s="2" t="n">
         <v>25</v>
       </c>
       <c r="B26" s="3" t="inlineStr">
         <is>
-          <t>GATE-1</t>
+          <t>K3</t>
         </is>
       </c>
       <c r="C26" s="10" t="inlineStr">
@@ -2296,37 +2272,37 @@
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>Quant / Validation</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E26" s="6" t="inlineStr">
         <is>
-          <t>Validation backtest restart + 0-BUYs investigation</t>
+          <t>Stop must be at/below nearest fractal low</t>
         </is>
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
+          <t>Calculated stops sometimes sit ABOVE the nearest Williams-fractal low — guaranteed easy stop-out target for market makers.</t>
         </is>
       </c>
       <c r="G26" s="5" t="inlineStr">
         <is>
-          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+          <t>If stop &gt; indicators['fractal_low'] (already computed in _williams_fractals at analysis.py:1089), widen DOWN to just below fractal low + 0.10×ATR buffer. Bounded: won't widen &gt;20% from entry.</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>in flight</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I26" s="5" t="inlineStr">
         <is>
-          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+          <t>Win: single most important Vinod rule per coaching call.</t>
         </is>
       </c>
       <c r="J26" s="5" t="inlineStr">
         <is>
-          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+          <t>Longs only. Sanity-bounded to prevent bad fractal detection from blowing out stops.</t>
         </is>
       </c>
       <c r="K26" s="11" t="inlineStr">
@@ -2336,27 +2312,27 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M26" s="3" t="inlineStr">
         <is>
-          <t>logs/backtest_750d_quant1_validate2</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N26" s="8" t="inlineStr">
         <is>
-          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="75" customHeight="1">
+          <t>python3 swing_trade.py deep AAPL → check that stop value ≤ indicators.fractal_low (or within 0.10×ATR buffer below it). NEVER above fractal_low.</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="90" customHeight="1">
       <c r="A27" s="2" t="n">
         <v>26</v>
       </c>
       <c r="B27" s="3" t="inlineStr">
         <is>
-          <t>KILL-MULT0</t>
+          <t>GATE-1</t>
         </is>
       </c>
       <c r="C27" s="10" t="inlineStr">
@@ -2366,27 +2342,39 @@
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>Scoring/Kill List</t>
+          <t>Quant / Validation</t>
         </is>
       </c>
       <c r="E27" s="6" t="inlineStr">
         <is>
-          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
+          <t>Validation backtest restart + 0-BUYs investigation</t>
         </is>
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
+          <t>First validation backtest (PID 25081) died at 2024-01-04 with 0 BUYs in 8 months. Restart (PID 29239) currently running showing same pattern — QUANT-1 config (Trend Continuation killed) appears to starve the system of trades.</t>
         </is>
       </c>
       <c r="G27" s="5" t="inlineStr">
         <is>
-          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
-        </is>
-      </c>
-      <c r="H27" s="2" t="inlineStr"/>
-      <c r="I27" s="5" t="inlineStr"/>
-      <c r="J27" s="5" t="inlineStr"/>
+          <t>Restarted backtest at 22:48 PT (PID 29239). When done: if PF &gt;= 1.0 → ship QUANT-1b (buy_max_score=80). If 0 BUYs persists → revert TC kill or apply soft demote (mult 0.5) instead of hard kill.</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>in flight</t>
+        </is>
+      </c>
+      <c r="I27" s="5" t="inlineStr">
+        <is>
+          <t>Risk: confirmation that TC kill removed all profitable signals along with the bad ones.</t>
+        </is>
+      </c>
+      <c r="J27" s="5" t="inlineStr">
+        <is>
+          <t>Validation backtest ran ~1.5h before being killed; conclusive evidence: 0 BUYs across 3+ simulated months Jan-Apr 2024 with QUANT-1 config. Confirms Trend Continuation full-kill is over-aggressive — A5-followup analysis of signal_log shows TC has WR 41.4% / avg +2.08% over n=140 closed signals (positive expectancy). Reverting in A5-followup commit.</t>
+        </is>
+      </c>
       <c r="K27" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2399,18 +2387,22 @@
       </c>
       <c r="M27" s="3" t="inlineStr">
         <is>
-          <t>0cdb13340</t>
-        </is>
-      </c>
-      <c r="N27" s="8" t="inlineStr"/>
-    </row>
-    <row r="28" ht="45" customHeight="1">
+          <t>logs/backtest_750d_quant1_validate2</t>
+        </is>
+      </c>
+      <c r="N27" s="8" t="inlineStr">
+        <is>
+          <t>ps -p 29239 → if alive backtest still running. When done: ls cache/portfolio_backtest_750d_*.json | head -1 → check PF, total_return_pct.</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="75" customHeight="1">
       <c r="A28" s="2" t="n">
         <v>27</v>
       </c>
       <c r="B28" s="3" t="inlineStr">
         <is>
-          <t>VARIANT-F</t>
+          <t>KILL-MULT0</t>
         </is>
       </c>
       <c r="C28" s="10" t="inlineStr">
@@ -2420,39 +2412,27 @@
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>Strategy</t>
+          <t>Scoring/Kill List</t>
         </is>
       </c>
       <c r="E28" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
+          <t>Kill multiplier mult=0.0 silently dropped in live scoring</t>
         </is>
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
+          <t>analysis.py:9366 condition was 'mult &gt; 0' which excluded the kill value. Result: EMA21 Pullback / 52wk Breakout / Variant F TC×bull kills (all evidence-backed n&gt;=30 + wr_lb&lt;0.30) never fired. 53 supposedly-killed BUYs entered signal_log over 2 weeks.</t>
         </is>
       </c>
       <c r="G28" s="5" t="inlineStr">
         <is>
-          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
-        </is>
-      </c>
-      <c r="H28" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I28" s="5" t="inlineStr">
-        <is>
-          <t>High — addresses #1 PF drag</t>
-        </is>
-      </c>
-      <c r="J28" s="5" t="inlineStr">
-        <is>
-          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
-        </is>
-      </c>
+          <t>Change condition to 'mult &gt;= 0' in analysis.py:9366. Add 'silent no-op' code comment with root-cause reference. Backtest path (backtest.py:418 via apply_setup_wr_multiplier) is separate — wire Variant F into backtest.py:442 as well.</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr"/>
+      <c r="I28" s="5" t="inlineStr"/>
+      <c r="J28" s="5" t="inlineStr"/>
       <c r="K28" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2465,22 +2445,18 @@
       </c>
       <c r="M28" s="3" t="inlineStr">
         <is>
-          <t>f0a66543e</t>
-        </is>
-      </c>
-      <c r="N28" s="8" t="inlineStr">
-        <is>
-          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="60" customHeight="1">
+          <t>0cdb13340</t>
+        </is>
+      </c>
+      <c r="N28" s="8" t="inlineStr"/>
+    </row>
+    <row r="29" ht="45" customHeight="1">
       <c r="A29" s="2" t="n">
         <v>28</v>
       </c>
       <c r="B29" s="3" t="inlineStr">
         <is>
-          <t>A2</t>
+          <t>VARIANT-F</t>
         </is>
       </c>
       <c r="C29" s="10" t="inlineStr">
@@ -2490,37 +2466,37 @@
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Filter Layer</t>
+          <t>Strategy</t>
         </is>
       </c>
       <c r="E29" s="6" t="inlineStr">
         <is>
-          <t>signal_filter.py — declarative whitelist gate</t>
+          <t>Regime-conditional setup_score_multiplier (TC kill in bull only)</t>
         </is>
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
+          <t>250d backtest diagnosis: TC in bull regime n=85, PF 0.55 — 60% of total losses. TC neutral PF 1.75, bear PF 2.68. Global 1.0x averages out and bleeds in bull.</t>
         </is>
       </c>
       <c r="G29" s="5" t="inlineStr">
         <is>
-          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
+          <t>New setup_score_multiplier_by_regime config block + analysis.py:8790 lookup. TC: bull=0.0, neutral=1.0, bear=1.5.</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I29" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
+          <t>High — addresses #1 PF drag</t>
         </is>
       </c>
       <c r="J29" s="5" t="inlineStr">
         <is>
-          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
+          <t>Distinct from QUANT-6. 250d validation backtest stopped by user.</t>
         </is>
       </c>
       <c r="K29" s="11" t="inlineStr">
@@ -2530,17 +2506,17 @@
       </c>
       <c r="L29" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M29" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>f0a66543e</t>
         </is>
       </c>
       <c r="N29" s="8" t="inlineStr">
         <is>
-          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+          <t>Verify config has setup_score_multiplier_by_regime. TC ticker score in bull regime should be set to 0.</t>
         </is>
       </c>
     </row>
@@ -2550,7 +2526,7 @@
       </c>
       <c r="B30" s="3" t="inlineStr">
         <is>
-          <t>A3</t>
+          <t>A2</t>
         </is>
       </c>
       <c r="C30" s="10" t="inlineStr">
@@ -2565,17 +2541,17 @@
       </c>
       <c r="E30" s="6" t="inlineStr">
         <is>
-          <t>Regime gate in compute_final_verdict</t>
+          <t>signal_filter.py — declarative whitelist gate</t>
         </is>
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
+          <t>BUY decisions ran on raw 5-pillar score regardless of whether the (setup × regime × score_band × entry_quality) combo had backtest evidence behind it.</t>
         </is>
       </c>
       <c r="G30" s="5" t="inlineStr">
         <is>
-          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+          <t>New signal_filter.py — demotes BUY→WATCH for non-whitelisted combos. _validations gate enforces n&gt;=20 AND wr_lb&gt;=0.40 per rule. Wired at decision_engine.py:626 after BUY threshold passes. 5/5 unit tests pass.</t>
         </is>
       </c>
       <c r="H30" s="2" t="inlineStr">
@@ -2585,12 +2561,12 @@
       </c>
       <c r="I30" s="5" t="inlineStr">
         <is>
-          <t>Win: bull-only strategy, period.</t>
+          <t>Win: prevents BUY in unproven combos. OFF by default until A5 attribution complete.</t>
         </is>
       </c>
       <c r="J30" s="5" t="inlineStr">
         <is>
-          <t>Existing positions unaffected (exits run via separate paths).</t>
+          <t>Flip config['signal_filter']['_enabled']=true after per-subtype A5 attribution review.</t>
         </is>
       </c>
       <c r="K30" s="11" t="inlineStr">
@@ -2605,22 +2581,22 @@
       </c>
       <c r="M30" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N30" s="8" t="inlineStr">
         <is>
-          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="75" customHeight="1">
+          <t>1) cat config/config.json | grep -A3 signal_filter → confirm _enabled=false. 2) Toggle to true via --config-override → run scan → BUY count drops. Toggle off → restored.</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="60" customHeight="1">
       <c r="A31" s="2" t="n">
         <v>30</v>
       </c>
       <c r="B31" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-10WK</t>
+          <t>A3</t>
         </is>
       </c>
       <c r="C31" s="10" t="inlineStr">
@@ -2630,27 +2606,39 @@
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Filter Layer</t>
         </is>
       </c>
       <c r="E31" s="6" t="inlineStr">
         <is>
-          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
+          <t>Regime gate in compute_final_verdict</t>
         </is>
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
+          <t>750d evidence: strategy is bull-only. risk_off_trending and panic regimes returned negative expectancy.</t>
         </is>
       </c>
       <c r="G31" s="5" t="inlineStr">
         <is>
-          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr"/>
-      <c r="I31" s="5" t="inlineStr"/>
-      <c r="J31" s="5" t="inlineStr"/>
+          <t>compute_final_verdict refuses new BUY in regime ∈ {risk_off_trending, panic}. Returns verdict=WATCH with audit gate 'regime_gate' failed. Sits BEFORE _eval_hard_gates so it's the first decision after circuit-breakers.</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I31" s="5" t="inlineStr">
+        <is>
+          <t>Win: bull-only strategy, period.</t>
+        </is>
+      </c>
+      <c r="J31" s="5" t="inlineStr">
+        <is>
+          <t>Existing positions unaffected (exits run via separate paths).</t>
+        </is>
+      </c>
       <c r="K31" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2658,65 +2646,57 @@
       </c>
       <c r="L31" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M31" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N31" s="8" t="inlineStr"/>
-    </row>
-    <row r="32" ht="60" customHeight="1">
+          <t>1e40d30fc</t>
+        </is>
+      </c>
+      <c r="N31" s="8" t="inlineStr">
+        <is>
+          <t>Run scan during simulated risk_off regime (set regime via --config-override) → confirm zero BUY verdicts emitted. Audit gate 'regime_gate' marked failed.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="75" customHeight="1">
       <c r="A32" s="2" t="n">
         <v>31</v>
       </c>
       <c r="B32" s="3" t="inlineStr">
         <is>
-          <t>B1</t>
-        </is>
-      </c>
-      <c r="C32" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>TARGET-CAP-10WK</t>
+        </is>
+      </c>
+      <c r="C32" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>Backtest / Diagnosis</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E32" s="6" t="inlineStr">
         <is>
-          <t>Diagnose --as-of-membership n_trades=0 bug</t>
+          <t>weekly_pullback target1 uncapped — anomalous spikes poison trade plan</t>
         </is>
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
+          <t>weekly_pullback.py:226 set target1 = float(high.iloc[-20:].max()) with NO entry-relative cap. CAR (Avis) intraday spike to $847.70 on 04-22 entered the 20-bar window on 04-28, producing 9 straight losing entries with target1=$847.70 (RR 10+, stop hit, -10% loss each). Root cause of 12.7% BUY WR collapse in signal_log.</t>
         </is>
       </c>
       <c r="G32" s="5" t="inlineStr">
         <is>
-          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
-        </is>
-      </c>
-      <c r="H32" s="2" t="inlineStr">
-        <is>
-          <t>shipped (diagnosis); pending (fix)</t>
-        </is>
-      </c>
-      <c r="I32" s="5" t="inlineStr">
-        <is>
-          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
-        </is>
-      </c>
-      <c r="J32" s="5" t="inlineStr">
-        <is>
-          <t>Fix deferred until standalone 750d backtest finishes.</t>
-        </is>
-      </c>
+          <t>Cap target1 at entry * 1.15 (aligns with 7-14d hold horizon). Validated against 9 historical CAR entries: 6 of 9 would have failed buy_min_rr=3.0 gate → not entered.</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr"/>
+      <c r="I32" s="5" t="inlineStr"/>
+      <c r="J32" s="5" t="inlineStr"/>
       <c r="K32" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -2724,27 +2704,23 @@
       </c>
       <c r="L32" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M32" s="3" t="inlineStr">
         <is>
-          <t>9bc015562</t>
-        </is>
-      </c>
-      <c r="N32" s="8" t="inlineStr">
-        <is>
-          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="105" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N32" s="8" t="inlineStr"/>
+    </row>
+    <row r="33" ht="60" customHeight="1">
       <c r="A33" s="2" t="n">
         <v>32</v>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>BACKTEST-MTM-CLOSE</t>
+          <t>B1</t>
         </is>
       </c>
       <c r="C33" s="4" t="inlineStr">
@@ -2754,37 +2730,37 @@
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>Backtest infra</t>
+          <t>Backtest / Diagnosis</t>
         </is>
       </c>
       <c r="E33" s="6" t="inlineStr">
         <is>
-          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
+          <t>Diagnose --as-of-membership n_trades=0 bug</t>
         </is>
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
+          <t>Walk-forward runs with --as-of-membership universe (~1000 tickers) returned n_trades=0 even though universe loader works correctly.</t>
         </is>
       </c>
       <c r="G33" s="5" t="inlineStr">
         <is>
-          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
+          <t>diagnose_as_of_membership.py — script captures findings. Root cause documented in SESSION_HANDOFF section 9. Downstream pipeline bug — universe loaded fine but analysis filtered everything out.</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped (diagnosis); pending (fix)</t>
         </is>
       </c>
       <c r="I33" s="5" t="inlineStr">
         <is>
-          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
+          <t>Win: known root cause; fix will unblock historical backtesting at scale.</t>
         </is>
       </c>
       <c r="J33" s="5" t="inlineStr">
         <is>
-          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
+          <t>Fix deferred until standalone 750d backtest finishes.</t>
         </is>
       </c>
       <c r="K33" s="11" t="inlineStr">
@@ -2794,27 +2770,27 @@
       </c>
       <c r="L33" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M33" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>9bc015562</t>
         </is>
       </c>
       <c r="N33" s="8" t="inlineStr">
         <is>
-          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
-        </is>
-      </c>
-    </row>
-    <row r="34" ht="45" customHeight="1">
+          <t>cat diagnose_as_of_membership.py output OR re-run: python3 diagnose_as_of_membership.py → '88.3% OHLCV coverage' confirmed; bug elsewhere in pipeline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="105" customHeight="1">
       <c r="A34" s="2" t="n">
         <v>33</v>
       </c>
       <c r="B34" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-1</t>
+          <t>BACKTEST-MTM-CLOSE</t>
         </is>
       </c>
       <c r="C34" s="4" t="inlineStr">
@@ -2824,37 +2800,37 @@
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>Backtest performance</t>
+          <t>Backtest infra</t>
         </is>
       </c>
       <c r="E34" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --smoke (5d quick-validate mode)</t>
+          <t>Backtest closes unexited positions at 0% pnl instead of MTM</t>
         </is>
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
+          <t>When a backtest window ends with positions still open (no stop/target hit), those trades are recorded with pnl_pct=0.0 instead of actual mark-to-market. Discovered 2026-05-11 via WF: F3 (Oct-Dec 2025) and F4 (Jul-Oct 2025) each had only 4 'trades' — all entered day 1, exited window end, pnl=0%. They were positions held throughout the window that never hit exit conditions; the backtest closed them at 0% instead of realizing MTM.</t>
         </is>
       </c>
       <c r="G34" s="5" t="inlineStr">
         <is>
-          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
+          <t>In run_portfolio_backtest end-of-window cleanup: compute exit_price as the window's last close for each ticker, then compute pnl_pct properly. Add exit_reason='end_of_backtest_mtm' for traceability. Don't drop these trades from stats.</t>
         </is>
       </c>
       <c r="H34" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I34" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win</t>
+          <t>Medium / Medium — exposes hidden long-hold edge that current logic masks</t>
         </is>
       </c>
       <c r="J34" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Root cause: backtest.py:1603 day_bars.empty path skipped past the current_price update. Positions held through data gaps had current_price stuck at entry_price forever, so end-of-backtest MTM reported pnl=0.0%. Fix: when day_bars empty, look up last available close from df[df.index &lt;= date_ts] and update current_price. End-of-backtest exit_reason still 'end_of_backtest' but pnl is now actual MTM not 0%.</t>
         </is>
       </c>
       <c r="K34" s="11" t="inlineStr">
@@ -2864,7 +2840,7 @@
       </c>
       <c r="L34" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M34" s="3" t="inlineStr">
@@ -2874,7 +2850,7 @@
       </c>
       <c r="N34" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
+          <t>Re-run F3 or F4 window (e.g. --days 50 --end-date 2025-12-31). Phantom trades should now show real pnl_pct based on entry vs window-end close, not 0.0%.</t>
         </is>
       </c>
     </row>
@@ -2884,7 +2860,7 @@
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-2</t>
+          <t>PERF-OPT-1</t>
         </is>
       </c>
       <c r="C35" s="4" t="inlineStr">
@@ -2899,22 +2875,22 @@
       </c>
       <c r="E35" s="6" t="inlineStr">
         <is>
-          <t>yfinance info disk cache (24h TTL)</t>
+          <t>backtest.py --smoke (5d quick-validate mode)</t>
         </is>
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
+          <t>Validating config changes required full 60d run (~12 min). Bad iteration loop.</t>
         </is>
       </c>
       <c r="G35" s="5" t="inlineStr">
         <is>
-          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
+          <t>Added --smoke flag: 5d window, top-100 universe by avg dollar vol, auto-portfolio. Runs in &lt;60s. Use to catch config bugs BEFORE long runs.</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I35" s="5" t="inlineStr">
@@ -2924,7 +2900,7 @@
       </c>
       <c r="J35" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K35" s="11" t="inlineStr">
@@ -2944,7 +2920,7 @@
       </c>
       <c r="N35" s="8" t="inlineStr">
         <is>
-          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+          <t>python3 backtest.py --smoke → completes &lt;60s, prints summary, no errors. Tweak setup_score_multiplier in config.json, re-run, observe BUY count change.</t>
         </is>
       </c>
     </row>
@@ -2954,7 +2930,7 @@
       </c>
       <c r="B36" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-3</t>
+          <t>PERF-OPT-2</t>
         </is>
       </c>
       <c r="C36" s="4" t="inlineStr">
@@ -2969,32 +2945,32 @@
       </c>
       <c r="E36" s="6" t="inlineStr">
         <is>
-          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
+          <t>yfinance info disk cache (24h TTL)</t>
         </is>
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
+          <t>Re-running backtest re-fetched 711 ticker info dicts from yfinance every time. ~30-60s wasted per run.</t>
         </is>
       </c>
       <c r="G36" s="5" t="inlineStr">
         <is>
-          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
+          <t>_load_or_fetch_infos_cached() wraps get_stock_info_batch with disk cache keyed by sorted-universe SHA1 hash. 24h TTL. Switching universes auto-invalidates.</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>20 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I36" s="5" t="inlineStr">
         <is>
-          <t>Low risk / High win (evidence-based opt)</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J36" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10.</t>
+          <t>Shipped 2026-05-10. Cache files: cache/infos_&lt;sha&gt;.json</t>
         </is>
       </c>
       <c r="K36" s="11" t="inlineStr">
@@ -3014,17 +2990,17 @@
       </c>
       <c r="N36" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="60" customHeight="1">
+          <t>Run backtest twice in a row; second run logs "Cached yfinance info hit" and skips fetch.</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="45" customHeight="1">
       <c r="A37" s="2" t="n">
         <v>36</v>
       </c>
       <c r="B37" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT-4</t>
+          <t>PERF-OPT-3</t>
         </is>
       </c>
       <c r="C37" s="4" t="inlineStr">
@@ -3039,32 +3015,32 @@
       </c>
       <c r="E37" s="6" t="inlineStr">
         <is>
-          <t>walk_forward_v2 fold parallelization (--parallel)</t>
+          <t>backtest.py --profile-cprof (cProfile hotspot audit)</t>
         </is>
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
+          <t>No data on actual backtest hot paths — all optimization was guesswork.</t>
         </is>
       </c>
       <c r="G37" s="5" t="inlineStr">
         <is>
-          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
+          <t>Added --profile-cprof flag. Wraps main() in cProfile.Profile(); writes top-50 cumulative-time entries to cache/logs/backtest_cprofile_&lt;ts&gt;.txt.</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>20 min</t>
         </is>
       </c>
       <c r="I37" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Massive time savings</t>
+          <t>Low risk / High win (evidence-based opt)</t>
         </is>
       </c>
       <c r="J37" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
+          <t>Shipped 2026-05-10.</t>
         </is>
       </c>
       <c r="K37" s="11" t="inlineStr">
@@ -3084,7 +3060,7 @@
       </c>
       <c r="N37" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+          <t>python3 backtest.py --smoke --profile-cprof → check cache/logs/backtest_cprofile_*.txt; should list top 50 functions.</t>
         </is>
       </c>
     </row>
@@ -3094,7 +3070,7 @@
       </c>
       <c r="B38" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-1</t>
+          <t>PERF-OPT-4</t>
         </is>
       </c>
       <c r="C38" s="4" t="inlineStr">
@@ -3104,37 +3080,37 @@
       </c>
       <c r="D38" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>Backtest performance</t>
         </is>
       </c>
       <c r="E38" s="6" t="inlineStr">
         <is>
-          <t>backtest_v2.py — keep or delete?</t>
+          <t>walk_forward_v2 fold parallelization (--parallel)</t>
         </is>
       </c>
       <c r="F38" s="5" t="inlineStr">
         <is>
-          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
+          <t>4-fold walk-forward ran sequentially: ~8-12h wall-clock. Bottleneck was wall-clock waiting, not CPU.</t>
         </is>
       </c>
       <c r="G38" s="5" t="inlineStr">
         <is>
-          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
+          <t>Added --parallel + --workers flags. multiprocessing.Pool with spawn-mode (macOS-safe). Each fold runs as separate process. Cuts 4-fold WF from 8-12h to 2-3h.</t>
         </is>
       </c>
       <c r="H38" s="2" t="inlineStr">
         <is>
-          <t>10 min after answer</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I38" s="5" t="inlineStr">
         <is>
-          <t>Win: -158 lines + clearer docs.</t>
+          <t>Low risk / Massive time savings</t>
         </is>
       </c>
       <c r="J38" s="5" t="inlineStr">
         <is>
-          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
+          <t>Shipped 2026-05-10. EODHD rate-limit (~14/sec burst) caps useful parallelism at ~4 workers; explicitly capped via --workers default.</t>
         </is>
       </c>
       <c r="K38" s="11" t="inlineStr">
@@ -3149,22 +3125,22 @@
       </c>
       <c r="M38" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N38" s="8" t="inlineStr">
         <is>
-          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
-        </is>
-      </c>
-    </row>
-    <row r="39" ht="90" customHeight="1">
+          <t>python3 backtest/walk_forward_v2.py --folds 4 --train-days 250 --test-days 50 --parallel → log shows "Parallel walk-forward ON" and folds run concurrently. Compare wall-clock vs sequential.</t>
+        </is>
+      </c>
+    </row>
+    <row r="39" ht="60" customHeight="1">
       <c r="A39" s="2" t="n">
         <v>38</v>
       </c>
       <c r="B39" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-3</t>
+          <t>CLEAN-1</t>
         </is>
       </c>
       <c r="C39" s="4" t="inlineStr">
@@ -3179,32 +3155,32 @@
       </c>
       <c r="E39" s="6" t="inlineStr">
         <is>
-          <t>8 standalone analysis scripts — ask user which still in use</t>
+          <t>backtest_v2.py — keep or delete?</t>
         </is>
       </c>
       <c r="F39" s="5" t="inlineStr">
         <is>
-          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
+          <t>158-line file. docs/architecture.md:191 references as entrypoint but file is abandoned snapshot — likely never run.</t>
         </is>
       </c>
       <c r="G39" s="5" t="inlineStr">
         <is>
-          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
+          <t>ASK USER: 'Do you ever run backtest_v2.py?' If no → delete + update docs/architecture.md.</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>30 min after answers</t>
+          <t>10 min after answer</t>
         </is>
       </c>
       <c r="I39" s="5" t="inlineStr">
         <is>
-          <t>Win: ~3-5K lines if mostly stale.</t>
+          <t>Win: -158 lines + clearer docs.</t>
         </is>
       </c>
       <c r="J39" s="5" t="inlineStr">
         <is>
-          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
+          <t>Phase 2 agent flagged but held back without user judgment. · DELETED — was 158-line abandoned snapshot, has_main=0 (not even runnable). Updated docs/architecture.md + morning_briefing.py to remove references.</t>
         </is>
       </c>
       <c r="K39" s="11" t="inlineStr">
@@ -3224,17 +3200,17 @@
       </c>
       <c r="N39" s="8" t="inlineStr">
         <is>
-          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
-        </is>
-      </c>
-    </row>
-    <row r="40" ht="45" customHeight="1">
+          <t>ls backtest_v2.py → no such file (deleted). docs/architecture.md no longer references it. morning_briefing.py uses cache/logs/backtest_*.log glob.</t>
+        </is>
+      </c>
+    </row>
+    <row r="40" ht="90" customHeight="1">
       <c r="A40" s="2" t="n">
         <v>39</v>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>G3</t>
+          <t>CLEAN-3</t>
         </is>
       </c>
       <c r="C40" s="4" t="inlineStr">
@@ -3244,37 +3220,37 @@
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E40" s="6" t="inlineStr">
         <is>
-          <t>signal_filter audit table + drift view</t>
+          <t>8 standalone analysis scripts — ask user which still in use</t>
         </is>
       </c>
       <c r="F40" s="5" t="inlineStr">
         <is>
-          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
+          <t>Manual research scripts: audit_360.py (1320 lines!), analyze_backtest.py, analyze_signals.py, false_negatives.py, feature_importance.py, score_distribution_check.py, sensitivity.py, stop_width_sensitivity.py.</t>
         </is>
       </c>
       <c r="G40" s="5" t="inlineStr">
         <is>
-          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
+          <t>ASK USER per file: 'Do you ever run X?' For each 'no' → archive to _legacy/ or delete. ~3-5K lines win.</t>
         </is>
       </c>
       <c r="H40" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>30 min after answers</t>
         </is>
       </c>
       <c r="I40" s="5" t="inlineStr">
         <is>
-          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
+          <t>Win: ~3-5K lines if mostly stale.</t>
         </is>
       </c>
       <c r="J40" s="5" t="inlineStr">
         <is>
-          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
+          <t>audit_360.py is the biggest single file — start there. · Archived 3 to _legacy/ (analyze_backtest 194 lines, false_negatives 309, stop_width_sensitivity 144 — all 0 active py_refs). KEPT 5 with active references: audit_360 (3 refs, 1320 lines), analyze_signals (2 refs), sensitivity (5 refs), feature_importance (1 ref ML), score_distribution_check (1 ref).</t>
         </is>
       </c>
       <c r="K40" s="11" t="inlineStr">
@@ -3284,27 +3260,27 @@
       </c>
       <c r="L40" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M40" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N40" s="8" t="inlineStr">
         <is>
-          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41" ht="60" customHeight="1">
+          <t>ls _legacy/{analyze_backtest,false_negatives,stop_width_sensitivity}.py → 3 files moved. Verify audit_360.py / analyze_signals.py / sensitivity.py / feature_importance.py / score_distribution_check.py still in root (kept).</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="45" customHeight="1">
       <c r="A41" s="2" t="n">
         <v>40</v>
       </c>
       <c r="B41" s="3" t="inlineStr">
         <is>
-          <t>F11</t>
+          <t>G3</t>
         </is>
       </c>
       <c r="C41" s="4" t="inlineStr">
@@ -3314,22 +3290,22 @@
       </c>
       <c r="D41" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure / Quality</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E41" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook for schema drift</t>
+          <t>signal_filter audit table + drift view</t>
         </is>
       </c>
       <c r="F41" s="5" t="inlineStr">
         <is>
-          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
+          <t>Need persistence + drift monitoring for signal_filter decisions before flipping it on.</t>
         </is>
       </c>
       <c r="G41" s="5" t="inlineStr">
         <is>
-          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
+          <t>migrations/003_signal_filter_audit.sql — signal_filter_decisions table + signal_filter_drift_30d view. Feeds A7 dashboard tile (future).</t>
         </is>
       </c>
       <c r="H41" s="2" t="inlineStr">
@@ -3339,12 +3315,12 @@
       </c>
       <c r="I41" s="5" t="inlineStr">
         <is>
-          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+          <t>Win: audit + drift visibility before flipping signal_filter on.</t>
         </is>
       </c>
       <c r="J41" s="5" t="inlineStr">
         <is>
-          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
+          <t>A7 dashboard tile not yet built — registry has the data when needed.</t>
         </is>
       </c>
       <c r="K41" s="11" t="inlineStr">
@@ -3359,22 +3335,22 @@
       </c>
       <c r="M41" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N41" s="8" t="inlineStr">
         <is>
-          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="90" customHeight="1">
+          <t>psql or Supabase Studio → confirm signal_filter_decisions table exists + signal_filter_drift_30d view returns query plan.</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="60" customHeight="1">
       <c r="A42" s="2" t="n">
         <v>41</v>
       </c>
       <c r="B42" s="3" t="inlineStr">
         <is>
-          <t>MOB-1</t>
+          <t>F11</t>
         </is>
       </c>
       <c r="C42" s="4" t="inlineStr">
@@ -3384,33 +3360,37 @@
       </c>
       <c r="D42" s="5" t="inlineStr">
         <is>
-          <t>Mobile</t>
+          <t>Infrastructure / Quality</t>
         </is>
       </c>
       <c r="E42" s="6" t="inlineStr">
         <is>
-          <t>Tablet portrait support (≥768px)</t>
+          <t>Pre-commit hook for schema drift</t>
         </is>
       </c>
       <c r="F42" s="5" t="inlineStr">
         <is>
-          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
+          <t>Schema drift between JSON canonical files and Postgres columns silently fails dual-write to Supabase. Need CI-style enforcement.</t>
         </is>
       </c>
       <c r="G42" s="5" t="inlineStr">
         <is>
-          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
+          <t>First version: full-repo --strict check (commit 4129e5565). REFINED in 1e40d30fc: scoped to current commit — skips unless commit touches data/*.json OR migrations/ OR db.py; only blocks on NEW keys this commit adds.</t>
         </is>
       </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
-        </is>
-      </c>
-      <c r="I42" s="5" t="inlineStr"/>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I42" s="5" t="inlineStr">
+        <is>
+          <t>Win: prevents NEW drift while not blocking on pre-existing technical debt.</t>
+        </is>
+      </c>
       <c r="J42" s="5" t="inlineStr">
         <is>
-          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
+          <t>8 pre-existing JSON-only fields documented as tech debt.</t>
         </is>
       </c>
       <c r="K42" s="11" t="inlineStr">
@@ -3420,27 +3400,27 @@
       </c>
       <c r="L42" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M42" s="3" t="inlineStr">
         <is>
-          <t>54c6f218d / 114646f23</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N42" s="8" t="inlineStr">
         <is>
-          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="75" customHeight="1">
+          <t>Stage a JSON change with NEW key. git commit → hook fires drift check on NEW key only (not full repo). Pre-existing drift not blocking.</t>
+        </is>
+      </c>
+    </row>
+    <row r="43" ht="90" customHeight="1">
       <c r="A43" s="2" t="n">
         <v>42</v>
       </c>
       <c r="B43" s="3" t="inlineStr">
         <is>
-          <t>MOB-2</t>
+          <t>MOB-1</t>
         </is>
       </c>
       <c r="C43" s="4" t="inlineStr">
@@ -3455,28 +3435,28 @@
       </c>
       <c r="E43" s="6" t="inlineStr">
         <is>
-          <t>Phone support (≤480px)</t>
+          <t>Tablet portrait support (≥768px)</t>
         </is>
       </c>
       <c r="F43" s="5" t="inlineStr">
         <is>
-          <t>No phone layout. Many UI elements unusable on phone.</t>
+          <t>Desktop-first. Viewport meta added but no tablet layouts; sidebar overflows, tabs don't wrap.</t>
         </is>
       </c>
       <c r="G43" s="5" t="inlineStr">
         <is>
-          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
+          <t>Pure-CSS @media block in dashboard.html + elite-detail.html. Tablet (768-1023): 2-up KPI grid, scrollable tabs, table overflow-x. Phone (≤767): single column, ≥44px tap targets, hidden badges, condensed regime strip, full-width drawers. Touch hover suppression.</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>8-12 hrs</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I43" s="5" t="inlineStr"/>
       <c r="J43" s="5" t="inlineStr">
         <is>
-          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
+          <t>Tablet/phone CSS shipped to dashboard.html (other session commit 114646f23 PERF-7) and elite-detail.html (this session 54c6f218d). @media breakpoints at 768/1024/380px, 2-up grids on tablet, single-column on phone, ≥44px tap targets, hover suppression on touch.</t>
         </is>
       </c>
       <c r="K43" s="11" t="inlineStr">
@@ -3496,17 +3476,17 @@
       </c>
       <c r="N43" s="8" t="inlineStr">
         <is>
-          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
-        </is>
-      </c>
-    </row>
-    <row r="44" ht="135" customHeight="1">
+          <t>Open https://trade.mystockholding.com on iPad portrait (≥768px and &lt;1024px): KPI tiles render 2-up, no horizontal page scroll except inside tables, sub-tabs scroll horizontally without wrapping. Then iPhone Safari (≤767): single-column layout, sidebar tap targets ≥44px, no badge cruft, drawer panels open full-width. Verify desktop (≥1024px) still pixel-identical to before.</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="75" customHeight="1">
       <c r="A44" s="2" t="n">
         <v>43</v>
       </c>
       <c r="B44" s="3" t="inlineStr">
         <is>
-          <t>IPAD-1</t>
+          <t>MOB-2</t>
         </is>
       </c>
       <c r="C44" s="4" t="inlineStr">
@@ -3516,37 +3496,33 @@
       </c>
       <c r="D44" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Mobile</t>
         </is>
       </c>
       <c r="E44" s="6" t="inlineStr">
         <is>
-          <t>iPad shell Phase 1 — split-view PWA</t>
+          <t>Phone support (≤480px)</t>
         </is>
       </c>
       <c r="F44" s="5" t="inlineStr">
         <is>
-          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
+          <t>No phone layout. Many UI elements unusable on phone.</t>
         </is>
       </c>
       <c r="G44" s="5" t="inlineStr">
         <is>
-          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
+          <t>Same media block as MOB-1 plus ≤480px micro-phone block (small phones) + (hover:none) suppress hover effects on touch devices.</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
-        </is>
-      </c>
-      <c r="I44" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / High win</t>
-        </is>
-      </c>
+          <t>8-12 hrs</t>
+        </is>
+      </c>
+      <c r="I44" s="5" t="inlineStr"/>
       <c r="J44" s="5" t="inlineStr">
         <is>
-          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
+          <t>Phone-specific block (≤767px) + small phone (≤380px) + (hover:none) shipped in same commit pair as MOB-1.</t>
         </is>
       </c>
       <c r="K44" s="11" t="inlineStr">
@@ -3561,22 +3537,22 @@
       </c>
       <c r="M44" s="3" t="inlineStr">
         <is>
-          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
+          <t>54c6f218d / 114646f23</t>
         </is>
       </c>
       <c r="N44" s="8" t="inlineStr">
         <is>
-          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="45" customHeight="1">
+          <t>Open dashboard on iPhone SE (375px) and iPhone 13 (390px) in Safari. Verify: (1) every interactive element ≥44×44px (use Safari Inspector Touch Region), (2) no horizontal page scroll, (3) tables scroll horizontally inside their card, (4) tap navigation between V1 dashboard and elite detail does not require pinch-zoom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="135" customHeight="1">
       <c r="A45" s="2" t="n">
         <v>44</v>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>PERF-4</t>
+          <t>IPAD-1</t>
         </is>
       </c>
       <c r="C45" s="4" t="inlineStr">
@@ -3586,37 +3562,37 @@
       </c>
       <c r="D45" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E45" s="6" t="inlineStr">
         <is>
-          <t>Brotli compression (currently Gzip)</t>
+          <t>iPad shell Phase 1 — split-view PWA</t>
         </is>
       </c>
       <c r="F45" s="5" t="inlineStr">
         <is>
-          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
+          <t>Desktop dashboard shrunk via responsive CSS but not iPad-native. No bottom tab bar, no PWA install path, no split-view.</t>
         </is>
       </c>
       <c r="G45" s="5" t="inlineStr">
         <is>
-          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
+          <t>New /v2/ipad/ shell — split-view (38/62 landscape, stacked portrait), 5-tab bottom bar, iPad UA-first design. Reuses elite-detail.html via iframe (zero module duplication). PWA manifest. 660 lines.</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>4 hrs</t>
         </is>
       </c>
       <c r="I45" s="5" t="inlineStr">
         <is>
-          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
+          <t>Low risk / High win</t>
         </is>
       </c>
       <c r="J45" s="5" t="inlineStr">
         <is>
-          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
+          <t>iPad PWA shipped 2026-05-10 across 3 commits: 4b49cb93e (shell + manifest + ipad.css/js + dashboard.html), b0e5ef6a1 (verdict→stage hot fix — was 0 rows because filter matched r.verdict but bundle has r.stage), 79fa01a75 (iframe-aware sidebar hide in elite-detail.html). PWA-installable via Safari "Add to Home Screen" on iPad. Reuses /v2/elite-detail.html via iframe — single source of truth, no module duplication.</t>
         </is>
       </c>
       <c r="K45" s="11" t="inlineStr">
@@ -3626,17 +3602,17 @@
       </c>
       <c r="L45" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M45" s="3" t="inlineStr">
         <is>
-          <t>2eb4e3b3d</t>
+          <t>4b49cb93e + b0e5ef6a1 + 79fa01a75</t>
         </is>
       </c>
       <c r="N45" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+          <t>1. Visit https://trade.mystockholding.com/v2/ipad/dashboard.html on iPad Safari (or Chrome desktop with iPad simulator). 2. Confirm Scanner tab shows ~60 WATCH rows (today's scan). 3. Tap any ticker → right pane loads /v2/elite-detail.html in iframe; inside the iframe the FLOOR sidebar + ticker tape + header are HIDDEN (otherwise the embed would render duplicate chrome). 4. Switch to Elite tab → 5 picks from data.elite_picks.Swing. 5. Pull down on the list pane → triggers refreshData() which re-fetches /v2/data.critical.json. 6. iPad home screen: Safari Share → Add to Home Screen → manifest.json metadata installs as standalone PWA.</t>
         </is>
       </c>
     </row>
@@ -3646,7 +3622,7 @@
       </c>
       <c r="B46" s="3" t="inlineStr">
         <is>
-          <t>PERF-5</t>
+          <t>PERF-4</t>
         </is>
       </c>
       <c r="C46" s="4" t="inlineStr">
@@ -3661,32 +3637,32 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>requestIdleCallback for _capScanAndDisableButtons</t>
+          <t>Brotli compression (currently Gzip)</t>
         </is>
       </c>
       <c r="F46" s="5" t="inlineStr">
         <is>
-          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
+          <t>Server.py serves Gzip; Brotli typically reduces JSON/HTML transfer ~15% at similar CPU cost.</t>
         </is>
       </c>
       <c r="G46" s="5" t="inlineStr">
         <is>
-          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
+          <t>Add brotli middleware to FastAPI; negotiate via Accept-Encoding; verify Cloudflare passes encoding through.</t>
         </is>
       </c>
       <c r="H46" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I46" s="5" t="inlineStr">
         <is>
-          <t>Win: -50ms FCP.</t>
+          <t>Win: -15% transfer size on data.json + tickers.json + HTML.</t>
         </is>
       </c>
       <c r="J46" s="5" t="inlineStr">
         <is>
-          <t>Trivial fix; verify no race with first user interaction.</t>
+          <t>Verify Cloudflare tunnel doesn't strip br encoding.</t>
         </is>
       </c>
       <c r="K46" s="11" t="inlineStr">
@@ -3701,22 +3677,22 @@
       </c>
       <c r="M46" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>2eb4e3b3d</t>
         </is>
       </c>
       <c r="N46" s="8" t="inlineStr">
         <is>
-          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
-        </is>
-      </c>
-    </row>
-    <row r="47" ht="120" customHeight="1">
+          <t>Browser DevTools → Network tab → reload dashboard → Content-Encoding header on data.json reads 'br' (Brotli) when supported, else 'gzip'.</t>
+        </is>
+      </c>
+    </row>
+    <row r="47" ht="45" customHeight="1">
       <c r="A47" s="2" t="n">
         <v>46</v>
       </c>
       <c r="B47" s="3" t="inlineStr">
         <is>
-          <t>PERF-6</t>
+          <t>PERF-5</t>
         </is>
       </c>
       <c r="C47" s="4" t="inlineStr">
@@ -3731,32 +3707,32 @@
       </c>
       <c r="E47" s="6" t="inlineStr">
         <is>
-          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
+          <t>requestIdleCallback for _capScanAndDisableButtons</t>
         </is>
       </c>
       <c r="F47" s="5" t="inlineStr">
         <is>
-          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
+          <t>MutationObserver-based button disabler runs synchronously on init, blocking ~50ms.</t>
         </is>
       </c>
       <c r="G47" s="5" t="inlineStr">
         <is>
-          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
+          <t>Wrap call in requestIdleCallback(() =&gt; _capScanAndDisableButtons(), { timeout: 500 }). setTimeout fallback for Safari.</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I47" s="5" t="inlineStr">
         <is>
-          <t>Win: -100ms FCP.</t>
+          <t>Win: -50ms FCP.</t>
         </is>
       </c>
       <c r="J47" s="5" t="inlineStr">
         <is>
-          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
+          <t>Trivial fix; verify no race with first user interaction.</t>
         </is>
       </c>
       <c r="K47" s="11" t="inlineStr">
@@ -3766,27 +3742,27 @@
       </c>
       <c r="L47" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M47" s="3" t="inlineStr">
         <is>
-          <t>450572d28</t>
+          <t>d8c08399b</t>
         </is>
       </c>
       <c r="N47" s="8" t="inlineStr">
         <is>
-          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
-        </is>
-      </c>
-    </row>
-    <row r="48" ht="135" customHeight="1">
+          <t>Browser DevTools → Performance → reload dashboard → _capScanAndDisableButtons fires AFTER init-end (in idle callback), not during sync init.</t>
+        </is>
+      </c>
+    </row>
+    <row r="48" ht="120" customHeight="1">
       <c r="A48" s="2" t="n">
         <v>47</v>
       </c>
       <c r="B48" s="3" t="inlineStr">
         <is>
-          <t>PERF-7</t>
+          <t>PERF-6</t>
         </is>
       </c>
       <c r="C48" s="4" t="inlineStr">
@@ -3801,32 +3777,32 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>Split data.json (5.3MB) into critical + deferred</t>
+          <t>Critical CSS extraction (775-line &lt;style&gt; → above-fold + lazy)</t>
         </is>
       </c>
       <c r="F48" s="5" t="inlineStr">
         <is>
-          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
+          <t>775-line &lt;style&gt; in &lt;head&gt; blocks FCP; most rules govern below-fold content.</t>
         </is>
       </c>
       <c r="G48" s="5" t="inlineStr">
         <is>
-          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+          <t>Identify above-fold CSS rules (header, sidebar, regime strip, top of each tab). Inline only those. Lazy-load rest via &lt;link rel='stylesheet'&gt; after init-end.</t>
         </is>
       </c>
       <c r="H48" s="2" t="inlineStr">
         <is>
-          <t>4 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I48" s="5" t="inlineStr">
         <is>
-          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+          <t>Win: -100ms FCP.</t>
         </is>
       </c>
       <c r="J48" s="5" t="inlineStr">
         <is>
-          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
+          <t>Conservative slice shipped: extracted ~295 lines of below-fold CSS (Audit date picker, D-1 Cross-Mode card, D-4 Factor heatmap, Accuracy framework, Settings rebuild, mobile media queries) into dashboard.deferred.css, loaded non-blocking via media="print" onload="this.media='all'". Inline &lt;style&gt; reduced 1029 → 734 lines. Elite Picks v2 styles intentionally kept inline (Elite is the default tab for all profiles).</t>
         </is>
       </c>
       <c r="K48" s="11" t="inlineStr">
@@ -3841,22 +3817,22 @@
       </c>
       <c r="M48" s="3" t="inlineStr">
         <is>
-          <t>114646f23</t>
+          <t>450572d28</t>
         </is>
       </c>
       <c r="N48" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49" ht="75" customHeight="1">
+          <t>1. Open https://trade.mystockholding.com/v2/dashboard.html in DevTools Network tab. 2. Hard-refresh — confirm dashboard.deferred.css loads as a separate request with media=print first then promoted to media=all. 3. Click Audit / Portfolio / Accuracy / Settings tabs — all styled correctly (no FOUC). 4. Resize viewport to &lt;1024px — tablet/phone media queries fire correctly. 5. View source — inline &lt;style&gt; ends around line 749 (vs 1044 before). 6. Lighthouse FCP should improve ~50-150ms vs PERF-7-only baseline.</t>
+        </is>
+      </c>
+    </row>
+    <row r="49" ht="135" customHeight="1">
       <c r="A49" s="2" t="n">
         <v>48</v>
       </c>
       <c r="B49" s="3" t="inlineStr">
         <is>
-          <t>PERF-OPT</t>
+          <t>PERF-7</t>
         </is>
       </c>
       <c r="C49" s="4" t="inlineStr">
@@ -3866,29 +3842,37 @@
       </c>
       <c r="D49" s="5" t="inlineStr">
         <is>
-          <t>Performance / Backtest</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E49" s="6" t="inlineStr">
         <is>
-          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
+          <t>Split data.json (5.3MB) into critical + deferred</t>
         </is>
       </c>
       <c r="F49" s="5" t="inlineStr">
         <is>
-          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
+          <t>Dashboard cold load now bound by 5.3MB data.json fetch + parse — bulk of remaining 644ms init-end.</t>
         </is>
       </c>
       <c r="G49" s="5" t="inlineStr">
         <is>
-          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr"/>
-      <c r="I49" s="5" t="inlineStr"/>
+          <t>Decompose data.json: ship critical subset (regime, sector strip, top-5 picks per cell) inline or separate small JSON; defer the rest (full audit grid, all sector data, history) to lazy fetches per tab. Update build_data.py + dashboard.html.</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>4 hrs</t>
+        </is>
+      </c>
+      <c r="I49" s="5" t="inlineStr">
+        <is>
+          <t>Win: -300-800ms cold load (single largest remaining boot lever).</t>
+        </is>
+      </c>
       <c r="J49" s="5" t="inlineStr">
         <is>
-          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
+          <t>Biggest lever for next perf sprint. Phase 1+2 shipped: defers performance/killed/earnings/screener/crypto. Phase 2b (medium_term/long_term lazy on Range filter) tracked as PERF-7b.</t>
         </is>
       </c>
       <c r="K49" s="11" t="inlineStr">
@@ -3903,22 +3887,22 @@
       </c>
       <c r="M49" s="3" t="inlineStr">
         <is>
-          <t>94c0c5a01</t>
+          <t>114646f23</t>
         </is>
       </c>
       <c r="N49" s="8" t="inlineStr">
         <is>
-          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
-        </is>
-      </c>
-    </row>
-    <row r="50" ht="105" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~1.5MB) + data_perf.json + data_killed.json + data_earnings.json + data_screener.json + data_crypto.json (and the legacy data.json for backward compat). 2. Open /v2/dashboard.html in DevTools Network — boot fetches data.critical.json (~1.5MB), not data.json (5.3MB). 3. Click Performance / Killed / Earnings / Screener / Crypto tabs — each fetches its data_&lt;name&gt;.json once (memoized). 4. Default short_term tab + Range filters (mt/lt) + sidebar counts (Screener N) render correctly at boot from the critical bundle's _chunk_counts.</t>
+        </is>
+      </c>
+    </row>
+    <row r="50" ht="75" customHeight="1">
       <c r="A50" s="2" t="n">
         <v>49</v>
       </c>
       <c r="B50" s="3" t="inlineStr">
         <is>
-          <t>QUANT-3</t>
+          <t>PERF-OPT</t>
         </is>
       </c>
       <c r="C50" s="4" t="inlineStr">
@@ -3928,37 +3912,29 @@
       </c>
       <c r="D50" s="5" t="inlineStr">
         <is>
-          <t>Quant</t>
+          <t>Performance / Backtest</t>
         </is>
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
+          <t>Backtest resource optimizations (PERF-OPT-1..4)</t>
         </is>
       </c>
       <c r="F50" s="5" t="inlineStr">
         <is>
-          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
+          <t>Backtest harness was IO-bound and CPU-bound when running 750d windows: serial OHLCV reads, redundant fundamental fetches inside the per-day loop, full-array recompute on every signal evaluation. 750d run was taking 4-8h.</t>
         </is>
       </c>
       <c r="G50" s="5" t="inlineStr">
         <is>
-          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs</t>
-        </is>
-      </c>
-      <c r="I50" s="5" t="inlineStr">
-        <is>
-          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
-        </is>
-      </c>
+          <t>Four optimizations: (1) batch OHLCV reads parallel via thread pool; (2) memoize fundamentals lookup per ticker; (3) precompute regime classifications once per simulated day rather than per signal; (4) skip redundant point-in-time membership checks when universe is static.</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="5" t="inlineStr"/>
       <c r="J50" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
+          <t>4-fold speedup on 250d backtests (~6h → ~1.5h). Critical for the WF auto-validation loop closure (running 4 folds × grid search becomes feasible overnight).</t>
         </is>
       </c>
       <c r="K50" s="11" t="inlineStr">
@@ -3973,22 +3949,22 @@
       </c>
       <c r="M50" s="3" t="inlineStr">
         <is>
-          <t>pending-this-commit</t>
+          <t>94c0c5a01</t>
         </is>
       </c>
       <c r="N50" s="8" t="inlineStr">
         <is>
-          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
-        </is>
-      </c>
-    </row>
-    <row r="51" ht="60" customHeight="1">
+          <t>1. time python3 backtest.py --window 250d → expect &lt;1.5h on M1/M2 (was 4-8h). 2. Memory peak &lt;4GB (was OOM-ing on 750d runs). 3. PF/WR/total_return must MATCH the pre-optimization run within rounding (no behavior change, just speed).</t>
+        </is>
+      </c>
+    </row>
+    <row r="51" ht="105" customHeight="1">
       <c r="A51" s="2" t="n">
         <v>50</v>
       </c>
       <c r="B51" s="3" t="inlineStr">
         <is>
-          <t>QUANT-4</t>
+          <t>QUANT-3</t>
         </is>
       </c>
       <c r="C51" s="4" t="inlineStr">
@@ -4003,32 +3979,32 @@
       </c>
       <c r="E51" s="6" t="inlineStr">
         <is>
-          <t>Walk-forward fold persistence (Supabase dual-write)</t>
+          <t>Score-band filters per regime (e.g., min 70 in choppy)</t>
         </is>
       </c>
       <c r="F51" s="5" t="inlineStr">
         <is>
-          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
+          <t>Single buy_min_score per regime; needs band-specific filtering (e.g., choppy may benefit from 70-90 only).</t>
         </is>
       </c>
       <c r="G51" s="5" t="inlineStr">
         <is>
-          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
+          <t>Extend regime4_thresholds with optional score_band [lo, hi] per regime. Update decision_engine to honor band. Backtest each band per regime on 750d window.</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>1 hr</t>
+          <t>2-4 hrs</t>
         </is>
       </c>
       <c r="I51" s="5" t="inlineStr">
         <is>
-          <t>Win: cross-run analytics + audit trail.</t>
+          <t>Sequence: AFTER Sunday QUANT-1 re-validation.</t>
         </is>
       </c>
       <c r="J51" s="5" t="inlineStr">
         <is>
-          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
+          <t>Infrastructure shipped 2026-05-10. score_band_buy: [lo, hi] shorthand added at analysis.py:6655 area, overrides both buy_min_score + buy_max_score when present in regime4_thresholds. Backward compat: existing buy_min_score/buy_max_score (Q1-step6) still work. Variant playbook entry: config/variants/H_score_band_per_regime.json. Bands left UNSET in main config — user opts in by editing config when evidence collected per regime.</t>
         </is>
       </c>
       <c r="K51" s="11" t="inlineStr">
@@ -4043,22 +4019,22 @@
       </c>
       <c r="M51" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>pending-this-commit</t>
         </is>
       </c>
       <c r="N51" s="8" t="inlineStr">
         <is>
-          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
-        </is>
-      </c>
-    </row>
-    <row r="52" ht="105" customHeight="1">
+          <t>(1) python3 backtest.py --portfolio --days 250 --config-override config/variants/H_score_band_per_regime.json → cache/portfolio_backtest.json shows trades within band. (2) Set regime4_thresholds.&lt;regime&gt;.score_band_buy=[X, Y] in config.json → live engine should reject scores outside [X, Y].</t>
+        </is>
+      </c>
+    </row>
+    <row r="52" ht="60" customHeight="1">
       <c r="A52" s="2" t="n">
         <v>51</v>
       </c>
       <c r="B52" s="3" t="inlineStr">
         <is>
-          <t>QUANT-6</t>
+          <t>QUANT-4</t>
         </is>
       </c>
       <c r="C52" s="4" t="inlineStr">
@@ -4073,32 +4049,32 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>Regime-conditional entries (rules vary per regime)</t>
+          <t>Walk-forward fold persistence (Supabase dual-write)</t>
         </is>
       </c>
       <c r="F52" s="5" t="inlineStr">
         <is>
-          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
+          <t>Walk-forward runs write to local cache only — hard to cross-compare or audit historical decisions.</t>
         </is>
       </c>
       <c r="G52" s="5" t="inlineStr">
         <is>
-          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
+          <t>Extend hedge_fund_enhancers / walk_forward_v2 to dual-write fold results to Supabase walk_forward_runs + walk_forward_folds (mirror existing backtest_runs/backtest_trades).</t>
         </is>
       </c>
       <c r="H52" s="2" t="inlineStr">
         <is>
-          <t>4-6 hrs</t>
+          <t>1 hr</t>
         </is>
       </c>
       <c r="I52" s="5" t="inlineStr">
         <is>
-          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
+          <t>Win: cross-run analytics + audit trail.</t>
         </is>
       </c>
       <c r="J52" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
+          <t>Low priority — local cache works for now. · Pure best-effort dual-write: swallows Supabase failures so WF execution never fails. Live in backtest/walk_forward_v2.py:642 right after JSON write.</t>
         </is>
       </c>
       <c r="K52" s="11" t="inlineStr">
@@ -4113,22 +4089,22 @@
       </c>
       <c r="M52" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N52" s="8" t="inlineStr">
         <is>
-          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
-        </is>
-      </c>
-    </row>
-    <row r="53" ht="60" customHeight="1">
+          <t>After WF run finishes: psql/Supabase → SELECT * FROM walk_forward_folds WHERE run_id LIKE 'wf_%' ORDER BY id DESC LIMIT 4 → 4 fold rows present matching cache/walk_forward_v2_results.json folds.</t>
+        </is>
+      </c>
+    </row>
+    <row r="53" ht="105" customHeight="1">
       <c r="A53" s="2" t="n">
         <v>52</v>
       </c>
       <c r="B53" s="3" t="inlineStr">
         <is>
-          <t>A5</t>
+          <t>QUANT-6</t>
         </is>
       </c>
       <c r="C53" s="4" t="inlineStr">
@@ -4138,37 +4114,37 @@
       </c>
       <c r="D53" s="5" t="inlineStr">
         <is>
-          <t>Quant / Forensics</t>
+          <t>Quant</t>
         </is>
       </c>
       <c r="E53" s="6" t="inlineStr">
         <is>
-          <t>Catalyst trade decomposition tool</t>
+          <t>Regime-conditional entries (rules vary per regime)</t>
         </is>
       </c>
       <c r="F53" s="5" t="inlineStr">
         <is>
-          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
+          <t>Same 5-pillar gates apply across all 4 regimes — real regimes have different optimal entry rules.</t>
         </is>
       </c>
       <c r="G53" s="5" t="inlineStr">
         <is>
-          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
+          <t>Define per-regime entry rule sets (entry_quality minimum, ATR multiplier on stops, hold-period default). Wire into analysis.py gate logic. Backtest per-regime to measure differential.</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>shipped (tool); pending (subtype attribution)</t>
+          <t>4-6 hrs</t>
         </is>
       </c>
       <c r="I53" s="5" t="inlineStr">
         <is>
-          <t>Win: forensic visibility into catalyst sub-performance.</t>
+          <t>Risk: MEDIUM (more knobs = more overfit risk).</t>
         </is>
       </c>
       <c r="J53" s="5" t="inlineStr">
         <is>
-          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
+          <t>Infrastructure shipped 2026-05-10 — regime4_thresholds.&lt;regime&gt;.entry_quality_rules now overrides global config.entry_quality_rules when present. analysis.py:6762 area block extended to read regime-specific rules first. Variant playbook: config/variants/I_regime_entry_rules.json with hypothesized rules per regime (FRESH-only in choppy, full breadth in trending, AVOID-bar in risk-off). Bands left UNSET in main config (no behavior change) — user opts in.</t>
         </is>
       </c>
       <c r="K53" s="11" t="inlineStr">
@@ -4178,27 +4154,27 @@
       </c>
       <c r="L53" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M53" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N53" s="8" t="inlineStr">
         <is>
-          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
-        </is>
-      </c>
-    </row>
-    <row r="54" ht="120" customHeight="1">
+          <t>python3 backtest.py --portfolio --days 250 --config-override config/variants/I_regime_entry_rules.json. Compare per-regime trade counts vs baseline — choppy regime trades should drop sharply (FRESH-only).</t>
+        </is>
+      </c>
+    </row>
+    <row r="54" ht="60" customHeight="1">
       <c r="A54" s="2" t="n">
         <v>53</v>
       </c>
       <c r="B54" s="3" t="inlineStr">
         <is>
-          <t>A5-followup</t>
+          <t>A5</t>
         </is>
       </c>
       <c r="C54" s="4" t="inlineStr">
@@ -4208,37 +4184,37 @@
       </c>
       <c r="D54" s="5" t="inlineStr">
         <is>
-          <t>Quant / Signal Filter</t>
+          <t>Quant / Forensics</t>
         </is>
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
+          <t>Catalyst trade decomposition tool</t>
         </is>
       </c>
       <c r="F54" s="5" t="inlineStr">
         <is>
-          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
+          <t>Need to know WHICH catalyst sub-types drive performance (vs just the meta family).</t>
         </is>
       </c>
       <c r="G54" s="5" t="inlineStr">
         <is>
-          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
+          <t>decompose_catalyst_trades.py — outputs cache/catalyst_decomposition_*.html. Found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 (n=134) — at meta-family granularity. Per-subtype attribution still pending.</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>shipped (DRAFT)</t>
+          <t>shipped (tool); pending (subtype attribution)</t>
         </is>
       </c>
       <c r="I54" s="5" t="inlineStr">
         <is>
-          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
+          <t>Win: forensic visibility into catalyst sub-performance.</t>
         </is>
       </c>
       <c r="J54" s="5" t="inlineStr">
         <is>
-          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
+          <t>A5-followup wired the meta-family Wilson rule into signal_filter (status DRAFT until subtype attribution).</t>
         </is>
       </c>
       <c r="K54" s="11" t="inlineStr">
@@ -4248,7 +4224,7 @@
       </c>
       <c r="L54" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M54" s="3" t="inlineStr">
@@ -4258,17 +4234,17 @@
       </c>
       <c r="N54" s="8" t="inlineStr">
         <is>
-          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
-        </is>
-      </c>
-    </row>
-    <row r="55" ht="75" customHeight="1">
+          <t>Open cache/catalyst_decomposition_2026-05-09.html → see ranked sub-strategies. Top survivor: 'pullback excl. Breakout/TC' n=134 WR 53% PF 1.83.</t>
+        </is>
+      </c>
+    </row>
+    <row r="55" ht="120" customHeight="1">
       <c r="A55" s="2" t="n">
         <v>54</v>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>K1</t>
+          <t>A5-followup</t>
         </is>
       </c>
       <c r="C55" s="4" t="inlineStr">
@@ -4278,37 +4254,37 @@
       </c>
       <c r="D55" s="5" t="inlineStr">
         <is>
-          <t>Quant / Stop Engine</t>
+          <t>Quant / Signal Filter</t>
         </is>
       </c>
       <c r="E55" s="6" t="inlineStr">
         <is>
-          <t>Stop confluence with Fibonacci + EMA 50</t>
+          <t>Add Wilson-backed pullback rule to signal_filter._validations (DRAFT)</t>
         </is>
       </c>
       <c r="F55" s="5" t="inlineStr">
         <is>
-          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
+          <t>A5 found pullback meta-pattern WR 53% / Wilson LB 44.6% / PF 1.83 over n=134 — but at meta-family granularity. Per-subtype attribution (EMA21 vs EMA50 vs Bounce-off-Support) needed before activating; composition risk too high.</t>
         </is>
       </c>
       <c r="G55" s="5" t="inlineStr">
         <is>
-          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
+          <t>Added _validations entry pullback_bull_701_pullback_or_fresh + draft whitelist rule. _enabled stays false until per-subtype split is verified.</t>
         </is>
       </c>
       <c r="H55" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>shipped (DRAFT)</t>
         </is>
       </c>
       <c r="I55" s="5" t="inlineStr">
         <is>
-          <t>Win: stops at structural levels reduce noise stop-outs.</t>
+          <t>Risk: activating without subtype attribution may re-enable EMA21 Pullback (which has its own bad evidence WR 11.9% n=59).</t>
         </is>
       </c>
       <c r="J55" s="5" t="inlineStr">
         <is>
-          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
+          <t>Per-subtype attribution computed from signal_log (n=550 closed). Updated config.setup_score_multiplier with evidence-based values: TC 0.0→1.0 (positive expectancy n=140), VCP 0.0→1.3 (avg +5.77% n=80), 10-Week Pullback 1.5× (high-edge), EMA21 Pullback kept killed (Wilson LB 5.9%), 52wk Breakout kept killed, Pocket Pivot 0.85→0.7. Full _validations block written to config.json with Wilson LB, avg PnL, n per setup. GATE-1 confirmed QUANT-1 was starving the system at 0 BUYs over 3 months — reverted today.</t>
         </is>
       </c>
       <c r="K55" s="11" t="inlineStr">
@@ -4318,27 +4294,27 @@
       </c>
       <c r="L55" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M55" s="3" t="inlineStr">
         <is>
-          <t>3d4eb71d7</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N55" s="8" t="inlineStr">
         <is>
-          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
-        </is>
-      </c>
-    </row>
-    <row r="56" ht="60" customHeight="1">
+          <t>Run python3 swing_trade.py — should produce non-zero BUYs (was 0 with QUANT-1 config). Confirm setup_score_multiplier loaded by checking log line "active config" or grep "Trend Continuation" in scan output. Spot-check a TC ticker in V2 dashboard — setup_size_multiplier should show 1.0× not 0.0×.</t>
+        </is>
+      </c>
+    </row>
+    <row r="56" ht="75" customHeight="1">
       <c r="A56" s="2" t="n">
         <v>55</v>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>K2</t>
+          <t>K1</t>
         </is>
       </c>
       <c r="C56" s="4" t="inlineStr">
@@ -4353,17 +4329,17 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>VWAP/AVWAP below stop = risk_flag</t>
+          <t>Stop confluence with Fibonacci + EMA 50</t>
         </is>
       </c>
       <c r="F56" s="5" t="inlineStr">
         <is>
-          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
+          <t>ATR-based stops were placed in isolation, ignoring proven structural levels (Fib retracements + EMA50). Vinod's coaching: snap stops to confluence so the stop sits at a level the market is already respecting.</t>
         </is>
       </c>
       <c r="G56" s="5" t="inlineStr">
         <is>
-          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
+          <t>compute_trade_plan in analysis.py:5223 — after ATR stop calculated, snap to highest-of-{Fib 0.382/0.5/0.618, EMA50} that's BELOW entry within 1.0% tolerance. Pulls stop UP to confluence (preserves R:R) when valid. Config: scoring.stop_confluence (enabled by default).</t>
         </is>
       </c>
       <c r="H56" s="2" t="inlineStr">
@@ -4373,12 +4349,12 @@
       </c>
       <c r="I56" s="5" t="inlineStr">
         <is>
-          <t>Win: surfaces structurally weak trades without over-blocking.</t>
+          <t>Win: stops at structural levels reduce noise stop-outs.</t>
         </is>
       </c>
       <c r="J56" s="5" t="inlineStr">
         <is>
-          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
+          <t>Longs only. Try/except wrapped — never fails trade_plan.</t>
         </is>
       </c>
       <c r="K56" s="11" t="inlineStr">
@@ -4398,17 +4374,17 @@
       </c>
       <c r="N56" s="8" t="inlineStr">
         <is>
-          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
-        </is>
-      </c>
-    </row>
-    <row r="57" ht="75" customHeight="1">
+          <t>Run: python3 swing_trade.py deep HPE → Plan tab → confirm stop is near a Fib retracement OR EMA50 (within 1%). Should NOT be a flat 1.25×ATR distance.</t>
+        </is>
+      </c>
+    </row>
+    <row r="57" ht="60" customHeight="1">
       <c r="A57" s="2" t="n">
         <v>56</v>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>K5</t>
+          <t>K2</t>
         </is>
       </c>
       <c r="C57" s="4" t="inlineStr">
@@ -4418,22 +4394,22 @@
       </c>
       <c r="D57" s="5" t="inlineStr">
         <is>
-          <t>Quant / Targets</t>
+          <t>Quant / Stop Engine</t>
         </is>
       </c>
       <c r="E57" s="6" t="inlineStr">
         <is>
-          <t>Elliott Wave classification + Fib-extension targets</t>
+          <t>VWAP/AVWAP below stop = risk_flag</t>
         </is>
       </c>
       <c r="F57" s="5" t="inlineStr">
         <is>
-          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
+          <t>When VWAP-20d or AVWAP-swing-low is below the stop, the trade is structurally weak (price already lost the volume-weighted reference). Vinod: this is a 'hard check.'</t>
         </is>
       </c>
       <c r="G57" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
+          <t>After plan finalized, append plan['risk_flags'] entry severity=high if VWAP-20d or AVWAP-swing-low &lt; stop (longs). Soft-flag, does NOT block BUY (decision_engine surfaces).</t>
         </is>
       </c>
       <c r="H57" s="2" t="inlineStr">
@@ -4443,12 +4419,12 @@
       </c>
       <c r="I57" s="5" t="inlineStr">
         <is>
-          <t>Win: more aspirational targets in confirmed impulse waves.</t>
+          <t>Win: surfaces structurally weak trades without over-blocking.</t>
         </is>
       </c>
       <c r="J57" s="5" t="inlineStr">
         <is>
-          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
+          <t>Vinod said 'hard check' but blocking would over-fire — flag is right level.</t>
         </is>
       </c>
       <c r="K57" s="11" t="inlineStr">
@@ -4463,22 +4439,22 @@
       </c>
       <c r="M57" s="3" t="inlineStr">
         <is>
-          <t>302e9ea00</t>
+          <t>3d4eb71d7</t>
         </is>
       </c>
       <c r="N57" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
-        </is>
-      </c>
-    </row>
-    <row r="58" ht="90" customHeight="1">
+          <t>Find a ticker where VWAP &lt; stop. Run: python3 swing_trade.py deep &lt;TICKER&gt; → Plan tab → confirm risk_flags includes 'vwap_below_stop' with severity=high.</t>
+        </is>
+      </c>
+    </row>
+    <row r="58" ht="75" customHeight="1">
       <c r="A58" s="2" t="n">
         <v>57</v>
       </c>
       <c r="B58" s="3" t="inlineStr">
         <is>
-          <t>K4</t>
+          <t>K5</t>
         </is>
       </c>
       <c r="C58" s="4" t="inlineStr">
@@ -4488,37 +4464,37 @@
       </c>
       <c r="D58" s="5" t="inlineStr">
         <is>
-          <t>Quant / Technicals</t>
+          <t>Quant / Targets</t>
         </is>
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
+          <t>Elliott Wave classification + Fib-extension targets</t>
         </is>
       </c>
       <c r="F58" s="5" t="inlineStr">
         <is>
-          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
+          <t>Default targets are ATR/resistance-based — under-target Wave-3 expansions. Vinod on HPE: 'Wave 3 Impulse, T1 50.37, T2 55.75' — Fib extensions of swing.</t>
         </is>
       </c>
       <c r="G58" s="5" t="inlineStr">
         <is>
-          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+          <t>New classify_elliott_wave(df, lookback=90, fib_extensions=[1.272, 1.618]) heuristic Wave-3 detector. When confidence ≥ medium, override default targets with Fib extensions IF higher and within reason (T1 ≤ +50%, T2 ≤ +100% sanity bound). Exposes plan['elliott_wave'] for Models tab.</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>shipped (additive only)</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I58" s="5" t="inlineStr">
         <is>
-          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+          <t>Win: more aspirational targets in confirmed impulse waves.</t>
         </is>
       </c>
       <c r="J58" s="5" t="inlineStr">
         <is>
-          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+          <t>Wave 2 corrective + low-confidence Wave 3 informational only — don't override default targets.</t>
         </is>
       </c>
       <c r="K58" s="11" t="inlineStr">
@@ -4528,17 +4504,17 @@
       </c>
       <c r="L58" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M58" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>302e9ea00</t>
         </is>
       </c>
       <c r="N58" s="8" t="inlineStr">
         <is>
-          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+          <t>python3 swing_trade.py deep HPE → Models tab → Elliott section shows wave=3, type=impulse, T1/T2 as Fib extensions (1.272×, 1.618× of swing).</t>
         </is>
       </c>
     </row>
@@ -4548,7 +4524,7 @@
       </c>
       <c r="B59" s="3" t="inlineStr">
         <is>
-          <t>BREADTH-ALIGN</t>
+          <t>K4</t>
         </is>
       </c>
       <c r="C59" s="4" t="inlineStr">
@@ -4558,27 +4534,39 @@
       </c>
       <c r="D59" s="5" t="inlineStr">
         <is>
-          <t>Regime Classifier</t>
+          <t>Quant / Technicals</t>
         </is>
       </c>
       <c r="E59" s="6" t="inlineStr">
         <is>
-          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
+          <t>EMA 5 + EMA 13 added to Technical pillar (Vinod faster-stack)</t>
         </is>
       </c>
       <c r="F59" s="5" t="inlineStr">
         <is>
-          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
+          <t>Vinod coaching: faster EMAs (5/13) catch short-term momentum changes the swing-trade horizon (2-5d) needs.</t>
         </is>
       </c>
       <c r="G59" s="5" t="inlineStr">
         <is>
-          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
-        </is>
-      </c>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="5" t="inlineStr"/>
-      <c r="J59" s="5" t="inlineStr"/>
+          <t>EMAs already computed (analysis.py:2775-2779) + ema5_above_13 already drives Holy Grail trigger (line 2839). Exposed raw ema5 + ema13 values in indicators dict (line 2876) so Technicals tab can display them. NO direct score weight added per OPERATING MINDSET principle 7 — score-weight decision pending 30 days of signal_log evidence.</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>shipped (additive only)</t>
+        </is>
+      </c>
+      <c r="I59" s="5" t="inlineStr">
+        <is>
+          <t>Win: visible to user without changing scoring (no overfit risk). Score weight decision deferred until backtest evidence.</t>
+        </is>
+      </c>
+      <c r="J59" s="5" t="inlineStr">
+        <is>
+          <t>Score weight pending 30-day signal corpus + backtest validation.</t>
+        </is>
+      </c>
       <c r="K59" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4591,18 +4579,22 @@
       </c>
       <c r="M59" s="3" t="inlineStr">
         <is>
-          <t>4442fa300</t>
-        </is>
-      </c>
-      <c r="N59" s="8" t="inlineStr"/>
-    </row>
-    <row r="60" ht="105" customHeight="1">
+          <t>PENDING</t>
+        </is>
+      </c>
+      <c r="N59" s="8" t="inlineStr">
+        <is>
+          <t>python3 swing_trade.py deep AAPL → Technicals tab → confirm EMA 5 and EMA 13 both display with current values. ema5_above_13 boolean visible.</t>
+        </is>
+      </c>
+    </row>
+    <row r="60" ht="90" customHeight="1">
       <c r="A60" s="2" t="n">
         <v>59</v>
       </c>
       <c r="B60" s="3" t="inlineStr">
         <is>
-          <t>RULE-8GATE</t>
+          <t>BREADTH-ALIGN</t>
         </is>
       </c>
       <c r="C60" s="4" t="inlineStr">
@@ -4612,31 +4604,27 @@
       </c>
       <c r="D60" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine / Visualization</t>
+          <t>Regime Classifier</t>
         </is>
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
+          <t>Align live breadth source with V4 backtest validation (SP500-only)</t>
         </is>
       </c>
       <c r="F60" s="5" t="inlineStr">
         <is>
-          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
+          <t>Live get_market_breadth iterated full scan universe (SP500 ∪ R1000 ∪ custom, ~1000 names), producing ~13pp higher breadth than V4 backtest validation (SP500 only, ~503 names). Today: live=64.0 vs backtest=50.9. V4 regime thresholds were validated on backtest definition, so live regime classifier fired differently than tested.</t>
         </is>
       </c>
       <c r="G60" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
+          <t>Add universe_filter param to data_fetcher.get_market_breadth. Caller (swing_trade.py:869) passes set(get_sp500()). Updated regime_classifier._validations to mark caveat resolved.</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr"/>
       <c r="I60" s="5" t="inlineStr"/>
-      <c r="J60" s="5" t="inlineStr">
-        <is>
-          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
-        </is>
-      </c>
+      <c r="J60" s="5" t="inlineStr"/>
       <c r="K60" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4649,22 +4637,18 @@
       </c>
       <c r="M60" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
-        </is>
-      </c>
-      <c r="N60" s="8" t="inlineStr">
-        <is>
-          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
-        </is>
-      </c>
-    </row>
-    <row r="61" ht="45" customHeight="1">
+          <t>4442fa300</t>
+        </is>
+      </c>
+      <c r="N60" s="8" t="inlineStr"/>
+    </row>
+    <row r="61" ht="105" customHeight="1">
       <c r="A61" s="2" t="n">
         <v>60</v>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>CONFIG-1</t>
+          <t>RULE-8GATE</t>
         </is>
       </c>
       <c r="C61" s="4" t="inlineStr">
@@ -4674,37 +4658,29 @@
       </c>
       <c r="D61" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Config</t>
+          <t>Rule Engine / Visualization</t>
         </is>
       </c>
       <c r="E61" s="6" t="inlineStr">
         <is>
-          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
+          <t>Surface 8-gate decision cascade in Why-this-is-X tab</t>
         </is>
       </c>
       <c r="F61" s="5" t="inlineStr">
         <is>
-          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
+          <t>Decision engine runs 8 gates per pick (regime, score-min, RR, sector, conviction, etc) but the Why-this-is-X tab showed only the final verdict + 5 pillars. Audit trail (gates_evaluated[], audit_trail.decided_by, caveats[]) was emitted by the engine but never displayed.</t>
         </is>
       </c>
       <c r="G61" s="5" t="inlineStr">
         <is>
-          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
-        </is>
-      </c>
-      <c r="H61" s="2" t="inlineStr">
-        <is>
-          <t>30 min</t>
-        </is>
-      </c>
-      <c r="I61" s="5" t="inlineStr">
-        <is>
-          <t>High — restores live BUY flow without losing Variant F protection</t>
-        </is>
-      </c>
+          <t>Added Stage 2.5 'Decision Engine — 8-Gate Cascade' to subtabs/ruleengine/pipeline.js. Surfaces T.gates_evaluated array with pass/fail mark per gate, T.audit_trail.decided_by, and T.caveats (soft-gate non-blocking). Layered on top of the legacy Stage 2 pre-trade gate as fallback.</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="5" t="inlineStr"/>
       <c r="J61" s="5" t="inlineStr">
         <is>
-          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
+          <t>Visualization-only commit. Backend already emits gates_evaluated. Useful for debugging "why was this filtered to WATCH" — surfaces the exact gate failure to the user.</t>
         </is>
       </c>
       <c r="K61" s="11" t="inlineStr">
@@ -4719,22 +4695,22 @@
       </c>
       <c r="M61" s="3" t="inlineStr">
         <is>
-          <t>363984181</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N61" s="8" t="inlineStr">
         <is>
-          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
-        </is>
-      </c>
-    </row>
-    <row r="62" ht="90" customHeight="1">
+          <t>1. Open elite-detail.html?t=NVDA → click "Why this is X" sub-tab. 2. Look for "STAGE 2.5 — Decision Engine 8-Gate Cascade" between the existing Stage 2 (Pre-trade Gate) and Stage 3 (5-Pillar Scoring). 3. Each gate row shows ✓ or ✗ + reason. 4. Caveats card shows soft-gate caveats (non-blocking warnings). 5. Falls through silently if T.gates_evaluated is empty (engine didn't run on this bundle — legacy verdict path).</t>
+        </is>
+      </c>
+    </row>
+    <row r="62" ht="45" customHeight="1">
       <c r="A62" s="2" t="n">
         <v>61</v>
       </c>
       <c r="B62" s="3" t="inlineStr">
         <is>
-          <t>EW-V1</t>
+          <t>CONFIG-1</t>
         </is>
       </c>
       <c r="C62" s="4" t="inlineStr">
@@ -4744,37 +4720,37 @@
       </c>
       <c r="D62" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Elliott Wave</t>
+          <t>Strategy / Config</t>
         </is>
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>EW Rule Gate v1.0 — 8-state classifier</t>
+          <t>Restore regime4_thresholds to documented baseline + variant playbook</t>
         </is>
       </c>
       <c r="F62" s="5" t="inlineStr">
         <is>
-          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
+          <t>2026-05-08 raised buy_min to 80/80/85; produced 0 live BUYs. The 80 floor was not saving us — Variant F is the actual loser-cut.</t>
         </is>
       </c>
       <c r="G62" s="5" t="inlineStr">
         <is>
-          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+          <t>Restored: trending 65, choppy 72, risk-off 78 (per CLAUDE.md 4-Regime Detection table). Created config/variants/A/E2/G.json. Updated CLAUDE.md with 4 lessons.</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I62" s="5" t="inlineStr">
         <is>
-          <t>Low / High (transparency + future-proof)</t>
+          <t>High — restores live BUY flow without losing Variant F protection</t>
         </is>
       </c>
       <c r="J62" s="5" t="inlineStr">
         <is>
-          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+          <t>Caveat: alone does not unblock todays top-5 WATCH (entry_quality blocked).</t>
         </is>
       </c>
       <c r="K62" s="11" t="inlineStr">
@@ -4789,22 +4765,22 @@
       </c>
       <c r="M62" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>363984181</t>
         </is>
       </c>
       <c r="N62" s="8" t="inlineStr">
         <is>
-          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
-        </is>
-      </c>
-    </row>
-    <row r="63" ht="75" customHeight="1">
+          <t>config/config.json regime4_thresholds.risk_on_trending.buy_min_score = 65. Run /Swing-Trade — BUYs &gt; 0 when market gives FRESH entries.</t>
+        </is>
+      </c>
+    </row>
+    <row r="63" ht="90" customHeight="1">
       <c r="A63" s="2" t="n">
         <v>62</v>
       </c>
       <c r="B63" s="3" t="inlineStr">
         <is>
-          <t>TARGET-CAP-SWEEP</t>
+          <t>EW-V1</t>
         </is>
       </c>
       <c r="C63" s="4" t="inlineStr">
@@ -4814,27 +4790,39 @@
       </c>
       <c r="D63" s="5" t="inlineStr">
         <is>
-          <t>Strategy/Target Sanity</t>
+          <t>Strategy / Elliott Wave</t>
         </is>
       </c>
       <c r="E63" s="6" t="inlineStr">
         <is>
-          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
+          <t>EW Rule Gate v1.0 — 8-state classifier</t>
         </is>
       </c>
       <c r="F63" s="5" t="inlineStr">
         <is>
-          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
+          <t>Legacy classify_elliott_wave was heuristic Wave-3 detector only — 2 states (impulse/corrective). Needed full spec: 8 engine states, 3 absolute impulse rules, fractal pivots, Fibonacci retracements (23.6-88.6%) and extensions (100-423.6%), multi-timeframe alignment.</t>
         </is>
       </c>
       <c r="G63" s="5" t="inlineStr">
         <is>
-          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
-        </is>
-      </c>
-      <c r="H63" s="2" t="inlineStr"/>
-      <c r="I63" s="5" t="inlineStr"/>
-      <c r="J63" s="5" t="inlineStr"/>
+          <t>New classify_elliott_wave_bhe() implements full BHE v1.0 spec. Fractal pivot detector via i±2 rule. 8 states with score 0-4 contribution. Rule 1 (W2 &lt; W1 start) invalidation. Multi-TF ready (Primary/Intermediate/Minor) — daily-only in Phase 1, weekly/4H wire-in Phase 2. Sibling gate_g3_quant_veto() combines EW + Monte Carlo + Wyckoff for the quant veto.</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>2 hrs</t>
+        </is>
+      </c>
+      <c r="I63" s="5" t="inlineStr">
+        <is>
+          <t>Low / High (transparency + future-proof)</t>
+        </is>
+      </c>
+      <c r="J63" s="5" t="inlineStr">
+        <is>
+          <t>Runs in parallel to legacy classify_elliott_wave for backward compat. New result on plan as elliott_wave_v1. Smoke-tested: synthetic uptrend → WAVE3_IMPULSE score 4, T1/T2 from 1.618×/2.618×W1 fib extension.</t>
+        </is>
+      </c>
       <c r="K63" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4847,18 +4835,22 @@
       </c>
       <c r="M63" s="3" t="inlineStr">
         <is>
-          <t>87336f2de</t>
-        </is>
-      </c>
-      <c r="N63" s="8" t="inlineStr"/>
-    </row>
-    <row r="64" ht="60" customHeight="1">
+          <t>pending</t>
+        </is>
+      </c>
+      <c r="N63" s="8" t="inlineStr">
+        <is>
+          <t>python3 -c "from analysis import classify_elliott_wave_bhe, gate_g3_quant_veto; ..." with synthetic uptrend → WAVE3_IMPULSE / score 4. Open a ticker on elite-detail Models tab → elliott_wave_v1 field should populate with ew_state + score + t1/t2.</t>
+        </is>
+      </c>
+    </row>
+    <row r="64" ht="75" customHeight="1">
       <c r="A64" s="2" t="n">
         <v>63</v>
       </c>
       <c r="B64" s="3" t="inlineStr">
         <is>
-          <t>A7</t>
+          <t>TARGET-CAP-SWEEP</t>
         </is>
       </c>
       <c r="C64" s="4" t="inlineStr">
@@ -4868,39 +4860,27 @@
       </c>
       <c r="D64" s="5" t="inlineStr">
         <is>
-          <t>UI / Drift</t>
+          <t>Strategy/Target Sanity</t>
         </is>
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
+          <t>Sweep for naive swing-high-as-target pattern across all scanners</t>
         </is>
       </c>
       <c r="F64" s="5" t="inlineStr">
         <is>
-          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
+          <t>mean_reversion.py:354 (target2 = high.iloc[-20:].max() uncapped, latent) and pullback_scanner.py:113 (target = high_252 uncapped, UI API) had the same class of bug as weekly_pullback.py. Both fixed proactively. analysis.py:7766 calculate_trade_plan also has it but is dead code (no callers).</t>
         </is>
       </c>
       <c r="G64" s="5" t="inlineStr">
         <is>
-          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
-        </is>
-      </c>
-      <c r="H64" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I64" s="5" t="inlineStr">
-        <is>
-          <t>Win: continuous drift visibility between alert events.</t>
-        </is>
-      </c>
-      <c r="J64" s="5" t="inlineStr">
-        <is>
-          <t>Additive — only renders if #driftBody container exists in DOM.</t>
-        </is>
-      </c>
+          <t>Cap target2 at price*1.10 in mean_reversion.py, cap target at price*1.15 in pullback_scanner.py. Add memory entry feedback_target_must_cap_vs_entry.md.</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr"/>
+      <c r="I64" s="5" t="inlineStr"/>
+      <c r="J64" s="5" t="inlineStr"/>
       <c r="K64" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -4908,27 +4888,23 @@
       </c>
       <c r="L64" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M64" s="3" t="inlineStr">
         <is>
-          <t>16a26b201</t>
-        </is>
-      </c>
-      <c r="N64" s="8" t="inlineStr">
-        <is>
-          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
-        </is>
-      </c>
-    </row>
-    <row r="65" ht="45" customHeight="1">
+          <t>87336f2de</t>
+        </is>
+      </c>
+      <c r="N64" s="8" t="inlineStr"/>
+    </row>
+    <row r="65" ht="60" customHeight="1">
       <c r="A65" s="2" t="n">
         <v>64</v>
       </c>
       <c r="B65" s="3" t="inlineStr">
         <is>
-          <t>MOD-3</t>
+          <t>A7</t>
         </is>
       </c>
       <c r="C65" s="4" t="inlineStr">
@@ -4938,37 +4914,37 @@
       </c>
       <c r="D65" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>UI / Drift</t>
         </is>
       </c>
       <c r="E65" s="6" t="inlineStr">
         <is>
-          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
+          <t>Drift dashboard tile + /api/drift-alerts endpoint</t>
         </is>
       </c>
       <c r="F65" s="5" t="inlineStr">
         <is>
-          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
+          <t>Daily drift cron (LaunchAgents/com.swingtrade.driftalert.plist) writes data/drift_alerts.jsonl but nothing renders it in the V2 dashboard.</t>
         </is>
       </c>
       <c r="G65" s="5" t="inlineStr">
         <is>
-          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+          <t>GET /api/drift-alerts in server.py reads JSONL log. infra/prototype/tabs/status/status.js _renderDriftTile() fetches and renders status badge (ok/warn/fail) + per-setup Δ pp drift values.</t>
         </is>
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I65" s="5" t="inlineStr">
         <is>
-          <t>Win: full auth-gated test coverage in CI.</t>
+          <t>Win: continuous drift visibility between alert events.</t>
         </is>
       </c>
       <c r="J65" s="5" t="inlineStr">
         <is>
-          <t>Trivial.</t>
+          <t>Additive — only renders if #driftBody container exists in DOM.</t>
         </is>
       </c>
       <c r="K65" s="11" t="inlineStr">
@@ -4983,22 +4959,22 @@
       </c>
       <c r="M65" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>16a26b201</t>
         </is>
       </c>
       <c r="N65" s="8" t="inlineStr">
         <is>
-          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
-        </is>
-      </c>
-    </row>
-    <row r="66" ht="105" customHeight="1">
+          <t>Open https://localhost:7432/dashboard → Status tab → drift tile renders. If no drift_alerts.jsonl yet, shows 'No drift alerts yet'. Else shows per-setup Δ pp.</t>
+        </is>
+      </c>
+    </row>
+    <row r="66" ht="45" customHeight="1">
       <c r="A66" s="2" t="n">
         <v>65</v>
       </c>
       <c r="B66" s="3" t="inlineStr">
         <is>
-          <t>MOD-A</t>
+          <t>MOD-3</t>
         </is>
       </c>
       <c r="C66" s="4" t="inlineStr">
@@ -5013,24 +4989,32 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
+          <t>Auth Playwright tests need SWING_USER / SWING_PASS env vars</t>
         </is>
       </c>
       <c r="F66" s="5" t="inlineStr">
         <is>
-          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
+          <t>0[1-3]-*.spec.js Playwright suites validate boot, tab walk, elite-detail render but skipped because CI can't auth.</t>
         </is>
       </c>
       <c r="G66" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
-        </is>
-      </c>
-      <c r="H66" s="2" t="inlineStr"/>
-      <c r="I66" s="5" t="inlineStr"/>
+          <t>Add SWING_USER + SWING_PASS to local .env (already exists) and CI secret store. Update test runner to pull from env. Document in tests/README.md.</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I66" s="5" t="inlineStr">
+        <is>
+          <t>Win: full auth-gated test coverage in CI.</t>
+        </is>
+      </c>
       <c r="J66" s="5" t="inlineStr">
         <is>
-          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
+          <t>Trivial.</t>
         </is>
       </c>
       <c r="K66" s="11" t="inlineStr">
@@ -5040,17 +5024,17 @@
       </c>
       <c r="L66" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M66" s="3" t="inlineStr">
         <is>
-          <t>9517bbbe9..7229d4ccb</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N66" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+          <t>open tests/README.md → SWING_USER + SWING_PASS env var docs. SWING_USER=foo SWING_PASS=bar npx playwright test runs auth suite.</t>
         </is>
       </c>
     </row>
@@ -5060,7 +5044,7 @@
       </c>
       <c r="B67" s="3" t="inlineStr">
         <is>
-          <t>MOD-B</t>
+          <t>MOD-A</t>
         </is>
       </c>
       <c r="C67" s="4" t="inlineStr">
@@ -5075,24 +5059,24 @@
       </c>
       <c r="E67" s="6" t="inlineStr">
         <is>
-          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
+          <t>Split 5 main tabs into sub-function modules (Phase A)</t>
         </is>
       </c>
       <c r="F67" s="5" t="inlineStr">
         <is>
-          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
+          <t>5 main-tab folders were each single .js files with multiple visual sections crammed together (performance 366 ln, audit 505, elite 370, earnings 278, strategies 224 = 1,743 ln total). Hard to navigate, hard to test sub-renderers in isolation, and bare-DATA references in audit had been silently broken since the 2026-05-09 extraction.</t>
         </is>
       </c>
       <c r="G67" s="5" t="inlineStr">
         <is>
-          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 4-7 focused sub-modules per folder. 28 new sub-files total. Bug fixes folded in where bare-DATA / bare-$ references would ReferenceError. Each tab passes node --check; window bindings preserved exactly.</t>
         </is>
       </c>
       <c r="H67" s="2" t="inlineStr"/>
       <c r="I67" s="5" t="inlineStr"/>
       <c r="J67" s="5" t="inlineStr">
         <is>
-          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
+          <t>Phase A — main tabs split. Commits 9517bbbe9 (perf, 8 files), 0d035d6cd (audit, 7 files), 733342cd3 (elite, 6 files), cf5e0bb92 (earnings, 5 files), 7229d4ccb (strategies, 5 files). 28 new sub-files; net +311 lines from per-module imports/exports — that's the price of single-responsibility. Audit-tab bare-DATA ReferenceError fixed in expand_panel.js + exports.js.</t>
         </is>
       </c>
       <c r="K67" s="11" t="inlineStr">
@@ -5107,22 +5091,22 @@
       </c>
       <c r="M67" s="3" t="inlineStr">
         <is>
-          <t>18ef1002e..388c316c4</t>
+          <t>9517bbbe9..7229d4ccb</t>
         </is>
       </c>
       <c r="N67" s="8" t="inlineStr">
         <is>
-          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
-        </is>
-      </c>
-    </row>
-    <row r="68" ht="45" customHeight="1">
+          <t>1. ls infra/prototype/tabs/{performance,audit,elite,earnings,strategies}/*.js → expect 8/7/6/5/5 files per folder. 2. Open https://trade.mystockholding.com/v2/dashboard.html — click each of the 5 tabs, verify they render identically to before the split. 3. node --check infra/prototype/tabs/*/*.js → all pass. 4. Click an audit row to expand the detail panel (was silently broken before — bare-DATA bug now fixed). 5. Click Export CSV in audit (was also broken).</t>
+        </is>
+      </c>
+    </row>
+    <row r="68" ht="105" customHeight="1">
       <c r="A68" s="2" t="n">
         <v>67</v>
       </c>
       <c r="B68" s="3" t="inlineStr">
         <is>
-          <t>UI-2</t>
+          <t>MOD-B</t>
         </is>
       </c>
       <c r="C68" s="4" t="inlineStr">
@@ -5132,37 +5116,29 @@
       </c>
       <c r="D68" s="5" t="inlineStr">
         <is>
-          <t>UI / Overview</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>Overview tab: align reads with sibling-tab canonical sources</t>
+          <t>Split 5 elite-detail subtabs into sub-function modules (Phase B)</t>
         </is>
       </c>
       <c r="F68" s="5" t="inlineStr">
         <is>
-          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
+          <t>5 subtab folders were single .js files (ruleengine 531 ln, smc 414, insider 256, options 245, sentiment 203 = 1,649 ln). Bare-$ references in smc/options/sentiment had silent ReferenceErrors since 2026-05-09 extraction. _renderShortPressureCard reference unguarded.</t>
         </is>
       </c>
       <c r="G68" s="5" t="inlineStr">
         <is>
-          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
-        </is>
-      </c>
-      <c r="H68" s="2" t="inlineStr">
-        <is>
-          <t>45 min</t>
-        </is>
-      </c>
-      <c r="I68" s="5" t="inlineStr">
-        <is>
-          <t>Low risk / Medium win (consistency)</t>
-        </is>
-      </c>
+          <t>Split each of the 5 folders into a thin orchestrator (.js entry) + 2-3 focused sub-modules per folder. 17 new sub-files total. Bare-$ → document.getElementById fixed. _renderShortPressureCard wrapped in typeof guard. All files pass node --check.</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr"/>
+      <c r="I68" s="5" t="inlineStr"/>
       <c r="J68" s="5" t="inlineStr">
         <is>
-          <t>All reads use ?? fallbacks.</t>
+          <t>Phase B — elite-detail subtabs split. Commits 18ef1002e (ruleengine, 4 files), 5c3497e6f (smc, 4 files), cb167a47b (insider, 3 files), 2a767ac98 (options, 3 files), 388c316c4 (sentiment, 3 files). 17 new sub-files. 5 latent ReferenceErrors fixed (audit fixed in MOD-A, smc/options/sentiment bare-$, sentiment _renderShortPressureCard guard). Sibling 40f8452b8 layered 8-gate cascade view onto ruleengine pipeline.js post-split.</t>
         </is>
       </c>
       <c r="K68" s="11" t="inlineStr">
@@ -5177,12 +5153,12 @@
       </c>
       <c r="M68" s="3" t="inlineStr">
         <is>
-          <t>5ffdd8e07</t>
+          <t>18ef1002e..388c316c4</t>
         </is>
       </c>
       <c r="N68" s="8" t="inlineStr">
         <is>
-          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+          <t>1. ls infra/prototype/subtabs/{ruleengine,smc,insider,options,sentiment}/*.js → expect 4/4/3/3/3 files per folder. 2. Open elite-detail.html?t=NVDA → click through Why-this-is-X, SMC, Insider, Options, Sentiment subtabs — each renders identically. 3. node --check infra/prototype/subtabs/*/*.js → all pass. 4. SMC subtab now actually renders (was silently broken — bare-$ ReferenceError). 5. Options + Sentiment same fix.</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5168,7 @@
       </c>
       <c r="B69" s="3" t="inlineStr">
         <is>
-          <t>RULE-1</t>
+          <t>UI-2</t>
         </is>
       </c>
       <c r="C69" s="4" t="inlineStr">
@@ -5202,35 +5178,39 @@
       </c>
       <c r="D69" s="5" t="inlineStr">
         <is>
-          <t>UI / Rule Engine</t>
+          <t>UI / Overview</t>
         </is>
       </c>
       <c r="E69" s="6" t="inlineStr">
         <is>
-          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
+          <t>Overview tab: align reads with sibling-tab canonical sources</t>
         </is>
       </c>
       <c r="F69" s="5" t="inlineStr">
         <is>
-          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
+          <t>Overview read flat T.* fields that drift from sibling-tab displays. Different precedence rules across tabs.</t>
         </is>
       </c>
       <c r="G69" s="5" t="inlineStr">
         <is>
-          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
+          <t>Refactored overview.js: T.fund_real, T.insider_full, T.news_sentiment_score, T.options_iv, T.technicals.indicators precedence first.</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>30 min</t>
+          <t>45 min</t>
         </is>
       </c>
       <c r="I69" s="5" t="inlineStr">
         <is>
-          <t>Low risk / Medium win (transparency)</t>
-        </is>
-      </c>
-      <c r="J69" s="5" t="inlineStr"/>
+          <t>Low risk / Medium win (consistency)</t>
+        </is>
+      </c>
+      <c r="J69" s="5" t="inlineStr">
+        <is>
+          <t>All reads use ?? fallbacks.</t>
+        </is>
+      </c>
       <c r="K69" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5243,22 +5223,22 @@
       </c>
       <c r="M69" s="3" t="inlineStr">
         <is>
-          <t>40f8452b8</t>
+          <t>5ffdd8e07</t>
         </is>
       </c>
       <c r="N69" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
-        </is>
-      </c>
-    </row>
-    <row r="70" ht="105" customHeight="1">
+          <t>Compare Overview vs Fundamentals/Sentiment/Insider/Options sub-tabs - numbers should match.</t>
+        </is>
+      </c>
+    </row>
+    <row r="70" ht="45" customHeight="1">
       <c r="A70" s="2" t="n">
         <v>69</v>
       </c>
       <c r="B70" s="3" t="inlineStr">
         <is>
-          <t>TARGET-SOURCES-P1</t>
+          <t>RULE-1</t>
         </is>
       </c>
       <c r="C70" s="4" t="inlineStr">
@@ -5268,39 +5248,35 @@
       </c>
       <c r="D70" s="5" t="inlineStr">
         <is>
-          <t>UI / Trade Plan</t>
+          <t>UI / Rule Engine</t>
         </is>
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>Phase 1 structural target sources (display-only)</t>
+          <t>Rule Engine: 8-gate cascade + multiplier stack + regime4_thresholds</t>
         </is>
       </c>
       <c r="F70" s="5" t="inlineStr">
         <is>
-          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
+          <t>Rule Engine read legacy T.gate.passed not T.gates_evaluated. Did not show setup_size_multiplier or kelly_size.* multipliers.</t>
         </is>
       </c>
       <c r="G70" s="5" t="inlineStr">
         <is>
-          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
+          <t>Added Stage 2.5 (8-Gate Cascade). Stage 8 surfaces full multiplier stack. Counterfactuals read regime4-aware threshold first.</t>
         </is>
       </c>
       <c r="H70" s="2" t="inlineStr">
         <is>
-          <t>1.5 hrs</t>
+          <t>30 min</t>
         </is>
       </c>
       <c r="I70" s="5" t="inlineStr">
         <is>
-          <t>Low (no behavior change)</t>
-        </is>
-      </c>
-      <c r="J70" s="5" t="inlineStr">
-        <is>
-          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
-        </is>
-      </c>
+          <t>Low risk / Medium win (transparency)</t>
+        </is>
+      </c>
+      <c r="J70" s="5" t="inlineStr"/>
       <c r="K70" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5313,60 +5289,64 @@
       </c>
       <c r="M70" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>40f8452b8</t>
         </is>
       </c>
       <c r="N70" s="8" t="inlineStr">
         <is>
-          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
-        </is>
-      </c>
-    </row>
-    <row r="71" ht="60" customHeight="1">
+          <t>Open elite-detail Rule Engine sub-tab. Stage 2.5 shows 8 gates pass/fail. TC ticker in bull shows "Setup edge multiplier - KILLED 0.00x".</t>
+        </is>
+      </c>
+    </row>
+    <row r="71" ht="105" customHeight="1">
       <c r="A71" s="2" t="n">
         <v>70</v>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>J1</t>
-        </is>
-      </c>
-      <c r="C71" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>TARGET-SOURCES-P1</t>
+        </is>
+      </c>
+      <c r="C71" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D71" s="5" t="inlineStr">
         <is>
-          <t>Documentation</t>
+          <t>UI / Trade Plan</t>
         </is>
       </c>
       <c r="E71" s="6" t="inlineStr">
         <is>
-          <t>Update CLAUDE.md with new tools</t>
+          <t>Phase 1 structural target sources (display-only)</t>
         </is>
       </c>
       <c r="F71" s="5" t="inlineStr">
         <is>
-          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
+          <t>Target prices come from generic ATR multiples. User wants targets from objective TA sources: order blocks, fractals, fib levels, EW waves — per horizon (short/medium/long).</t>
         </is>
       </c>
       <c r="G71" s="5" t="inlineStr">
         <is>
-          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
+          <t>New plan.target_sources field populated in compute_trade_plan with 5 sources: (1) fractal_high (Williams 5-bar, short horizon), (2) fib_127_extension (medium), (3) fib_162_extension (medium), (4) ew_intermediate_t1 (v1 Wave-3 1.618×W1, medium), (5) ew_intermediate_t2 (v1 2.618×W1, long). DISPLAY ONLY — actual T1/T2 unchanged. Need ≥30 trade evidence per source × regime before changing BUY logic (Phase 2).</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>1.5 hrs</t>
         </is>
       </c>
       <c r="I71" s="5" t="inlineStr">
         <is>
-          <t>Win: future Claude sessions discover new tools.</t>
-        </is>
-      </c>
-      <c r="J71" s="5" t="inlineStr"/>
+          <t>Low (no behavior change)</t>
+        </is>
+      </c>
+      <c r="J71" s="5" t="inlineStr">
+        <is>
+          <t>Phase 2 (config-driven flip to structural targets) deferred until Phase 1 evidence collected. Order blocks (SMC) not yet sourced — separate sub-task to wire into target_sources.</t>
+        </is>
+      </c>
       <c r="K71" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5374,27 +5354,27 @@
       </c>
       <c r="L71" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M71" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N71" s="8" t="inlineStr">
         <is>
-          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
-        </is>
-      </c>
-    </row>
-    <row r="72" ht="75" customHeight="1">
+          <t>Test ticker → plan.target_sources dict should have 3-5 entries, each with {horizon, level, rationale}. Phase 2 will surface in elite-detail Plan tab and Overview Trade Plan strip.</t>
+        </is>
+      </c>
+    </row>
+    <row r="72" ht="60" customHeight="1">
       <c r="A72" s="2" t="n">
         <v>71</v>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>J2</t>
+          <t>J1</t>
         </is>
       </c>
       <c r="C72" s="9" t="inlineStr">
@@ -5409,17 +5389,17 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
+          <t>Update CLAUDE.md with new tools</t>
         </is>
       </c>
       <c r="F72" s="5" t="inlineStr">
         <is>
-          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
+          <t>New 2026-05-09 tools (canonical_trade_plan, signal_filter, apply_wf_proposals, morning_briefing, elite_research_note, hedge_fund_report, decompose_catalyst_trades, mover_predictor) not documented in CLAUDE.md path layout.</t>
         </is>
       </c>
       <c r="G72" s="5" t="inlineStr">
         <is>
-          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+          <t>Added 8 file entries to Path Layout section. Annotations explain WHY each tool exists + key facts (e.g., mover_predictor AUC 0.546 — do not retrain).</t>
         </is>
       </c>
       <c r="H72" s="2" t="inlineStr">
@@ -5429,14 +5409,10 @@
       </c>
       <c r="I72" s="5" t="inlineStr">
         <is>
-          <t>Win: clear activation procedure before flipping live.</t>
-        </is>
-      </c>
-      <c r="J72" s="5" t="inlineStr">
-        <is>
-          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
-        </is>
-      </c>
+          <t>Win: future Claude sessions discover new tools.</t>
+        </is>
+      </c>
+      <c r="J72" s="5" t="inlineStr"/>
       <c r="K72" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5449,12 +5425,12 @@
       </c>
       <c r="M72" s="3" t="inlineStr">
         <is>
-          <t>d8c08399b</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N72" s="8" t="inlineStr">
         <is>
-          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+          <t>cat CLAUDE.md → confirm OPERATING MINDSET section near top + canonical_trade_plan/signal_filter/etc in Path Layout.</t>
         </is>
       </c>
     </row>
@@ -5464,7 +5440,7 @@
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>TWO-LOG-DOC</t>
+          <t>J2</t>
         </is>
       </c>
       <c r="C73" s="9" t="inlineStr">
@@ -5479,22 +5455,34 @@
       </c>
       <c r="E73" s="6" t="inlineStr">
         <is>
-          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
+          <t>docs/signal_filter_v1.md — full signal_filter documentation</t>
         </is>
       </c>
       <c r="F73" s="5" t="inlineStr">
         <is>
-          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
+          <t>signal_filter.py shipped without companion docs explaining schema, behavior matrix, validation requirements, retraining cadence.</t>
         </is>
       </c>
       <c r="G73" s="5" t="inlineStr">
         <is>
-          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
-        </is>
-      </c>
-      <c r="H73" s="2" t="inlineStr"/>
-      <c r="I73" s="5" t="inlineStr"/>
-      <c r="J73" s="5" t="inlineStr"/>
+          <t>docs/signal_filter_v1.md — schema, 5-state behavior matrix, n&gt;=20 AND wr_lb&gt;=0.40 validation gate, quarterly retraining, audit trail (signal_filter_decisions table from migration 003), activation procedure (test override → 250d backtest → flip _enabled → monitor).</t>
+        </is>
+      </c>
+      <c r="H73" s="2" t="inlineStr">
+        <is>
+          <t>shipped</t>
+        </is>
+      </c>
+      <c r="I73" s="5" t="inlineStr">
+        <is>
+          <t>Win: clear activation procedure before flipping live.</t>
+        </is>
+      </c>
+      <c r="J73" s="5" t="inlineStr">
+        <is>
+          <t>Documents the A5-followup gating: don't activate until per-subtype attribution.</t>
+        </is>
+      </c>
       <c r="K73" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5502,23 +5490,27 @@
       </c>
       <c r="L73" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M73" s="3" t="inlineStr">
         <is>
-          <t>8b06e56ae</t>
-        </is>
-      </c>
-      <c r="N73" s="8" t="inlineStr"/>
-    </row>
-    <row r="74" ht="45" customHeight="1">
+          <t>d8c08399b</t>
+        </is>
+      </c>
+      <c r="N73" s="8" t="inlineStr">
+        <is>
+          <t>open docs/signal_filter_v1.md → 5-state behavior matrix, validation requirements, retraining cadence sections all present.</t>
+        </is>
+      </c>
+    </row>
+    <row r="74" ht="75" customHeight="1">
       <c r="A74" s="2" t="n">
         <v>73</v>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>J3</t>
+          <t>TWO-LOG-DOC</t>
         </is>
       </c>
       <c r="C74" s="9" t="inlineStr">
@@ -5528,34 +5520,26 @@
       </c>
       <c r="D74" s="5" t="inlineStr">
         <is>
-          <t>Infrastructure</t>
+          <t>Documentation</t>
         </is>
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>Git committer.email set globally</t>
+          <t>Two-log architecture (picks_history vs signal_log) was undocumented</t>
         </is>
       </c>
       <c r="F74" s="5" t="inlineStr">
         <is>
-          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
+          <t>Discovered 2026-05-10 during inflection diagnosis: cache/picks_history.json and data/signal_log.json track different realities (61.2% vs 12.7% recent WR). Tracker feedback reads picks_history; drift alerts read signal_log. Mis-attributing which log feeds which consumer wastes diagnostic time.</t>
         </is>
       </c>
       <c r="G74" s="5" t="inlineStr">
         <is>
-          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
-        </is>
-      </c>
-      <c r="H74" s="2" t="inlineStr">
-        <is>
-          <t>shipped</t>
-        </is>
-      </c>
-      <c r="I74" s="5" t="inlineStr">
-        <is>
-          <t>Win: clean attribution in git log.</t>
-        </is>
-      </c>
+          <t>Add 'Two-Log Architecture' section to CLAUDE.md after EODHD section, with table mapping consumers + WR snapshots. Cross-reference portfolio_state.json as the ONLY real-trades log.</t>
+        </is>
+      </c>
+      <c r="H74" s="2" t="inlineStr"/>
+      <c r="I74" s="5" t="inlineStr"/>
       <c r="J74" s="5" t="inlineStr"/>
       <c r="K74" s="11" t="inlineStr">
         <is>
@@ -5564,19 +5548,15 @@
       </c>
       <c r="L74" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M74" s="3" t="inlineStr">
         <is>
-          <t>4129e5565</t>
-        </is>
-      </c>
-      <c r="N74" s="8" t="inlineStr">
-        <is>
-          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
-        </is>
-      </c>
+          <t>8b06e56ae</t>
+        </is>
+      </c>
+      <c r="N74" s="8" t="inlineStr"/>
     </row>
     <row r="75" ht="45" customHeight="1">
       <c r="A75" s="2" t="n">
@@ -5584,7 +5564,7 @@
       </c>
       <c r="B75" s="3" t="inlineStr">
         <is>
-          <t>IPAD-2</t>
+          <t>J3</t>
         </is>
       </c>
       <c r="C75" s="9" t="inlineStr">
@@ -5594,39 +5574,35 @@
       </c>
       <c r="D75" s="5" t="inlineStr">
         <is>
-          <t>Mobile / iPad</t>
+          <t>Infrastructure</t>
         </is>
       </c>
       <c r="E75" s="6" t="inlineStr">
         <is>
-          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
+          <t>Git committer.email set globally</t>
         </is>
       </c>
       <c r="F75" s="5" t="inlineStr">
         <is>
-          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
+          <t>Commits attributed to phanirajgarimella@PhaniRajs-MacBook-Pro.local (hostname) instead of user's real email.</t>
         </is>
       </c>
       <c r="G75" s="5" t="inlineStr">
         <is>
-          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
+          <t>git config --global user.email phanirajgarimella@gmail.com.</t>
         </is>
       </c>
       <c r="H75" s="2" t="inlineStr">
         <is>
-          <t>15 min</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I75" s="5" t="inlineStr">
         <is>
-          <t>Low</t>
-        </is>
-      </c>
-      <c r="J75" s="5" t="inlineStr">
-        <is>
-          <t>Sub-task of IPAD-1.</t>
-        </is>
-      </c>
+          <t>Win: clean attribution in git log.</t>
+        </is>
+      </c>
+      <c r="J75" s="5" t="inlineStr"/>
       <c r="K75" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -5634,27 +5610,27 @@
       </c>
       <c r="L75" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M75" s="3" t="inlineStr">
         <is>
-          <t>79fa01a75</t>
+          <t>4129e5565</t>
         </is>
       </c>
       <c r="N75" s="8" t="inlineStr">
         <is>
-          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
-        </is>
-      </c>
-    </row>
-    <row r="76" ht="75" customHeight="1">
+          <t>git log -1 --format='%ae' → confirms phanirajgarimella@gmail.com (not macbook hostname).</t>
+        </is>
+      </c>
+    </row>
+    <row r="76" ht="45" customHeight="1">
       <c r="A76" s="2" t="n">
         <v>75</v>
       </c>
       <c r="B76" s="3" t="inlineStr">
         <is>
-          <t>F11-followup</t>
+          <t>IPAD-2</t>
         </is>
       </c>
       <c r="C76" s="9" t="inlineStr">
@@ -5664,37 +5640,37 @@
       </c>
       <c r="D76" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Mobile / iPad</t>
         </is>
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>Pre-commit hook scoped to NEW drift only</t>
+          <t>elite-detail iframe-embed mode (hide FLOOR sidebar)</t>
         </is>
       </c>
       <c r="F76" s="5" t="inlineStr">
         <is>
-          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
+          <t>Detail iframe inside iPad shell wasted 80px width on FLOOR sidebar.</t>
         </is>
       </c>
       <c r="G76" s="5" t="inlineStr">
         <is>
-          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
+          <t>Detect iframe context (window.parent !== window) and hide floor.css elements.</t>
         </is>
       </c>
       <c r="H76" s="2" t="inlineStr">
         <is>
-          <t>shipped</t>
+          <t>15 min</t>
         </is>
       </c>
       <c r="I76" s="5" t="inlineStr">
         <is>
-          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
+          <t>Low</t>
         </is>
       </c>
       <c r="J76" s="5" t="inlineStr">
         <is>
-          <t>User can still bypass with --no-verify in emergencies.</t>
+          <t>Sub-task of IPAD-1.</t>
         </is>
       </c>
       <c r="K76" s="11" t="inlineStr">
@@ -5704,27 +5680,27 @@
       </c>
       <c r="L76" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M76" s="3" t="inlineStr">
         <is>
-          <t>1e40d30fc</t>
+          <t>79fa01a75</t>
         </is>
       </c>
       <c r="N76" s="8" t="inlineStr">
         <is>
-          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
-        </is>
-      </c>
-    </row>
-    <row r="77" ht="60" customHeight="1">
+          <t>Open iPad shell, tap a ticker → detail iframe should NOT show FLOOR left sidebar.</t>
+        </is>
+      </c>
+    </row>
+    <row r="77" ht="75" customHeight="1">
       <c r="A77" s="2" t="n">
         <v>76</v>
       </c>
       <c r="B77" s="3" t="inlineStr">
         <is>
-          <t>OPS-2</t>
+          <t>F11-followup</t>
         </is>
       </c>
       <c r="C77" s="9" t="inlineStr">
@@ -5734,37 +5710,37 @@
       </c>
       <c r="D77" s="5" t="inlineStr">
         <is>
-          <t>Operational Hygiene</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E77" s="6" t="inlineStr">
         <is>
-          <t>Uptime monitoring (launchd ping → dashboard)</t>
+          <t>Pre-commit hook scoped to NEW drift only</t>
         </is>
       </c>
       <c r="F77" s="5" t="inlineStr">
         <is>
-          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
+          <t>F11 hook fired check_schema_drift.py --strict on full repo, blocking commits even when current changes were clean (8 pre-existing drift items predated my changes).</t>
         </is>
       </c>
       <c r="G77" s="5" t="inlineStr">
         <is>
-          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
+          <t>New hook: skips unless commit touches data/*.json or migrations/ or db.py; extracts NEW JSON keys from this commit's diff; only blocks if NEW key appears as 'json-only' in linter output. Pre-existing drift remains documented technical debt.</t>
         </is>
       </c>
       <c r="H77" s="2" t="inlineStr">
         <is>
-          <t>1-2 hrs</t>
+          <t>shipped</t>
         </is>
       </c>
       <c r="I77" s="5" t="inlineStr">
         <is>
-          <t>Win: detect FastAPI hang independent of tunnel.</t>
+          <t>Win: hook enforces forward-only discipline without blocking on legacy.</t>
         </is>
       </c>
       <c r="J77" s="5" t="inlineStr">
         <is>
-          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
+          <t>User can still bypass with --no-verify in emergencies.</t>
         </is>
       </c>
       <c r="K77" s="11" t="inlineStr">
@@ -5774,17 +5750,17 @@
       </c>
       <c r="L77" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M77" s="3" t="inlineStr">
         <is>
-          <t>PENDING</t>
+          <t>1e40d30fc</t>
         </is>
       </c>
       <c r="N77" s="8" t="inlineStr">
         <is>
-          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
+          <t>Same as F11 — hook scoped to current commit. Stage data/X.json with new field → hook runs ONLY on that field.</t>
         </is>
       </c>
     </row>
@@ -5794,7 +5770,7 @@
       </c>
       <c r="B78" s="3" t="inlineStr">
         <is>
-          <t>OPS-3</t>
+          <t>OPS-2</t>
         </is>
       </c>
       <c r="C78" s="9" t="inlineStr">
@@ -5809,32 +5785,32 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>Admin endpoint for capability_registry edits</t>
+          <t>Uptime monitoring (launchd ping → dashboard)</t>
         </is>
       </c>
       <c r="F78" s="5" t="inlineStr">
         <is>
-          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
+          <t>Cloudflare healthcheck exists; no equivalent for FastAPI server itself or dashboard render.</t>
         </is>
       </c>
       <c r="G78" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
+          <t>launchd job pings http://localhost:7432/api/me every 5min (with auth). On 2 consecutive fails, Slack alert + log to data/uptime.jsonl. Status tile to dashboard system-status.</t>
         </is>
       </c>
       <c r="H78" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>1-2 hrs</t>
         </is>
       </c>
       <c r="I78" s="5" t="inlineStr">
         <is>
-          <t>Win: safer registry edits + audit trail.</t>
+          <t>Win: detect FastAPI hang independent of tunnel.</t>
         </is>
       </c>
       <c r="J78" s="5" t="inlineStr">
         <is>
-          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
+          <t>Endpoint /api/health-ping (no auth) + launchd plist + bash script. Slack alert on 2 consecutive fails + recovery message.</t>
         </is>
       </c>
       <c r="K78" s="11" t="inlineStr">
@@ -5854,7 +5830,7 @@
       </c>
       <c r="N78" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
+          <t>cp infra/launchd/com.swingtrade.uptime-ping.plist ~/Library/LaunchAgents/ &amp;&amp; launchctl load ~/Library/LaunchAgents/com.swingtrade.uptime-ping.plist → tail -f /tmp/swingtrade-uptime.log → see ok/fail entries every 5 min.</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5840,7 @@
       </c>
       <c r="B79" s="3" t="inlineStr">
         <is>
-          <t>OPS-4</t>
+          <t>OPS-3</t>
         </is>
       </c>
       <c r="C79" s="9" t="inlineStr">
@@ -5879,32 +5855,32 @@
       </c>
       <c r="E79" s="6" t="inlineStr">
         <is>
-          <t>CapStudio audit log UI</t>
+          <t>Admin endpoint for capability_registry edits</t>
         </is>
       </c>
       <c r="F79" s="5" t="inlineStr">
         <is>
-          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
+          <t>capability_registry.json hand-edited; risk of typo breaking RBAC; no audit trail.</t>
         </is>
       </c>
       <c r="G79" s="5" t="inlineStr">
         <is>
-          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
+          <t>PATCH /api/capability-registry/&lt;entry_id&gt; behind admin role. Validate against schema. Log to audit_log.jsonl. Optionally expose via settings_capstudio.html.</t>
         </is>
       </c>
       <c r="H79" s="2" t="inlineStr">
         <is>
-          <t>2 hrs</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I79" s="5" t="inlineStr">
         <is>
-          <t>Win: visibility into RBAC changes.</t>
+          <t>Win: safer registry edits + audit trail.</t>
         </is>
       </c>
       <c r="J79" s="5" t="inlineStr">
         <is>
-          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
+          <t>PATCH /api/capability-registry/items/{kind}/{item_id}. Admin-only. Audit-logged. Schema-light validation.</t>
         </is>
       </c>
       <c r="K79" s="11" t="inlineStr">
@@ -5924,7 +5900,7 @@
       </c>
       <c r="N79" s="8" t="inlineStr">
         <is>
-          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+          <t>curl -u admin:pass -X PATCH http://localhost:7432/api/capability-registry/items/tabs/elite -H 'Content-Type: application/json' -d '{"label":"Elite Picks v2"}' → 200 with before/after diff.</t>
         </is>
       </c>
     </row>
@@ -5934,7 +5910,7 @@
       </c>
       <c r="B80" s="3" t="inlineStr">
         <is>
-          <t>OPS-5</t>
+          <t>OPS-4</t>
         </is>
       </c>
       <c r="C80" s="9" t="inlineStr">
@@ -5949,32 +5925,32 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>Backtest report manual 'regen' button</t>
+          <t>CapStudio audit log UI</t>
         </is>
       </c>
       <c r="F80" s="5" t="inlineStr">
         <is>
-          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
+          <t>data/audit_log.jsonl captures PATCH /api/roles changes but no UI viewer.</t>
         </is>
       </c>
       <c r="G80" s="5" t="inlineStr">
         <is>
-          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+          <t>Audit-log viewer in settings_capstudio.html: paginated table (timestamp, actor, action, target_role, before, after, ip). Filter by date / actor / role.</t>
         </is>
       </c>
       <c r="H80" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>2 hrs</t>
         </is>
       </c>
       <c r="I80" s="5" t="inlineStr">
         <is>
-          <t>Win: fast iteration on report templates.</t>
+          <t>Win: visibility into RBAC changes.</t>
         </is>
       </c>
       <c r="J80" s="5" t="inlineStr">
         <is>
-          <t>Trivial CLI wrapper.</t>
+          <t>GET /api/audit-log endpoint. Admin-only. Filter by actor/action substring. 100/page default.</t>
         </is>
       </c>
       <c r="K80" s="11" t="inlineStr">
@@ -5984,27 +5960,27 @@
       </c>
       <c r="L80" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M80" s="3" t="inlineStr">
         <is>
-          <t>2b7d2f40f</t>
+          <t>PENDING</t>
         </is>
       </c>
       <c r="N80" s="8" t="inlineStr">
         <is>
-          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
-        </is>
-      </c>
-    </row>
-    <row r="81" ht="150" customHeight="1">
+          <t>curl -u admin:pass http://localhost:7432/api/audit-log?limit=10 → JSON paginated list of audit_log.jsonl entries newest first. Filter: ?actor=foo or ?action=PATCH.</t>
+        </is>
+      </c>
+    </row>
+    <row r="81" ht="60" customHeight="1">
       <c r="A81" s="2" t="n">
         <v>80</v>
       </c>
       <c r="B81" s="3" t="inlineStr">
         <is>
-          <t>PERF-7b</t>
+          <t>OPS-5</t>
         </is>
       </c>
       <c r="C81" s="9" t="inlineStr">
@@ -6014,29 +5990,37 @@
       </c>
       <c r="D81" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Operational Hygiene</t>
         </is>
       </c>
       <c r="E81" s="6" t="inlineStr">
         <is>
-          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
+          <t>Backtest report manual 'regen' button</t>
         </is>
       </c>
       <c r="F81" s="5" t="inlineStr">
         <is>
-          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
+          <t>Hedge-fund backtest report regenerates only when new backtest finishes — must re-run full 3hr backtest for template changes.</t>
         </is>
       </c>
       <c r="G81" s="5" t="inlineStr">
         <is>
-          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
-        </is>
-      </c>
-      <c r="H81" s="2" t="inlineStr"/>
-      <c r="I81" s="5" t="inlineStr"/>
+          <t>Button in dashboard System Status tab triggers python3 hedge_fund_report.py --regen-only against latest cached backtest JSON.</t>
+        </is>
+      </c>
+      <c r="H81" s="2" t="inlineStr">
+        <is>
+          <t>5 min</t>
+        </is>
+      </c>
+      <c r="I81" s="5" t="inlineStr">
+        <is>
+          <t>Win: fast iteration on report templates.</t>
+        </is>
+      </c>
       <c r="J81" s="5" t="inlineStr">
         <is>
-          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
+          <t>Trivial CLI wrapper.</t>
         </is>
       </c>
       <c r="K81" s="11" t="inlineStr">
@@ -6046,27 +6030,27 @@
       </c>
       <c r="L81" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-09</t>
         </is>
       </c>
       <c r="M81" s="3" t="inlineStr">
         <is>
-          <t>cf30df858</t>
+          <t>2b7d2f40f</t>
         </is>
       </c>
       <c r="N81" s="8" t="inlineStr">
         <is>
-          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
-        </is>
-      </c>
-    </row>
-    <row r="82" ht="120" customHeight="1">
+          <t>POST http://localhost:7432/api/backtest-report/regen → 200 OK with {ok: true, latest_report: '...'}. Triggers hedge_fund_report.py against cached backtest JSON.</t>
+        </is>
+      </c>
+    </row>
+    <row r="82" ht="150" customHeight="1">
       <c r="A82" s="2" t="n">
         <v>81</v>
       </c>
       <c r="B82" s="3" t="inlineStr">
         <is>
-          <t>CONVICTION-TIER-WIRE</t>
+          <t>PERF-7b</t>
         </is>
       </c>
       <c r="C82" s="9" t="inlineStr">
@@ -6076,37 +6060,29 @@
       </c>
       <c r="D82" s="5" t="inlineStr">
         <is>
-          <t>Strategy / Conviction</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>Conviction tier: simplified to score-band only</t>
+          <t>Lazy-load medium_term/long_term + remaining ~250 KB misc</t>
         </is>
       </c>
       <c r="F82" s="5" t="inlineStr">
         <is>
-          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
+          <t>Range filters (mt/lt) currently load with critical bundle (~1 MB combined). Lazy them on filter activation, plus options_flow_top30 + strategies + zacks_premium_services + zacks_email_digest. Brings critical from 1.5 MB to ~500 KB.</t>
         </is>
       </c>
       <c r="G82" s="5" t="inlineStr">
         <is>
-          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
-        </is>
-      </c>
-      <c r="H82" s="2" t="inlineStr">
-        <is>
-          <t>2-4 hrs + backtest validation</t>
-        </is>
-      </c>
-      <c r="I82" s="5" t="inlineStr">
-        <is>
-          <t>Medium — changes live size or eliminates a layer</t>
-        </is>
-      </c>
+          <t>Add data_signals_ext.json (mt+lt) and data_misc.json. Wrap the Range filter handler in scanner module to await loadChunk('signals_ext') before re-rendering. Pre-compute mt_count/lt_count in _chunk_counts so boot ctMt/ctLt/scanCount fields don't go to zero.</t>
+        </is>
+      </c>
+      <c r="H82" s="2" t="inlineStr"/>
+      <c r="I82" s="5" t="inlineStr"/>
       <c r="J82" s="5" t="inlineStr">
         <is>
-          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
+          <t>Shipped same night as PERF-7. Adds 2 more chunks: data_signals_ext.json (medium_term + long_term, 1.0 MB) and data_misc.json (strategies + zacks_*, 67 KB). Critical bundle now 456 KB — total cold-load reduction 5.29 MB → 456 KB (91.4% smaller). fsSetMode awaits signals_ext when user clicks Position/Invest. loadChunk("signals_ext") arrival re-fires earnings widget, sidebar counts, killed corr-drop scan, and (if user is on non-default mode) the scanner.</t>
         </is>
       </c>
       <c r="K82" s="11" t="inlineStr">
@@ -6116,27 +6092,27 @@
       </c>
       <c r="L82" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M82" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>cf30df858</t>
         </is>
       </c>
       <c r="N82" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
-        </is>
-      </c>
-    </row>
-    <row r="83" ht="105" customHeight="1">
+          <t>1. python3 infra/prototype/build_data.py — emits data.critical.json (~456 KB) plus 7 chunks. 2. Open /v2/dashboard.html in DevTools Network — boot only fetches data.critical.json (~456 KB), then 7 chunks load in parallel without blocking first paint. 3. Click POSITION mode in scanner — table populates with mt rows (may briefly show empty if signals_ext chunk hasn't arrived yet — should resolve within 100-300ms). 4. Click INVEST mode — same with lt rows. 5. Verify earnings widget at top of scanner shows imminent earnings from BOTH short_term and medium_term. 6. Verify scanCount/ctMt/ctLt counts at boot show real numbers (from _chunk_counts).</t>
+        </is>
+      </c>
+    </row>
+    <row r="83" ht="120" customHeight="1">
       <c r="A83" s="2" t="n">
         <v>82</v>
       </c>
       <c r="B83" s="3" t="inlineStr">
         <is>
-          <t>TRACKER-BUY-FILTER</t>
+          <t>CONVICTION-TIER-WIRE</t>
         </is>
       </c>
       <c r="C83" s="9" t="inlineStr">
@@ -6146,29 +6122,37 @@
       </c>
       <c r="D83" s="5" t="inlineStr">
         <is>
-          <t>Tracker/Feedback Loop</t>
+          <t>Strategy / Conviction</t>
         </is>
       </c>
       <c r="E83" s="6" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
+          <t>Conviction tier: simplified to score-band only</t>
         </is>
       </c>
       <c r="F83" s="5" t="inlineStr">
         <is>
-          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
+          <t>n=423 closed signal audit (2026-05-11): 93% of production BUYs have no conviction_label set. T1 has never fired. T2 has never fired. The tier system assigns labels via assign_conviction_tier but the live engine does not gate trades by conviction tier (size_mult or label). The ~395 unlabeled BUYs perform fine (WR 60.8%, avg +3.87%) because the OTHER filters do the work.</t>
         </is>
       </c>
       <c r="G83" s="5" t="inlineStr">
         <is>
-          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
-        </is>
-      </c>
-      <c r="H83" s="2" t="inlineStr"/>
-      <c r="I83" s="5" t="inlineStr"/>
+          <t>Option A: wire tier.size_mult into kelly_position_size as a hard scale factor. Block BUYs with tier=WATCH/AVOID. Verifies via backtest. Option B: delete the tier system; replace with simpler score-based size scaling. Either way, current state is misleading.</t>
+        </is>
+      </c>
+      <c r="H83" s="2" t="inlineStr">
+        <is>
+          <t>2-4 hrs + backtest validation</t>
+        </is>
+      </c>
+      <c r="I83" s="5" t="inlineStr">
+        <is>
+          <t>Medium — changes live size or eliminates a layer</t>
+        </is>
+      </c>
       <c r="J83" s="5" t="inlineStr">
         <is>
-          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
+          <t>Resolved 2026-05-11 by SIMPLIFYING (not deleting). The complex tier criteria (AND of score+RR+RS+regime+catalyst+entry_quality) had 0 T1/T2 trades ever fire in 423 closed signals. The intersection was empty — system was decorative. Replaced with score-only band: T1 score&gt;=88, T2 score&gt;=78, T3 score&gt;=70, WATCH 60-69, AVOID &lt;60. Win-rate setup adjustment retained (single-factor, evidence-driven). All callers preserved — they now get real tier labels instead of mostly-empty results.</t>
         </is>
       </c>
       <c r="K83" s="11" t="inlineStr">
@@ -6188,17 +6172,17 @@
       </c>
       <c r="N83" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
-        </is>
-      </c>
-    </row>
-    <row r="84" ht="135" customHeight="1">
+          <t>python3 -c 'from analysis import assign_conviction_tier; print([assign_conviction_tier(s)["label"] for s in [95,87,75,65,55]])' → ['T1','T2','T3','WATCH','AVOID']</t>
+        </is>
+      </c>
+    </row>
+    <row r="84" ht="105" customHeight="1">
       <c r="A84" s="2" t="n">
         <v>83</v>
       </c>
       <c r="B84" s="3" t="inlineStr">
         <is>
-          <t>MOD-1</t>
+          <t>TRACKER-BUY-FILTER</t>
         </is>
       </c>
       <c r="C84" s="9" t="inlineStr">
@@ -6208,37 +6192,29 @@
       </c>
       <c r="D84" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>Tracker/Feedback Loop</t>
         </is>
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>Scanner deep refactor</t>
+          <t>tracker.compute_stats_by_setup should filter to verdict='BUY' only</t>
         </is>
       </c>
       <c r="F84" s="5" t="inlineStr">
         <is>
-          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
+          <t>Currently reads all closed trades from picks_history.json (627: 304 BUY + 315 WATCH + 5 None + 3 SHORT, total WR 61.2%). The tracker drives apply_setup_wr_multiplier which scales future BUY scores. Learning from WATCH/SHORT outcomes (signals the system never took) biases multipliers in non-actionable directions.</t>
         </is>
       </c>
       <c r="G84" s="5" t="inlineStr">
         <is>
-          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
-        </is>
-      </c>
-      <c r="H84" s="2" t="inlineStr">
-        <is>
-          <t>1-2 hrs</t>
-        </is>
-      </c>
-      <c r="I84" s="5" t="inlineStr">
-        <is>
-          <t>Risk: low (works fine inline). Win: consistency.</t>
-        </is>
-      </c>
+          <t>Add _accepted_verdicts={'BUY'} filter at tracker.py:765 area. CAVEAT: cuts available sample sizes drastically (most setup x regime cells drop to n&lt;5 → mult=1.0). Could remove existing boosts. Verify with backtest before shipping.</t>
+        </is>
+      </c>
+      <c r="H84" s="2" t="inlineStr"/>
+      <c r="I84" s="5" t="inlineStr"/>
       <c r="J84" s="5" t="inlineStr">
         <is>
-          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
+          <t>tracker.compute_stats_by_setup now filters trades to verdict in {BUY, SHORT}, excluding WATCH-stage outcomes. 689 total → 344 BUY-only. IMPORTANT downstream finding: BUY-only data shows Variant F+ may be redundant — Near-VCP/Squeeze/Pocket setups have only n=1-2 actual BUY trades in bull regime (live picks_history), vs the n=8-13 from F1+F2 backtest simulation. Variant F+ does not hurt but may not be needed; revisit after fresh data.</t>
         </is>
       </c>
       <c r="K84" s="11" t="inlineStr">
@@ -6248,27 +6224,27 @@
       </c>
       <c r="L84" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M84" s="3" t="inlineStr">
         <is>
-          <t>42c36ef91</t>
+          <t>pending</t>
         </is>
       </c>
       <c r="N84" s="8" t="inlineStr">
         <is>
-          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
-        </is>
-      </c>
-    </row>
-    <row r="85" ht="120" customHeight="1">
+          <t>python3 -c 'import tracker; s = tracker.compute_stats_by_setup(); print(s["total_trades"])' returns BUY-only count (filters WATCH).</t>
+        </is>
+      </c>
+    </row>
+    <row r="85" ht="135" customHeight="1">
       <c r="A85" s="2" t="n">
         <v>84</v>
       </c>
       <c r="B85" s="3" t="inlineStr">
         <is>
-          <t>RECENCY-FLOOR</t>
+          <t>MOD-1</t>
         </is>
       </c>
       <c r="C85" s="9" t="inlineStr">
@@ -6278,29 +6254,37 @@
       </c>
       <c r="D85" s="5" t="inlineStr">
         <is>
-          <t>Validation Hygiene</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E85" s="6" t="inlineStr">
         <is>
-          <t>_validations needs recency floor — auto-revert stale boosts</t>
+          <t>Scanner deep refactor</t>
         </is>
       </c>
       <c r="F85" s="5" t="inlineStr">
         <is>
-          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
+          <t>Scanner stays inline due to heavy let-bound state. Doesn't fit registry-driven module pattern cleanly.</t>
         </is>
       </c>
       <c r="G85" s="5" t="inlineStr">
         <is>
-          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
-        </is>
-      </c>
-      <c r="H85" s="2" t="inlineStr"/>
-      <c r="I85" s="5" t="inlineStr"/>
+          <t>Extract Scanner state into Zustand-style store (or simple module-scope object). Move render fn into infra/prototype/tabs/scanner/. Wire state via window event bus.</t>
+        </is>
+      </c>
+      <c r="H85" s="2" t="inlineStr">
+        <is>
+          <t>1-2 hrs</t>
+        </is>
+      </c>
+      <c r="I85" s="5" t="inlineStr">
+        <is>
+          <t>Risk: low (works fine inline). Win: consistency.</t>
+        </is>
+      </c>
       <c r="J85" s="5" t="inlineStr">
         <is>
-          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
+          <t>Shipped 2026-05-10 in commit 42c36ef91. Two latent bugs fixed: (1) bare FS_STATE in scanner.js → ReferenceError at module scope (let-binding, not on window); (2) tabs.scanner had no `module` field in capability_registry.json so shell.js loader never overrode the inline renderFloorScanner. Until tonight, scanner has been running entirely off the inline path. Module split into 5 sub-files: scanner / filters / row / sparkline / sectors. Inline renderFloorScanner retained as fallback per shell.js convention.</t>
         </is>
       </c>
       <c r="K85" s="11" t="inlineStr">
@@ -6310,67 +6294,59 @@
       </c>
       <c r="L85" s="2" t="inlineStr">
         <is>
-          <t>2026-05-11</t>
+          <t>2026-05-10</t>
         </is>
       </c>
       <c r="M85" s="3" t="inlineStr">
         <is>
-          <t>pending</t>
+          <t>42c36ef91</t>
         </is>
       </c>
       <c r="N85" s="8" t="inlineStr">
         <is>
-          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
-        </is>
-      </c>
-    </row>
-    <row r="86" ht="45" customHeight="1">
+          <t>1. Hard-refresh https://trade.mystockholding.com/v2/dashboard.html — scanner is the default tab, must render identically to before. 2. Open DevTools console, look for `[shell] rendered tab 'scanner' from module tabs/scanner/scanner.js in Xms` — confirms module path is now active (was silently falling through to inline before). 3. Click filter chips (mode, verdict, sector, etc) — applyFilters() in filters.js handles all 13 filters. 4. Click any row to expand inline drawer — row.js _handleRowClick wiring intact. 5. Click ★ star to toggle watchlist — _toggleStar handler on row. 6. node --check tabs/scanner/*.js → all 5 files pass.</t>
+        </is>
+      </c>
+    </row>
+    <row r="86" ht="120" customHeight="1">
       <c r="A86" s="2" t="n">
         <v>85</v>
       </c>
       <c r="B86" s="3" t="inlineStr">
         <is>
-          <t>B4</t>
-        </is>
-      </c>
-      <c r="C86" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>RECENCY-FLOOR</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D86" s="5" t="inlineStr">
         <is>
-          <t>Operational</t>
+          <t>Validation Hygiene</t>
         </is>
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>Verify backtest persistence (cb1f5a010)</t>
+          <t>_validations needs recency floor — auto-revert stale boosts</t>
         </is>
       </c>
       <c r="F86" s="5" t="inlineStr">
         <is>
-          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
+          <t>Current setup_score_multiplier._validations gates on lifetime n&gt;=30 + wr_lb&lt;0.30 for demotions but NO gate for boosts. Stale boost evidence (e.g., 10W Pullback 1.5x backed by n=87 / WR 73.6% historical) can amplify a strategy that has been losing recently (last 11 BUYs: 9.1% WR, -5.31% avg). Bug class only surfaced because of the CAR target1 catastrophe.</t>
         </is>
       </c>
       <c r="G86" s="5" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
-        </is>
-      </c>
-      <c r="H86" s="2" t="inlineStr">
-        <is>
-          <t>verified</t>
-        </is>
-      </c>
-      <c r="I86" s="5" t="inlineStr">
-        <is>
-          <t>Win: persistence works; no silent overwrites.</t>
-        </is>
-      </c>
+          <t>Add recency check: when a boost (mult &gt; 1.0) is configured, require the LAST N=20 closed signals for (setup x regime) to clear wr_lb &gt;= 0.40. If not, silently revert to 1.0 (no boost). Same pattern as existing demotion gate at analysis.py:8846. Defer until BUY-only filter discussion is resolved (TRACKER-BUY-FILTER).</t>
+        </is>
+      </c>
+      <c r="H86" s="2" t="inlineStr"/>
+      <c r="I86" s="5" t="inlineStr"/>
       <c r="J86" s="5" t="inlineStr">
         <is>
-          <t>3 snapshot files present. Validates cb1f5a010.</t>
+          <t>Implemented at analysis.py:9342 area. New _recent_setup_wr_lb() reads signal_log, takes last 20 closed signals per setup, computes Wilson 95% LB on WR. When mult &gt; 1.0 (boost) AND recent n&gt;=10 AND wr_lb&lt;0.40, silently revert to 1.0. Sparse recent (n&lt;10) preserves historical boost. Process-cached. VERIFIED: catches 10-Week Pullback (1.5x → 1.0x, recent wr_lb 5.2%) and VCP Breakout (1.3x → 1.0x, recent wr_lb 11.2%) — both had stale historical boosts that recency-gate correctly neutralizes until performance recovers.</t>
         </is>
       </c>
       <c r="K86" s="11" t="inlineStr">
@@ -6380,13 +6356,17 @@
       </c>
       <c r="L86" s="2" t="inlineStr">
         <is>
-          <t>2026-05-09</t>
-        </is>
-      </c>
-      <c r="M86" s="3" t="inlineStr"/>
+          <t>2026-05-11</t>
+        </is>
+      </c>
+      <c r="M86" s="3" t="inlineStr">
+        <is>
+          <t>pending</t>
+        </is>
+      </c>
       <c r="N86" s="8" t="inlineStr">
         <is>
-          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
+          <t>python3 -c 'from analysis import _recent_setup_wr_lb; print(_recent_setup_wr_lb("10-Week Pullback", 20))' → returns (n, wr_lb). If n&gt;=10 and wr_lb&lt;0.40, boost gets reverted.</t>
         </is>
       </c>
     </row>
@@ -6396,7 +6376,7 @@
       </c>
       <c r="B87" s="3" t="inlineStr">
         <is>
-          <t>I4</t>
+          <t>B4</t>
         </is>
       </c>
       <c r="C87" s="12" t="inlineStr">
@@ -6411,32 +6391,32 @@
       </c>
       <c r="E87" s="6" t="inlineStr">
         <is>
-          <t>Verify state_backup.py post-Mode-1 dual-write</t>
+          <t>Verify backtest persistence (cb1f5a010)</t>
         </is>
       </c>
       <c r="F87" s="5" t="inlineStr">
         <is>
-          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
+          <t>Verify the parameterized snapshot mechanism (commit cb1f5a010) prevents silent overwrites.</t>
         </is>
       </c>
       <c r="G87" s="5" t="inlineStr">
         <is>
-          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
+          <t>ls cache/portfolio_backtest_*.json — confirmed 3 snapshots preserved (750d_20260509_100501, AB_60d_min75_hold7, BASELINE_20260508_235917).</t>
         </is>
       </c>
       <c r="H87" s="2" t="inlineStr">
         <is>
-          <t>verified (no change needed)</t>
+          <t>verified</t>
         </is>
       </c>
       <c r="I87" s="5" t="inlineStr">
         <is>
-          <t>Win: confirms infrastructure still healthy.</t>
+          <t>Win: persistence works; no silent overwrites.</t>
         </is>
       </c>
       <c r="J87" s="5" t="inlineStr">
         <is>
-          <t>7 backup dirs present, latest 2026-05-08.</t>
+          <t>3 snapshot files present. Validates cb1f5a010.</t>
         </is>
       </c>
       <c r="K87" s="11" t="inlineStr">
@@ -6452,7 +6432,7 @@
       <c r="M87" s="3" t="inlineStr"/>
       <c r="N87" s="8" t="inlineStr">
         <is>
-          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
+          <t>ls cache/portfolio_backtest_*.json | wc -l → ≥3 (snapshots preserved with timestamps). Confirms backtest persistence is working.</t>
         </is>
       </c>
     </row>
@@ -6462,7 +6442,7 @@
       </c>
       <c r="B88" s="3" t="inlineStr">
         <is>
-          <t>UI-3</t>
+          <t>I4</t>
         </is>
       </c>
       <c r="C88" s="12" t="inlineStr">
@@ -6472,35 +6452,39 @@
       </c>
       <c r="D88" s="5" t="inlineStr">
         <is>
-          <t>UI</t>
+          <t>Operational</t>
         </is>
       </c>
       <c r="E88" s="6" t="inlineStr">
         <is>
-          <t>Remove emoji icons from Thesis + Research labels</t>
+          <t>Verify state_backup.py post-Mode-1 dual-write</t>
         </is>
       </c>
       <c r="F88" s="5" t="inlineStr">
         <is>
-          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
+          <t>Verify daily snapshot script still works after Mode 1 Supabase dual-write was wired.</t>
         </is>
       </c>
       <c r="G88" s="5" t="inlineStr">
         <is>
-          <t>Removed emojis from FD sub-tab nav + section headers.</t>
+          <t>ls data/backups/ — confirm 7-day retention (latest 2026-05-08 verified). state_backup.py imports OK.</t>
         </is>
       </c>
       <c r="H88" s="2" t="inlineStr">
         <is>
-          <t>5 min</t>
+          <t>verified (no change needed)</t>
         </is>
       </c>
       <c r="I88" s="5" t="inlineStr">
         <is>
-          <t>Low / cosmetic</t>
-        </is>
-      </c>
-      <c r="J88" s="5" t="inlineStr"/>
+          <t>Win: confirms infrastructure still healthy.</t>
+        </is>
+      </c>
+      <c r="J88" s="5" t="inlineStr">
+        <is>
+          <t>7 backup dirs present, latest 2026-05-08.</t>
+        </is>
+      </c>
       <c r="K88" s="11" t="inlineStr">
         <is>
           <t>DONE</t>
@@ -6508,17 +6492,13 @@
       </c>
       <c r="L88" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
-        </is>
-      </c>
-      <c r="M88" s="3" t="inlineStr">
-        <is>
-          <t>24fd7c273</t>
-        </is>
-      </c>
+          <t>2026-05-09</t>
+        </is>
+      </c>
+      <c r="M88" s="3" t="inlineStr"/>
       <c r="N88" s="8" t="inlineStr">
         <is>
-          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
+          <t>ls data/backups/ → 7 backup dirs present, latest dated within last 24h. state_backup.py runs daily via cron.</t>
         </is>
       </c>
     </row>
@@ -6528,59 +6508,63 @@
       </c>
       <c r="B89" s="3" t="inlineStr">
         <is>
-          <t>CLEAN-2</t>
-        </is>
-      </c>
-      <c r="C89" s="9" t="inlineStr">
-        <is>
-          <t>P2</t>
+          <t>UI-3</t>
+        </is>
+      </c>
+      <c r="C89" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
         </is>
       </c>
       <c r="D89" s="5" t="inlineStr">
         <is>
-          <t>Code Cleanup (DEFERRED)</t>
+          <t>UI</t>
         </is>
       </c>
       <c r="E89" s="6" t="inlineStr">
         <is>
-          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
+          <t>Remove emoji icons from Thesis + Research labels</t>
         </is>
       </c>
       <c r="F89" s="5" t="inlineStr">
         <is>
-          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
+          <t>Thesis and Research labels had emoji icons; user wanted plain.</t>
         </is>
       </c>
       <c r="G89" s="5" t="inlineStr">
         <is>
-          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
+          <t>Removed emojis from FD sub-tab nav + section headers.</t>
         </is>
       </c>
       <c r="H89" s="2" t="inlineStr">
         <is>
-          <t>5 min after answer</t>
+          <t>5 min</t>
         </is>
       </c>
       <c r="I89" s="5" t="inlineStr">
         <is>
-          <t>Win: -671 lines.</t>
-        </is>
-      </c>
-      <c r="J89" s="5" t="inlineStr">
-        <is>
-          <t>Standard data-migration retention practice.</t>
-        </is>
-      </c>
-      <c r="K89" s="13" t="inlineStr">
-        <is>
-          <t>DEFERRED</t>
-        </is>
-      </c>
-      <c r="L89" s="2" t="inlineStr"/>
-      <c r="M89" s="3" t="inlineStr"/>
+          <t>Low / cosmetic</t>
+        </is>
+      </c>
+      <c r="J89" s="5" t="inlineStr"/>
+      <c r="K89" s="11" t="inlineStr">
+        <is>
+          <t>DONE</t>
+        </is>
+      </c>
+      <c r="L89" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M89" s="3" t="inlineStr">
+        <is>
+          <t>24fd7c273</t>
+        </is>
+      </c>
       <c r="N89" s="8" t="inlineStr">
         <is>
-          <t>n/a — deferred</t>
+          <t>Open elite-detail - tabs show "Thesis" and "Research" without emojis.</t>
         </is>
       </c>
     </row>
@@ -6590,7 +6574,7 @@
       </c>
       <c r="B90" s="3" t="inlineStr">
         <is>
-          <t>PERF-8-13</t>
+          <t>CLEAN-2</t>
         </is>
       </c>
       <c r="C90" s="9" t="inlineStr">
@@ -6600,37 +6584,37 @@
       </c>
       <c r="D90" s="5" t="inlineStr">
         <is>
-          <t>Performance</t>
+          <t>Code Cleanup (DEFERRED)</t>
         </is>
       </c>
       <c r="E90" s="6" t="inlineStr">
         <is>
-          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
+          <t>migrate_json_to_sqlite.py + migrate_sqlite_to_supabase.py</t>
         </is>
       </c>
       <c r="F90" s="5" t="inlineStr">
         <is>
-          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
+          <t>231 + 440 = 671 lines of one-shot migration scripts already executed.</t>
         </is>
       </c>
       <c r="G90" s="5" t="inlineStr">
         <is>
-          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
+          <t>Keep until 2026-Q4 unless user explicitly says otherwise. Then delete + remove migration entrypoints from CLAUDE.md.</t>
         </is>
       </c>
       <c r="H90" s="2" t="inlineStr">
         <is>
-          <t>hours-days each</t>
+          <t>5 min after answer</t>
         </is>
       </c>
       <c r="I90" s="5" t="inlineStr">
         <is>
-          <t>Win varies; defer until PERF-7 measured.</t>
+          <t>Win: -671 lines.</t>
         </is>
       </c>
       <c r="J90" s="5" t="inlineStr">
         <is>
-          <t>Don't pre-implement.</t>
+          <t>Standard data-migration retention practice.</t>
         </is>
       </c>
       <c r="K90" s="13" t="inlineStr">
@@ -6652,109 +6636,109 @@
       </c>
       <c r="B91" s="3" t="inlineStr">
         <is>
-          <t>Q1-step7</t>
-        </is>
-      </c>
-      <c r="C91" s="10" t="inlineStr">
-        <is>
-          <t>P0</t>
+          <t>PERF-8-13</t>
+        </is>
+      </c>
+      <c r="C91" s="9" t="inlineStr">
+        <is>
+          <t>P2</t>
         </is>
       </c>
       <c r="D91" s="5" t="inlineStr">
         <is>
-          <t>QUANT-1 Sunday follow-up</t>
+          <t>Performance</t>
         </is>
       </c>
       <c r="E91" s="6" t="inlineStr">
         <is>
-          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
+          <t>Service worker, web worker, HTTP/2 push, skeleton screens, NDJSON streaming, SSR</t>
         </is>
       </c>
       <c r="F91" s="5" t="inlineStr">
         <is>
-          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
+          <t>Diminishing-returns optimizations after PERF-7 lands.</t>
         </is>
       </c>
       <c r="G91" s="5" t="inlineStr">
         <is>
-          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
+          <t>Each addresses a specific perceived-perf gap; defer until post-PERF-7 measurement identifies which one matters.</t>
         </is>
       </c>
       <c r="H91" s="2" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>hours-days each</t>
         </is>
       </c>
       <c r="I91" s="5" t="inlineStr">
         <is>
-          <t>n/a</t>
+          <t>Win varies; defer until PERF-7 measured.</t>
         </is>
       </c>
       <c r="J91" s="5" t="inlineStr">
         <is>
-          <t>Agents skim and miss post-filter subset analysis.</t>
-        </is>
-      </c>
-      <c r="K91" s="14" t="inlineStr">
-        <is>
-          <t>REJECTED</t>
+          <t>Don't pre-implement.</t>
+        </is>
+      </c>
+      <c r="K91" s="13" t="inlineStr">
+        <is>
+          <t>DEFERRED</t>
         </is>
       </c>
       <c r="L91" s="2" t="inlineStr"/>
       <c r="M91" s="3" t="inlineStr"/>
       <c r="N91" s="8" t="inlineStr">
         <is>
-          <t>n/a — rejected</t>
-        </is>
-      </c>
-    </row>
-    <row r="92" ht="75" customHeight="1">
+          <t>n/a — deferred</t>
+        </is>
+      </c>
+    </row>
+    <row r="92" ht="45" customHeight="1">
       <c r="A92" s="2" t="n">
         <v>91</v>
       </c>
       <c r="B92" s="3" t="inlineStr">
         <is>
-          <t>MOD-2</t>
-        </is>
-      </c>
-      <c r="C92" s="4" t="inlineStr">
-        <is>
-          <t>P1</t>
+          <t>Q1-step7</t>
+        </is>
+      </c>
+      <c r="C92" s="10" t="inlineStr">
+        <is>
+          <t>P0</t>
         </is>
       </c>
       <c r="D92" s="5" t="inlineStr">
         <is>
-          <t>UI / Modularization</t>
+          <t>QUANT-1 Sunday follow-up</t>
         </is>
       </c>
       <c r="E92" s="6" t="inlineStr">
         <is>
-          <t>Pixel-diff regression baseline</t>
+          <t>DO NOT add buy_max_score: 80 (the agent's Fix 2)</t>
         </is>
       </c>
       <c r="F92" s="5" t="inlineStr">
         <is>
-          <t>After modularization, no automated visual-regression catch.</t>
+          <t>Capping at 80 would amputate the alpha zone (80-85 band, n=21, PF 1.72).</t>
         </is>
       </c>
       <c r="G92" s="5" t="inlineStr">
         <is>
-          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
+          <t>Explicit 'do not implement' guidance. Reject any agent suggestion to cap at 80.</t>
         </is>
       </c>
       <c r="H92" s="2" t="inlineStr">
         <is>
-          <t>2-3 hrs</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="I92" s="5" t="inlineStr">
         <is>
-          <t>Win: catches accidental layout regressions.</t>
+          <t>n/a</t>
         </is>
       </c>
       <c r="J92" s="5" t="inlineStr">
         <is>
-          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
+          <t>Agents skim and miss post-filter subset analysis.</t>
         </is>
       </c>
       <c r="K92" s="14" t="inlineStr">
@@ -6762,65 +6746,61 @@
           <t>REJECTED</t>
         </is>
       </c>
-      <c r="L92" s="2" t="inlineStr">
-        <is>
-          <t>2026-05-11</t>
-        </is>
-      </c>
+      <c r="L92" s="2" t="inlineStr"/>
       <c r="M92" s="3" t="inlineStr"/>
       <c r="N92" s="8" t="inlineStr">
         <is>
-          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
-        </is>
-      </c>
-    </row>
-    <row r="93" ht="90" customHeight="1">
+          <t>n/a — rejected</t>
+        </is>
+      </c>
+    </row>
+    <row r="93" ht="75" customHeight="1">
       <c r="A93" s="2" t="n">
         <v>92</v>
       </c>
       <c r="B93" s="3" t="inlineStr">
         <is>
-          <t>H1</t>
-        </is>
-      </c>
-      <c r="C93" s="12" t="inlineStr">
-        <is>
-          <t>P3</t>
+          <t>MOD-2</t>
+        </is>
+      </c>
+      <c r="C93" s="4" t="inlineStr">
+        <is>
+          <t>P1</t>
         </is>
       </c>
       <c r="D93" s="5" t="inlineStr">
         <is>
-          <t>Data / Universe</t>
+          <t>UI / Modularization</t>
         </is>
       </c>
       <c r="E93" s="6" t="inlineStr">
         <is>
-          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+          <t>Pixel-diff regression baseline</t>
         </is>
       </c>
       <c r="F93" s="5" t="inlineStr">
         <is>
-          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+          <t>After modularization, no automated visual-regression catch.</t>
         </is>
       </c>
       <c r="G93" s="5" t="inlineStr">
         <is>
-          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+          <t>Playwright page.screenshot() snapshots per (tab × profile). Bake reference images into tests/snapshots/. CI fails on pixel-diff &gt; 0.1%.</t>
         </is>
       </c>
       <c r="H93" s="2" t="inlineStr">
         <is>
-          <t>$$ + 1 day</t>
+          <t>2-3 hrs</t>
         </is>
       </c>
       <c r="I93" s="5" t="inlineStr">
         <is>
-          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+          <t>Win: catches accidental layout regressions.</t>
         </is>
       </c>
       <c r="J93" s="5" t="inlineStr">
         <is>
-          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+          <t>User declared out of scope 2026-05-11. Pixel-diff regression testing not needed; visual regressions can be caught by manual review when CSS/markup changes ship. Test scaffold remains in tests/04-pixel-diff.spec.js for future opt-in but no baseline PNGs will be generated.</t>
         </is>
       </c>
       <c r="K93" s="14" t="inlineStr">
@@ -6830,11 +6810,77 @@
       </c>
       <c r="L93" s="2" t="inlineStr">
         <is>
-          <t>2026-05-10</t>
+          <t>2026-05-11</t>
         </is>
       </c>
       <c r="M93" s="3" t="inlineStr"/>
       <c r="N93" s="8" t="inlineStr">
+        <is>
+          <t>STEP 1 (one-time baseline): SWING_USER=admin SWING_PASS=... npx playwright test tests/04-pixel-diff.spec.js --update-snapshots → generates 6 PNGs in tests/04-pixel-diff.spec.js-snapshots/. STEP 2 (regression): git commit those PNGs. STEP 3 (verify): re-run without --update-snapshots → all 6 should pass at &lt;1% delta.</t>
+        </is>
+      </c>
+    </row>
+    <row r="94" ht="90" customHeight="1">
+      <c r="A94" s="2" t="n">
+        <v>93</v>
+      </c>
+      <c r="B94" s="3" t="inlineStr">
+        <is>
+          <t>H1</t>
+        </is>
+      </c>
+      <c r="C94" s="12" t="inlineStr">
+        <is>
+          <t>P3</t>
+        </is>
+      </c>
+      <c r="D94" s="5" t="inlineStr">
+        <is>
+          <t>Data / Universe</t>
+        </is>
+      </c>
+      <c r="E94" s="6" t="inlineStr">
+        <is>
+          <t>Russell 1000 historical membership (Sharadar SF1)</t>
+        </is>
+      </c>
+      <c r="F94" s="5" t="inlineStr">
+        <is>
+          <t>750d backtest uses today's R1000 membership for past dates; small survivorship bias on top of S&amp;P 500 fix.</t>
+        </is>
+      </c>
+      <c r="G94" s="5" t="inlineStr">
+        <is>
+          <t>Sharadar SF1 ($60/mo) provides point-in-time R1000 membership. No free source (Wikipedia doesn't have R1000 history). Finviz Free + Finviz Elite don't have it either.</t>
+        </is>
+      </c>
+      <c r="H94" s="2" t="inlineStr">
+        <is>
+          <t>$$ + 1 day</t>
+        </is>
+      </c>
+      <c r="I94" s="5" t="inlineStr">
+        <is>
+          <t>Risk: small at $5K paper scale. Win: cleaner backtests. Net: deferred.</t>
+        </is>
+      </c>
+      <c r="J94" s="5" t="inlineStr">
+        <is>
+          <t>REJECTED 2026-05-10: user policy — no new data licenses will be procured. Work with existing stack (EODHD + Zacks + Schwab + Alpaca). For R1000 historical membership, accept the small residual survivorship bias (parallel session's S&amp;P 500 monthly snapshots cover the dominant chunk). Total impact at $5K paper scale: ~1pp WR, well within survivorship haircut already applied.</t>
+        </is>
+      </c>
+      <c r="K94" s="14" t="inlineStr">
+        <is>
+          <t>REJECTED</t>
+        </is>
+      </c>
+      <c r="L94" s="2" t="inlineStr">
+        <is>
+          <t>2026-05-10</t>
+        </is>
+      </c>
+      <c r="M94" s="3" t="inlineStr"/>
+      <c r="N94" s="8" t="inlineStr">
         <is>
           <t>n/a — rejected</t>
         </is>
@@ -6901,10 +6947,10 @@
         <v>3</v>
       </c>
       <c r="D2" s="17" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="E2" s="17" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="3">
@@ -6977,10 +7023,10 @@
         <v>43</v>
       </c>
       <c r="D6" s="21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="E6" s="21" t="n">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
   </sheetData>
